--- a/Docs/SkillTemplates/スキル定義テンプレート.xlsx
+++ b/Docs/SkillTemplates/スキル定義テンプレート.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル" sheetId="1" r:id="Rd90710111c414c16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="モンスター列追加例" sheetId="2" r:id="Rb4464bc53c6b4419"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="3" r:id="R5376a4b0798c4dfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル" sheetId="1" r:id="R8872928e537f4ebf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="モンスター列追加例" sheetId="2" r:id="R991bb1496a2f4cac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="3" r:id="R9d6a79c2007b48b5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,7 +91,7 @@
       <x:name val="Noto Sans JP"/>
     </x:font>
   </x:fonts>
-  <x:fills count="18">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -178,6 +178,11 @@
         <x:fgColor rgb="FFFFF3D5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF214E66"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border>
@@ -191,7 +196,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="90">
+  <x:cellXfs count="96">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -406,6 +411,16 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -9698,344 +9713,1476 @@
       </x:c>
     </x:row>
     <x:row r="40" ht="25" customHeight="1">
-      <x:c r="A40" s="10"/>
-      <x:c r="D40" s="12"/>
-      <x:c r="E40" s="12"/>
-      <x:c r="F40" s="12"/>
-      <x:c r="G40" s="14"/>
-      <x:c r="H40" s="14"/>
-      <x:c r="I40" s="14"/>
-      <x:c r="J40" s="14"/>
-      <x:c r="N40" s="14"/>
-      <x:c r="O40" s="12"/>
-      <x:c r="S40" s="14"/>
-      <x:c r="T40" s="12"/>
-      <x:c r="V40" s="42" t="str">
+      <x:c r="A40" s="93" t="str">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B40" s="90" t="str">
+        <x:v>衝撃波</x:v>
+      </x:c>
+      <x:c r="C40" s="90" t="str">
+        <x:v>使用者の位置に衝撃波を表示し、半径3の敵へ一度だけダメージを与える。</x:v>
+      </x:c>
+      <x:c r="D40" s="94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E40" s="94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F40" s="94" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G40" s="95" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H40" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I40" s="95" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="J40" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K40" s="90" t="str">
+        <x:v>自身</x:v>
+      </x:c>
+      <x:c r="L40" s="90" t="str">
+        <x:v>ダメージ</x:v>
+      </x:c>
+      <x:c r="M40" s="90" t="str">
+        <x:v>攻撃力</x:v>
+      </x:c>
+      <x:c r="N40" s="95" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="O40" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P40" s="90" t="str">
+        <x:v>使用者と同じ</x:v>
+      </x:c>
+      <x:c r="Q40" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="R40" s="90" t="str">
+        <x:v>範囲内の敵</x:v>
+      </x:c>
+      <x:c r="S40" s="95" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T40" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U40" s="90" t="str">
+        <x:v>発射物</x:v>
+      </x:c>
+      <x:c r="V40" s="42" t="n">
         <x:f>IF($A40="","",IF(AND($U40="発射物",$DI40&lt;&gt;"パッシブ"),$BE40,0))</x:f>
-      </x:c>
-      <x:c r="W40" s="42" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W40" s="42" t="n">
         <x:f>IF($A40="","",IF(AND($U40="発射物",$DI40&lt;&gt;"パッシブ"),$BF40,0))</x:f>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="X40" s="42" t="str">
         <x:f>IF($A40="","",IF(AND($U40="発射物",$DI40&lt;&gt;"パッシブ"),IF($BG40="有効","有効","無効"),"無効"))</x:f>
-      </x:c>
-      <x:c r="AD40" s="14"/>
-      <x:c r="AE40" s="14"/>
-      <x:c r="AF40" s="14"/>
-      <x:c r="AH40" s="14"/>
-      <x:c r="AJ40" s="14"/>
-      <x:c r="AN40" s="14"/>
-      <x:c r="AO40" s="14"/>
-      <x:c r="AP40" s="14"/>
-      <x:c r="AR40" s="14"/>
-      <x:c r="AT40" s="14"/>
-      <x:c r="AX40" s="14"/>
-      <x:c r="AY40" s="14"/>
-      <x:c r="AZ40" s="14"/>
-      <x:c r="BB40" s="14"/>
-      <x:c r="BD40" s="14"/>
-      <x:c r="BE40" s="14"/>
-      <x:c r="BF40" s="14"/>
-      <x:c r="BK40" s="14"/>
-      <x:c r="BM40" s="14"/>
-      <x:c r="BN40" s="14"/>
-      <x:c r="BP40" s="14"/>
-      <x:c r="BQ40" s="14"/>
-      <x:c r="BR40" s="14"/>
-      <x:c r="BT40" s="14"/>
-      <x:c r="BU40" s="14"/>
-      <x:c r="BV40" s="14"/>
-      <x:c r="BW40" s="14"/>
-      <x:c r="BX40" s="14"/>
-      <x:c r="BY40" s="14"/>
-      <x:c r="BZ40" s="14"/>
-      <x:c r="CA40" s="14"/>
-      <x:c r="CB40" s="14"/>
-      <x:c r="CC40" s="14"/>
-      <x:c r="CD40" s="14"/>
-      <x:c r="CE40" s="14"/>
-      <x:c r="CF40" s="14"/>
-      <x:c r="CJ40" s="14"/>
-      <x:c r="CK40" s="14"/>
-      <x:c r="CL40" s="14"/>
-      <x:c r="CM40" s="14"/>
-      <x:c r="CO40" s="14"/>
-      <x:c r="CQ40" s="14"/>
-      <x:c r="CS40" s="14"/>
-      <x:c r="CT40" s="14"/>
-      <x:c r="CU40" s="14"/>
-      <x:c r="CW40" s="14"/>
-      <x:c r="CX40" s="14"/>
-      <x:c r="CY40" s="14"/>
-      <x:c r="CZ40" s="14"/>
-      <x:c r="DC40" s="14"/>
-      <x:c r="DD40" s="14"/>
-      <x:c r="DI40" s="88"/>
-      <x:c r="DJ40" s="88"/>
-      <x:c r="DK40" s="88"/>
-      <x:c r="DL40" s="88"/>
-      <x:c r="DM40" s="88"/>
-      <x:c r="DN40" s="88"/>
-      <x:c r="DO40" s="88"/>
-      <x:c r="DP40" s="88"/>
-      <x:c r="DQ40" s="88"/>
-      <x:c r="DR40" s="88"/>
-      <x:c r="DS40" s="88"/>
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="Y40" s="90"/>
+      <x:c r="Z40" s="90"/>
+      <x:c r="AA40" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AB40" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AC40" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AD40" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE40" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF40" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG40" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AH40" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AI40" s="90" t="str">
+        <x:v>時間更新</x:v>
+      </x:c>
+      <x:c r="AJ40" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK40" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AL40" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AM40" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AN40" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO40" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP40" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ40" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AR40" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS40" s="90" t="str">
+        <x:v>時間更新</x:v>
+      </x:c>
+      <x:c r="AT40" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU40" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AV40" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AW40" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AX40" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY40" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ40" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA40" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="BB40" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC40" s="90" t="str">
+        <x:v>時間更新</x:v>
+      </x:c>
+      <x:c r="BD40" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE40" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF40" s="95" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="BG40" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BH40" s="90"/>
+      <x:c r="BI40" s="90" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="BJ40" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BK40" s="95" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="BL40" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BM40" s="95" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="BN40" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BO40" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BP40" s="95" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BQ40" s="95" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="BR40" s="95" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BS40" s="90" t="str">
+        <x:v>その場</x:v>
+      </x:c>
+      <x:c r="BT40" s="95" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="BU40" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="BV40" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BW40" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="BX40" s="95" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BY40" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="BZ40" s="95" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="CA40" s="95" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="CB40" s="95" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="CC40" s="95" t="n">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="CD40" s="95" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="CE40" s="95" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CF40" s="95" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CG40" s="90" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="CH40" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CI40" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CJ40" s="95" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="CK40" s="95" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="CL40" s="95" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="CM40" s="95" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="CN40" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CO40" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CP40" s="90" t="str">
+        <x:v>追尾</x:v>
+      </x:c>
+      <x:c r="CQ40" s="95" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="CR40" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CS40" s="95" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CT40" s="95" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="CU40" s="95" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="CV40" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CW40" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CX40" s="95" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="CY40" s="95" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="CZ40" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DA40" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="DB40" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="DC40" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="DD40" s="95" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="DE40" s="90" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="DF40" s="90" t="str">
+        <x:v>#B4ECFFFF</x:v>
+      </x:c>
+      <x:c r="DG40" s="90" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="DH40" s="90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DI40" s="88" t="str">
+        <x:v>アクティブ</x:v>
+      </x:c>
+      <x:c r="DJ40" s="88" t="str">
+        <x:v>使用者</x:v>
+      </x:c>
+      <x:c r="DK40" s="88" t="str">
+        <x:v>追従なし</x:v>
+      </x:c>
+      <x:c r="DL40" s="88" t="str">
+        <x:v>生成時</x:v>
+      </x:c>
+      <x:c r="DM40" s="88" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DN40" s="88" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="DO40" s="88" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DP40" s="88" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="DQ40" s="88" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DR40" s="88" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="DS40" s="88" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="25" customHeight="1">
-      <x:c r="A41" s="10"/>
-      <x:c r="D41" s="12"/>
-      <x:c r="E41" s="12"/>
-      <x:c r="F41" s="12"/>
-      <x:c r="G41" s="14"/>
-      <x:c r="H41" s="14"/>
-      <x:c r="I41" s="14"/>
-      <x:c r="J41" s="14"/>
-      <x:c r="N41" s="14"/>
-      <x:c r="O41" s="12"/>
-      <x:c r="S41" s="14"/>
-      <x:c r="T41" s="12"/>
-      <x:c r="V41" s="42" t="str">
+      <x:c r="A41" s="93" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B41" s="90" t="str">
+        <x:v>炎の陣</x:v>
+      </x:c>
+      <x:c r="C41" s="90" t="str">
+        <x:v>使用した地点に5秒残り、0.5秒ごとに半径3の敵へ火属性ダメージを与える。</x:v>
+      </x:c>
+      <x:c r="D41" s="94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E41" s="94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F41" s="94" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G41" s="95" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H41" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I41" s="95" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="J41" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K41" s="90" t="str">
+        <x:v>自身</x:v>
+      </x:c>
+      <x:c r="L41" s="90" t="str">
+        <x:v>ダメージ</x:v>
+      </x:c>
+      <x:c r="M41" s="90" t="str">
+        <x:v>魔法攻撃力</x:v>
+      </x:c>
+      <x:c r="N41" s="95" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O41" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P41" s="90" t="str">
+        <x:v>火</x:v>
+      </x:c>
+      <x:c r="Q41" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="R41" s="90" t="str">
+        <x:v>範囲内の敵</x:v>
+      </x:c>
+      <x:c r="S41" s="95" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T41" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U41" s="90" t="str">
+        <x:v>発射物</x:v>
+      </x:c>
+      <x:c r="V41" s="42" t="n">
         <x:f>IF($A41="","",IF(AND($U41="発射物",$DI41&lt;&gt;"パッシブ"),$BE41,0))</x:f>
-      </x:c>
-      <x:c r="W41" s="42" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W41" s="42" t="n">
         <x:f>IF($A41="","",IF(AND($U41="発射物",$DI41&lt;&gt;"パッシブ"),$BF41,0))</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X41" s="42" t="str">
         <x:f>IF($A41="","",IF(AND($U41="発射物",$DI41&lt;&gt;"パッシブ"),IF($BG41="有効","有効","無効"),"無効"))</x:f>
-      </x:c>
-      <x:c r="AD41" s="14"/>
-      <x:c r="AE41" s="14"/>
-      <x:c r="AF41" s="14"/>
-      <x:c r="AH41" s="14"/>
-      <x:c r="AJ41" s="14"/>
-      <x:c r="AN41" s="14"/>
-      <x:c r="AO41" s="14"/>
-      <x:c r="AP41" s="14"/>
-      <x:c r="AR41" s="14"/>
-      <x:c r="AT41" s="14"/>
-      <x:c r="AX41" s="14"/>
-      <x:c r="AY41" s="14"/>
-      <x:c r="AZ41" s="14"/>
-      <x:c r="BB41" s="14"/>
-      <x:c r="BD41" s="14"/>
-      <x:c r="BE41" s="14"/>
-      <x:c r="BF41" s="14"/>
-      <x:c r="BK41" s="14"/>
-      <x:c r="BM41" s="14"/>
-      <x:c r="BN41" s="14"/>
-      <x:c r="BP41" s="14"/>
-      <x:c r="BQ41" s="14"/>
-      <x:c r="BR41" s="14"/>
-      <x:c r="BT41" s="14"/>
-      <x:c r="BU41" s="14"/>
-      <x:c r="BV41" s="14"/>
-      <x:c r="BW41" s="14"/>
-      <x:c r="BX41" s="14"/>
-      <x:c r="BY41" s="14"/>
-      <x:c r="BZ41" s="14"/>
-      <x:c r="CA41" s="14"/>
-      <x:c r="CB41" s="14"/>
-      <x:c r="CC41" s="14"/>
-      <x:c r="CD41" s="14"/>
-      <x:c r="CE41" s="14"/>
-      <x:c r="CF41" s="14"/>
-      <x:c r="CJ41" s="14"/>
-      <x:c r="CK41" s="14"/>
-      <x:c r="CL41" s="14"/>
-      <x:c r="CM41" s="14"/>
-      <x:c r="CO41" s="14"/>
-      <x:c r="CQ41" s="14"/>
-      <x:c r="CS41" s="14"/>
-      <x:c r="CT41" s="14"/>
-      <x:c r="CU41" s="14"/>
-      <x:c r="CW41" s="14"/>
-      <x:c r="CX41" s="14"/>
-      <x:c r="CY41" s="14"/>
-      <x:c r="CZ41" s="14"/>
-      <x:c r="DC41" s="14"/>
-      <x:c r="DD41" s="14"/>
-      <x:c r="DI41" s="88"/>
-      <x:c r="DJ41" s="88"/>
-      <x:c r="DK41" s="88"/>
-      <x:c r="DL41" s="88"/>
-      <x:c r="DM41" s="88"/>
-      <x:c r="DN41" s="88"/>
-      <x:c r="DO41" s="88"/>
-      <x:c r="DP41" s="88"/>
-      <x:c r="DQ41" s="88"/>
-      <x:c r="DR41" s="88"/>
-      <x:c r="DS41" s="88"/>
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="Y41" s="90"/>
+      <x:c r="Z41" s="90"/>
+      <x:c r="AA41" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AB41" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AC41" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AD41" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE41" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF41" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG41" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AH41" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AI41" s="90" t="str">
+        <x:v>時間更新</x:v>
+      </x:c>
+      <x:c r="AJ41" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK41" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AL41" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AM41" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AN41" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO41" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP41" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ41" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AR41" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS41" s="90" t="str">
+        <x:v>時間更新</x:v>
+      </x:c>
+      <x:c r="AT41" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU41" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AV41" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AW41" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AX41" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY41" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ41" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA41" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="BB41" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC41" s="90" t="str">
+        <x:v>時間更新</x:v>
+      </x:c>
+      <x:c r="BD41" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE41" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF41" s="95" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BG41" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BH41" s="90"/>
+      <x:c r="BI41" s="90" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="BJ41" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BK41" s="95" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="BL41" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BM41" s="95" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="BN41" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BO41" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BP41" s="95" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BQ41" s="95" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="BR41" s="95" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BS41" s="90" t="str">
+        <x:v>その場</x:v>
+      </x:c>
+      <x:c r="BT41" s="95" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="BU41" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="BV41" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BW41" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="BX41" s="95" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BY41" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="BZ41" s="95" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="CA41" s="95" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="CB41" s="95" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="CC41" s="95" t="n">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="CD41" s="95" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="CE41" s="95" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CF41" s="95" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CG41" s="90" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="CH41" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CI41" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CJ41" s="95" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="CK41" s="95" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="CL41" s="95" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="CM41" s="95" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="CN41" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CO41" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CP41" s="90" t="str">
+        <x:v>追尾</x:v>
+      </x:c>
+      <x:c r="CQ41" s="95" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="CR41" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CS41" s="95" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CT41" s="95" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="CU41" s="95" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="CV41" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CW41" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CX41" s="95" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="CY41" s="95" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="CZ41" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DA41" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="DB41" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="DC41" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="DD41" s="95" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="DE41" s="90" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="DF41" s="90" t="str">
+        <x:v>#FFAA66FF</x:v>
+      </x:c>
+      <x:c r="DG41" s="90" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="DH41" s="90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DI41" s="88" t="str">
+        <x:v>アクティブ</x:v>
+      </x:c>
+      <x:c r="DJ41" s="88" t="str">
+        <x:v>使用者</x:v>
+      </x:c>
+      <x:c r="DK41" s="88" t="str">
+        <x:v>追従なし</x:v>
+      </x:c>
+      <x:c r="DL41" s="88" t="str">
+        <x:v>一定間隔</x:v>
+      </x:c>
+      <x:c r="DM41" s="88" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="DN41" s="88" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="DO41" s="88" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DP41" s="88" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="DQ41" s="88" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DR41" s="88" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="DS41" s="88" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="25" customHeight="1">
-      <x:c r="A42" s="10"/>
-      <x:c r="D42" s="12"/>
-      <x:c r="E42" s="12"/>
-      <x:c r="F42" s="12"/>
-      <x:c r="G42" s="14"/>
-      <x:c r="H42" s="14"/>
-      <x:c r="I42" s="14"/>
-      <x:c r="J42" s="14"/>
-      <x:c r="N42" s="14"/>
-      <x:c r="O42" s="12"/>
-      <x:c r="S42" s="14"/>
-      <x:c r="T42" s="12"/>
-      <x:c r="V42" s="42" t="str">
+      <x:c r="A42" s="93" t="str">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B42" s="90" t="str">
+        <x:v>癒しの陣</x:v>
+      </x:c>
+      <x:c r="C42" s="90" t="str">
+        <x:v>使用した地点に5秒残り、1秒ごとに半径3の味方を回復する。</x:v>
+      </x:c>
+      <x:c r="D42" s="94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E42" s="94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F42" s="94" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G42" s="95" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H42" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I42" s="95" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="J42" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K42" s="90" t="str">
+        <x:v>自身</x:v>
+      </x:c>
+      <x:c r="L42" s="90" t="str">
+        <x:v>回復</x:v>
+      </x:c>
+      <x:c r="M42" s="90" t="str">
+        <x:v>魔法攻撃力</x:v>
+      </x:c>
+      <x:c r="N42" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="O42" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P42" s="90" t="str">
+        <x:v>使用者と同じ</x:v>
+      </x:c>
+      <x:c r="Q42" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="R42" s="90" t="str">
+        <x:v>範囲内の味方</x:v>
+      </x:c>
+      <x:c r="S42" s="95" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T42" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U42" s="90" t="str">
+        <x:v>発射物</x:v>
+      </x:c>
+      <x:c r="V42" s="42" t="n">
         <x:f>IF($A42="","",IF(AND($U42="発射物",$DI42&lt;&gt;"パッシブ"),$BE42,0))</x:f>
-      </x:c>
-      <x:c r="W42" s="42" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W42" s="42" t="n">
         <x:f>IF($A42="","",IF(AND($U42="発射物",$DI42&lt;&gt;"パッシブ"),$BF42,0))</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X42" s="42" t="str">
         <x:f>IF($A42="","",IF(AND($U42="発射物",$DI42&lt;&gt;"パッシブ"),IF($BG42="有効","有効","無効"),"無効"))</x:f>
-      </x:c>
-      <x:c r="AD42" s="14"/>
-      <x:c r="AE42" s="14"/>
-      <x:c r="AF42" s="14"/>
-      <x:c r="AH42" s="14"/>
-      <x:c r="AJ42" s="14"/>
-      <x:c r="AN42" s="14"/>
-      <x:c r="AO42" s="14"/>
-      <x:c r="AP42" s="14"/>
-      <x:c r="AR42" s="14"/>
-      <x:c r="AT42" s="14"/>
-      <x:c r="AX42" s="14"/>
-      <x:c r="AY42" s="14"/>
-      <x:c r="AZ42" s="14"/>
-      <x:c r="BB42" s="14"/>
-      <x:c r="BD42" s="14"/>
-      <x:c r="BE42" s="14"/>
-      <x:c r="BF42" s="14"/>
-      <x:c r="BK42" s="14"/>
-      <x:c r="BM42" s="14"/>
-      <x:c r="BN42" s="14"/>
-      <x:c r="BP42" s="14"/>
-      <x:c r="BQ42" s="14"/>
-      <x:c r="BR42" s="14"/>
-      <x:c r="BT42" s="14"/>
-      <x:c r="BU42" s="14"/>
-      <x:c r="BV42" s="14"/>
-      <x:c r="BW42" s="14"/>
-      <x:c r="BX42" s="14"/>
-      <x:c r="BY42" s="14"/>
-      <x:c r="BZ42" s="14"/>
-      <x:c r="CA42" s="14"/>
-      <x:c r="CB42" s="14"/>
-      <x:c r="CC42" s="14"/>
-      <x:c r="CD42" s="14"/>
-      <x:c r="CE42" s="14"/>
-      <x:c r="CF42" s="14"/>
-      <x:c r="CJ42" s="14"/>
-      <x:c r="CK42" s="14"/>
-      <x:c r="CL42" s="14"/>
-      <x:c r="CM42" s="14"/>
-      <x:c r="CO42" s="14"/>
-      <x:c r="CQ42" s="14"/>
-      <x:c r="CS42" s="14"/>
-      <x:c r="CT42" s="14"/>
-      <x:c r="CU42" s="14"/>
-      <x:c r="CW42" s="14"/>
-      <x:c r="CX42" s="14"/>
-      <x:c r="CY42" s="14"/>
-      <x:c r="CZ42" s="14"/>
-      <x:c r="DC42" s="14"/>
-      <x:c r="DD42" s="14"/>
-      <x:c r="DI42" s="88"/>
-      <x:c r="DJ42" s="88"/>
-      <x:c r="DK42" s="88"/>
-      <x:c r="DL42" s="88"/>
-      <x:c r="DM42" s="88"/>
-      <x:c r="DN42" s="88"/>
-      <x:c r="DO42" s="88"/>
-      <x:c r="DP42" s="88"/>
-      <x:c r="DQ42" s="88"/>
-      <x:c r="DR42" s="88"/>
-      <x:c r="DS42" s="88"/>
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="Y42" s="90"/>
+      <x:c r="Z42" s="90"/>
+      <x:c r="AA42" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AB42" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AC42" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AD42" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE42" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF42" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG42" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AH42" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AI42" s="90" t="str">
+        <x:v>時間更新</x:v>
+      </x:c>
+      <x:c r="AJ42" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK42" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AL42" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AM42" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AN42" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO42" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP42" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ42" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AR42" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS42" s="90" t="str">
+        <x:v>時間更新</x:v>
+      </x:c>
+      <x:c r="AT42" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU42" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AV42" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AW42" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AX42" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY42" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ42" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA42" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="BB42" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC42" s="90" t="str">
+        <x:v>時間更新</x:v>
+      </x:c>
+      <x:c r="BD42" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE42" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF42" s="95" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BG42" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BH42" s="90"/>
+      <x:c r="BI42" s="90" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="BJ42" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BK42" s="95" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="BL42" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BM42" s="95" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="BN42" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BO42" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BP42" s="95" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BQ42" s="95" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="BR42" s="95" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BS42" s="90" t="str">
+        <x:v>その場</x:v>
+      </x:c>
+      <x:c r="BT42" s="95" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="BU42" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="BV42" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BW42" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="BX42" s="95" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BY42" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="BZ42" s="95" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="CA42" s="95" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="CB42" s="95" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="CC42" s="95" t="n">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="CD42" s="95" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="CE42" s="95" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CF42" s="95" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CG42" s="90" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="CH42" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CI42" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CJ42" s="95" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="CK42" s="95" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="CL42" s="95" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="CM42" s="95" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="CN42" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CO42" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CP42" s="90" t="str">
+        <x:v>追尾</x:v>
+      </x:c>
+      <x:c r="CQ42" s="95" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="CR42" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CS42" s="95" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CT42" s="95" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="CU42" s="95" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="CV42" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CW42" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CX42" s="95" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="CY42" s="95" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="CZ42" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DA42" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="DB42" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="DC42" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="DD42" s="95" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="DE42" s="90" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="DF42" s="90" t="str">
+        <x:v>#8AFFBFFF</x:v>
+      </x:c>
+      <x:c r="DG42" s="90" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="DH42" s="90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DI42" s="88" t="str">
+        <x:v>アクティブ</x:v>
+      </x:c>
+      <x:c r="DJ42" s="88" t="str">
+        <x:v>使用者</x:v>
+      </x:c>
+      <x:c r="DK42" s="88" t="str">
+        <x:v>追従なし</x:v>
+      </x:c>
+      <x:c r="DL42" s="88" t="str">
+        <x:v>一定間隔</x:v>
+      </x:c>
+      <x:c r="DM42" s="88" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DN42" s="88" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="DO42" s="88" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DP42" s="88" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="DQ42" s="88" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DR42" s="88" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="DS42" s="88" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="25" customHeight="1">
-      <x:c r="A43" s="10"/>
-      <x:c r="D43" s="12"/>
-      <x:c r="E43" s="12"/>
-      <x:c r="F43" s="12"/>
-      <x:c r="G43" s="14"/>
-      <x:c r="H43" s="14"/>
-      <x:c r="I43" s="14"/>
-      <x:c r="J43" s="14"/>
-      <x:c r="N43" s="14"/>
-      <x:c r="O43" s="12"/>
-      <x:c r="S43" s="14"/>
-      <x:c r="T43" s="12"/>
-      <x:c r="V43" s="42" t="str">
+      <x:c r="A43" s="93" t="str">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B43" s="90" t="str">
+        <x:v>守護の陣</x:v>
+      </x:c>
+      <x:c r="C43" s="90" t="str">
+        <x:v>使用した地点に5秒残り、1秒ごとに半径3の味方へ防御力＋30％を1.5秒付与する。</x:v>
+      </x:c>
+      <x:c r="D43" s="94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E43" s="94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F43" s="94" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G43" s="95" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H43" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I43" s="95" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="J43" s="95" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K43" s="90" t="str">
+        <x:v>自身</x:v>
+      </x:c>
+      <x:c r="L43" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="M43" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="N43" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O43" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P43" s="90" t="str">
+        <x:v>使用者と同じ</x:v>
+      </x:c>
+      <x:c r="Q43" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="R43" s="90" t="str">
+        <x:v>範囲内の味方</x:v>
+      </x:c>
+      <x:c r="S43" s="95" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T43" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U43" s="90" t="str">
+        <x:v>発射物</x:v>
+      </x:c>
+      <x:c r="V43" s="42" t="n">
         <x:f>IF($A43="","",IF(AND($U43="発射物",$DI43&lt;&gt;"パッシブ"),$BE43,0))</x:f>
-      </x:c>
-      <x:c r="W43" s="42" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W43" s="42" t="n">
         <x:f>IF($A43="","",IF(AND($U43="発射物",$DI43&lt;&gt;"パッシブ"),$BF43,0))</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X43" s="42" t="str">
         <x:f>IF($A43="","",IF(AND($U43="発射物",$DI43&lt;&gt;"パッシブ"),IF($BG43="有効","有効","無効"),"無効"))</x:f>
-      </x:c>
-      <x:c r="AD43" s="14"/>
-      <x:c r="AE43" s="14"/>
-      <x:c r="AF43" s="14"/>
-      <x:c r="AH43" s="14"/>
-      <x:c r="AJ43" s="14"/>
-      <x:c r="AN43" s="14"/>
-      <x:c r="AO43" s="14"/>
-      <x:c r="AP43" s="14"/>
-      <x:c r="AR43" s="14"/>
-      <x:c r="AT43" s="14"/>
-      <x:c r="AX43" s="14"/>
-      <x:c r="AY43" s="14"/>
-      <x:c r="AZ43" s="14"/>
-      <x:c r="BB43" s="14"/>
-      <x:c r="BD43" s="14"/>
-      <x:c r="BE43" s="14"/>
-      <x:c r="BF43" s="14"/>
-      <x:c r="BK43" s="14"/>
-      <x:c r="BM43" s="14"/>
-      <x:c r="BN43" s="14"/>
-      <x:c r="BP43" s="14"/>
-      <x:c r="BQ43" s="14"/>
-      <x:c r="BR43" s="14"/>
-      <x:c r="BT43" s="14"/>
-      <x:c r="BU43" s="14"/>
-      <x:c r="BV43" s="14"/>
-      <x:c r="BW43" s="14"/>
-      <x:c r="BX43" s="14"/>
-      <x:c r="BY43" s="14"/>
-      <x:c r="BZ43" s="14"/>
-      <x:c r="CA43" s="14"/>
-      <x:c r="CB43" s="14"/>
-      <x:c r="CC43" s="14"/>
-      <x:c r="CD43" s="14"/>
-      <x:c r="CE43" s="14"/>
-      <x:c r="CF43" s="14"/>
-      <x:c r="CJ43" s="14"/>
-      <x:c r="CK43" s="14"/>
-      <x:c r="CL43" s="14"/>
-      <x:c r="CM43" s="14"/>
-      <x:c r="CO43" s="14"/>
-      <x:c r="CQ43" s="14"/>
-      <x:c r="CS43" s="14"/>
-      <x:c r="CT43" s="14"/>
-      <x:c r="CU43" s="14"/>
-      <x:c r="CW43" s="14"/>
-      <x:c r="CX43" s="14"/>
-      <x:c r="CY43" s="14"/>
-      <x:c r="CZ43" s="14"/>
-      <x:c r="DC43" s="14"/>
-      <x:c r="DD43" s="14"/>
-      <x:c r="DI43" s="88"/>
-      <x:c r="DJ43" s="88"/>
-      <x:c r="DK43" s="88"/>
-      <x:c r="DL43" s="88"/>
-      <x:c r="DM43" s="88"/>
-      <x:c r="DN43" s="88"/>
-      <x:c r="DO43" s="88"/>
-      <x:c r="DP43" s="88"/>
-      <x:c r="DQ43" s="88"/>
-      <x:c r="DR43" s="88"/>
-      <x:c r="DS43" s="88"/>
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="Y43" s="90"/>
+      <x:c r="Z43" s="90"/>
+      <x:c r="AA43" s="90" t="str">
+        <x:v>バフ</x:v>
+      </x:c>
+      <x:c r="AB43" s="90" t="str">
+        <x:v>防御力</x:v>
+      </x:c>
+      <x:c r="AC43" s="90" t="str">
+        <x:v>割合変化</x:v>
+      </x:c>
+      <x:c r="AD43" s="95" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AE43" s="95" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="AF43" s="95" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="AG43" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AH43" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AI43" s="90" t="str">
+        <x:v>時間更新</x:v>
+      </x:c>
+      <x:c r="AJ43" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK43" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AL43" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AM43" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AN43" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AO43" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP43" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ43" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AR43" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS43" s="90" t="str">
+        <x:v>時間更新</x:v>
+      </x:c>
+      <x:c r="AT43" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU43" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AV43" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AW43" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="AX43" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AY43" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AZ43" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BA43" s="90" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="BB43" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BC43" s="90" t="str">
+        <x:v>時間更新</x:v>
+      </x:c>
+      <x:c r="BD43" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE43" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF43" s="95" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BG43" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BH43" s="90"/>
+      <x:c r="BI43" s="90" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="BJ43" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BK43" s="95" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="BL43" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BM43" s="95" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="BN43" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BO43" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="BP43" s="95" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BQ43" s="95" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="BR43" s="95" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BS43" s="90" t="str">
+        <x:v>その場</x:v>
+      </x:c>
+      <x:c r="BT43" s="95" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="BU43" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="BV43" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BW43" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="BX43" s="95" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BY43" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="BZ43" s="95" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="CA43" s="95" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="CB43" s="95" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="CC43" s="95" t="n">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="CD43" s="95" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="CE43" s="95" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CF43" s="95" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CG43" s="90" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="CH43" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CI43" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CJ43" s="95" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="CK43" s="95" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="CL43" s="95" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="CM43" s="95" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="CN43" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CO43" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CP43" s="90" t="str">
+        <x:v>追尾</x:v>
+      </x:c>
+      <x:c r="CQ43" s="95" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="CR43" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CS43" s="95" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CT43" s="95" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="CU43" s="95" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="CV43" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="CW43" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CX43" s="95" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="CY43" s="95" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="CZ43" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DA43" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="DB43" s="90" t="str">
+        <x:v>無効</x:v>
+      </x:c>
+      <x:c r="DC43" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="DD43" s="95" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="DE43" s="90" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="DF43" s="90" t="str">
+        <x:v>#BDA8FFFF</x:v>
+      </x:c>
+      <x:c r="DG43" s="90" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="DH43" s="90" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DI43" s="88" t="str">
+        <x:v>アクティブ</x:v>
+      </x:c>
+      <x:c r="DJ43" s="88" t="str">
+        <x:v>使用者</x:v>
+      </x:c>
+      <x:c r="DK43" s="88" t="str">
+        <x:v>追従なし</x:v>
+      </x:c>
+      <x:c r="DL43" s="88" t="str">
+        <x:v>一定間隔</x:v>
+      </x:c>
+      <x:c r="DM43" s="88" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DN43" s="88" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="DO43" s="88" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DP43" s="88" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="DQ43" s="88" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DR43" s="88" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="DS43" s="88" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="25" customHeight="1">
       <x:c r="A44" s="10"/>
@@ -23522,7 +24669,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R285f1149c16b48b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R353538fd27764554"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23638,7 +24785,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56965fdc623d47e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59ed44e7d5184992"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26782,6 +27929,174 @@
         <x:v>新しいパッシブを主人公で覚えるには人間一覧または転生種族へ追加</x:v>
       </x:c>
     </x:row>
+    <x:row r="259" ht="32" customHeight="1">
+      <x:c r="A259" s="92" t="str">
+        <x:v>陣・衝撃波の設定例</x:v>
+      </x:c>
+      <x:c r="B259" s="92" t="str">
+        <x:v>項目</x:v>
+      </x:c>
+      <x:c r="C259" s="92" t="str">
+        <x:v>設定・値</x:v>
+      </x:c>
+      <x:c r="D259" s="92" t="str">
+        <x:v>注意</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" ht="58" customHeight="1">
+      <x:c r="A260" s="89" t="str">
+        <x:v>共通</x:v>
+      </x:c>
+      <x:c r="B260" s="89" t="str">
+        <x:v>入力例の場所</x:v>
+      </x:c>
+      <x:c r="C260" s="89" t="str">
+        <x:v>スキルシート40～43行（ID39～42）</x:v>
+      </x:c>
+      <x:c r="D260" s="89" t="str">
+        <x:v>既存38スキルは維持。画像は各番号で配置</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" ht="58" customHeight="1">
+      <x:c r="A261" s="89" t="str">
+        <x:v>衝撃波</x:v>
+      </x:c>
+      <x:c r="B261" s="89" t="str">
+        <x:v>生成時に一度だけ攻撃</x:v>
+      </x:c>
+      <x:c r="C261" s="89" t="str">
+        <x:v>対象＝自身、適用先＝範囲内の敵、移動＝その場</x:v>
+      </x:c>
+      <x:c r="D261" s="89" t="str">
+        <x:v>生成位置＝使用者、追従なし、寿命0.35秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" ht="58" customHeight="1">
+      <x:c r="A262" s="89" t="str">
+        <x:v>炎の陣</x:v>
+      </x:c>
+      <x:c r="B262" s="89" t="str">
+        <x:v>一定間隔で攻撃</x:v>
+      </x:c>
+      <x:c r="C262" s="89" t="str">
+        <x:v>効果発生タイミング＝一定間隔、効果間隔秒＝0.5</x:v>
+      </x:c>
+      <x:c r="D262" s="89" t="str">
+        <x:v>寿命5秒、火属性、使用地点に残る</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" ht="58" customHeight="1">
+      <x:c r="A263" s="89" t="str">
+        <x:v>癒しの陣</x:v>
+      </x:c>
+      <x:c r="B263" s="89" t="str">
+        <x:v>一定間隔で回復</x:v>
+      </x:c>
+      <x:c r="C263" s="89" t="str">
+        <x:v>適用先＝範囲内の味方、効果間隔秒＝1</x:v>
+      </x:c>
+      <x:c r="D263" s="89" t="str">
+        <x:v>寿命5秒、使用者も範囲内なら回復</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" ht="58" customHeight="1">
+      <x:c r="A264" s="89" t="str">
+        <x:v>守護の陣</x:v>
+      </x:c>
+      <x:c r="B264" s="89" t="str">
+        <x:v>一定間隔で防御バフ</x:v>
+      </x:c>
+      <x:c r="C264" s="89" t="str">
+        <x:v>追加効果1＝バフ／防御力／割合変化／30</x:v>
+      </x:c>
+      <x:c r="D264" s="89" t="str">
+        <x:v>効果持続1.5秒、1秒ごとに時間更新。退出後は期限で解除</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" ht="58" customHeight="1">
+      <x:c r="A265" s="89" t="str">
+        <x:v>範囲</x:v>
+      </x:c>
+      <x:c r="B265" s="89" t="str">
+        <x:v>命中上限＝0</x:v>
+      </x:c>
+      <x:c r="C265" s="89" t="str">
+        <x:v>半径3以内の全員へ効果</x:v>
+      </x:c>
+      <x:c r="D265" s="89" t="str">
+        <x:v>命中半径と範囲半径は別。定期効果は範囲半径を使う</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" ht="58" customHeight="1">
+      <x:c r="A266" s="89" t="str">
+        <x:v>表示</x:v>
+      </x:c>
+      <x:c r="B266" s="89" t="str">
+        <x:v>表示倍率＝3は仮値</x:v>
+      </x:c>
+      <x:c r="C266" s="89" t="str">
+        <x:v>スプライトのサイズ・PPUに合わせて調整</x:v>
+      </x:c>
+      <x:c r="D266" s="89" t="str">
+        <x:v>見た目の倍率を変えても効果範囲は変わらない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" ht="58" customHeight="1">
+      <x:c r="A267" s="89" t="str">
+        <x:v>追従</x:v>
+      </x:c>
+      <x:c r="B267" s="89" t="str">
+        <x:v>使用者についてくる陣</x:v>
+      </x:c>
+      <x:c r="C267" s="89" t="str">
+        <x:v>追従先を「使用者」に変更</x:v>
+      </x:c>
+      <x:c r="D267" s="89" t="str">
+        <x:v>その場＋追従なしなら使用地点に残る</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" ht="58" customHeight="1">
+      <x:c r="A268" s="89" t="str">
+        <x:v>対象位置</x:v>
+      </x:c>
+      <x:c r="B268" s="89" t="str">
+        <x:v>対象の足元に生成する陣</x:v>
+      </x:c>
+      <x:c r="C268" s="89" t="str">
+        <x:v>対象＝敵一体／味方一体、生成位置＝対象</x:v>
+      </x:c>
+      <x:c r="D268" s="89" t="str">
+        <x:v>追従なしなら初期地点に残る。対象追従なら移動に追従</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" ht="58" customHeight="1">
+      <x:c r="A269" s="89" t="str">
+        <x:v>初回効果</x:v>
+      </x:c>
+      <x:c r="B269" s="89" t="str">
+        <x:v>一定間隔の最初の効果</x:v>
+      </x:c>
+      <x:c r="C269" s="89" t="str">
+        <x:v>指定した秒数を待ってから発生</x:v>
+      </x:c>
+      <x:c r="D269" s="89" t="str">
+        <x:v>生成時の即時効果とは異なる</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" ht="58" customHeight="1">
+      <x:c r="A270" s="89" t="str">
+        <x:v>生成・取り込み</x:v>
+      </x:c>
+      <x:c r="B270" s="89" t="str">
+        <x:v>番号画像を配置後、Excelを取り込む</x:v>
+      </x:c>
+      <x:c r="C270" s="89" t="str">
+        <x:v>素材/Projectile/39.png～42.png（Sprite）</x:v>
+      </x:c>
+      <x:c r="D270" s="89" t="str">
+        <x:v>素材/Profectileでも可。画像不足時は取り込みが止まる</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Docs/SkillTemplates/スキル定義テンプレート.xlsx
+++ b/Docs/SkillTemplates/スキル定義テンプレート.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル" sheetId="1" r:id="R8872928e537f4ebf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="モンスター列追加例" sheetId="2" r:id="R991bb1496a2f4cac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="3" r:id="R9d6a79c2007b48b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル" sheetId="1" r:id="Raee5c59f0e494a22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="モンスター列追加例" sheetId="2" r:id="Rf54cb92c3ffe4a1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="3" r:id="Rf2b980a9d8f34ac1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,7 +91,7 @@
       <x:name val="Noto Sans JP"/>
     </x:font>
   </x:fonts>
-  <x:fills count="19">
+  <x:fills count="21">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -183,6 +183,16 @@
         <x:fgColor rgb="FF214E66"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF214E66"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3D5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border>
@@ -196,7 +206,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="96">
+  <x:cellXfs count="102">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -421,6 +431,16 @@
     <x:xf numFmtId="200" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -881,6 +901,7 @@
     <x:col min="121" max="121" width="22" hidden="0" customWidth="1"/>
     <x:col min="122" max="122" width="22" hidden="0" customWidth="1"/>
     <x:col min="123" max="123" width="22" hidden="0" customWidth="1"/>
+    <x:col min="124" max="124" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
@@ -1252,6 +1273,9 @@
       </x:c>
       <x:c r="DS1" s="87" t="str">
         <x:v>パッシブ3_効果量</x:v>
+      </x:c>
+      <x:c r="DT1" s="98" t="str">
+        <x:v>発射物_画像番号</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="25" customHeight="1">
@@ -1609,6 +1633,9 @@
       <x:c r="DQ2" s="88"/>
       <x:c r="DR2" s="88"/>
       <x:c r="DS2" s="88"/>
+      <x:c r="DT2" s="100" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="9" t="str">
@@ -1965,6 +1992,9 @@
       <x:c r="DQ3" s="88"/>
       <x:c r="DR3" s="88"/>
       <x:c r="DS3" s="88"/>
+      <x:c r="DT3" s="100" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
       <x:c r="A4" s="9" t="str">
@@ -2028,15 +2058,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U4" s="7" t="str">
-        <x:v>即時</x:v>
+        <x:v>発射物</x:v>
       </x:c>
       <x:c r="V4" s="41" t="n">
         <x:f>IF($A4="","",IF(AND($U4="発射物",$DI4&lt;&gt;"パッシブ"),$BE4,0))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="W4" s="41" t="n">
         <x:f>IF($A4="","",IF(AND($U4="発射物",$DI4&lt;&gt;"パッシブ"),$BF4,0))</x:f>
-        <x:v>0</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="X4" s="41" t="str">
         <x:f>IF($A4="","",IF(AND($U4="発射物",$DI4&lt;&gt;"パッシブ"),IF($BG4="有効","有効","無効"),"無効"))</x:f>
@@ -2135,17 +2165,17 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="BE4" s="43" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF4" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="BG4" s="44" t="str">
-        <x:v>有効</x:v>
+        <x:v>無効</x:v>
       </x:c>
       <x:c r="BH4" s="45"/>
       <x:c r="BI4" s="45" t="str">
-        <x:v>無効</x:v>
+        <x:v>有効</x:v>
       </x:c>
       <x:c r="BJ4" s="45" t="str">
         <x:v>無効</x:v>
@@ -2175,7 +2205,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="BS4" s="45" t="str">
-        <x:v>直進</x:v>
+        <x:v>その場</x:v>
       </x:c>
       <x:c r="BT4" s="51" t="n">
         <x:v>8</x:v>
@@ -2280,7 +2310,7 @@
         <x:v>無効</x:v>
       </x:c>
       <x:c r="DB4" s="45" t="str">
-        <x:v>有効</x:v>
+        <x:v>無効</x:v>
       </x:c>
       <x:c r="DC4" s="51" t="n">
         <x:v>2</x:v>
@@ -2310,7 +2340,7 @@
         <x:v>追従なし</x:v>
       </x:c>
       <x:c r="DL4" s="88" t="str">
-        <x:v>命中時</x:v>
+        <x:v>生成時</x:v>
       </x:c>
       <x:c r="DM4" s="88" t="n">
         <x:v>1</x:v>
@@ -2321,6 +2351,9 @@
       <x:c r="DQ4" s="88"/>
       <x:c r="DR4" s="88"/>
       <x:c r="DS4" s="88"/>
+      <x:c r="DT4" s="100" t="n">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
       <x:c r="A5" s="9" t="str">
@@ -2677,6 +2710,9 @@
       <x:c r="DQ5" s="88"/>
       <x:c r="DR5" s="88"/>
       <x:c r="DS5" s="88"/>
+      <x:c r="DT5" s="100" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
       <x:c r="A6" s="9" t="str">
@@ -3033,6 +3069,9 @@
       <x:c r="DQ6" s="88"/>
       <x:c r="DR6" s="88"/>
       <x:c r="DS6" s="88"/>
+      <x:c r="DT6" s="100" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
       <x:c r="A7" s="9" t="str">
@@ -3389,6 +3428,9 @@
       <x:c r="DQ7" s="88"/>
       <x:c r="DR7" s="88"/>
       <x:c r="DS7" s="88"/>
+      <x:c r="DT7" s="100" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
       <x:c r="A8" s="9" t="str">
@@ -3452,15 +3494,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="U8" s="7" t="str">
-        <x:v>即時</x:v>
+        <x:v>発射物</x:v>
       </x:c>
       <x:c r="V8" s="41" t="n">
         <x:f>IF($A8="","",IF(AND($U8="発射物",$DI8&lt;&gt;"パッシブ"),$BE8,0))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="W8" s="41" t="n">
         <x:f>IF($A8="","",IF(AND($U8="発射物",$DI8&lt;&gt;"パッシブ"),$BF8,0))</x:f>
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X8" s="41" t="str">
         <x:f>IF($A8="","",IF(AND($U8="発射物",$DI8&lt;&gt;"パッシブ"),IF($BG8="有効","有効","無効"),"無効"))</x:f>
@@ -3559,17 +3601,17 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="BE8" s="43" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF8" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BG8" s="44" t="str">
-        <x:v>有効</x:v>
+        <x:v>無効</x:v>
       </x:c>
       <x:c r="BH8" s="45"/>
       <x:c r="BI8" s="45" t="str">
-        <x:v>無効</x:v>
+        <x:v>有効</x:v>
       </x:c>
       <x:c r="BJ8" s="45" t="str">
         <x:v>無効</x:v>
@@ -3599,7 +3641,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="BS8" s="45" t="str">
-        <x:v>直進</x:v>
+        <x:v>その場</x:v>
       </x:c>
       <x:c r="BT8" s="51" t="n">
         <x:v>8</x:v>
@@ -3704,7 +3746,7 @@
         <x:v>無効</x:v>
       </x:c>
       <x:c r="DB8" s="45" t="str">
-        <x:v>有効</x:v>
+        <x:v>無効</x:v>
       </x:c>
       <x:c r="DC8" s="51" t="n">
         <x:v>2</x:v>
@@ -3734,7 +3776,7 @@
         <x:v>追従なし</x:v>
       </x:c>
       <x:c r="DL8" s="88" t="str">
-        <x:v>命中時</x:v>
+        <x:v>一定間隔</x:v>
       </x:c>
       <x:c r="DM8" s="88" t="n">
         <x:v>1</x:v>
@@ -3745,6 +3787,9 @@
       <x:c r="DQ8" s="88"/>
       <x:c r="DR8" s="88"/>
       <x:c r="DS8" s="88"/>
+      <x:c r="DT8" s="100" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="25" customHeight="1">
       <x:c r="A9" s="9" t="str">
@@ -4101,6 +4146,9 @@
       <x:c r="DQ9" s="88"/>
       <x:c r="DR9" s="88"/>
       <x:c r="DS9" s="88"/>
+      <x:c r="DT9" s="100" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="25" customHeight="1">
       <x:c r="A10" s="9" t="str">
@@ -4457,6 +4505,9 @@
       <x:c r="DQ10" s="88"/>
       <x:c r="DR10" s="88"/>
       <x:c r="DS10" s="88"/>
+      <x:c r="DT10" s="100" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="25" customHeight="1">
       <x:c r="A11" s="9" t="str">
@@ -4813,6 +4864,9 @@
       <x:c r="DQ11" s="88"/>
       <x:c r="DR11" s="88"/>
       <x:c r="DS11" s="88"/>
+      <x:c r="DT11" s="100" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="25" customHeight="1">
       <x:c r="A12" s="9" t="str">
@@ -4876,15 +4930,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U12" s="7" t="str">
-        <x:v>即時</x:v>
+        <x:v>発射物</x:v>
       </x:c>
       <x:c r="V12" s="41" t="n">
         <x:f>IF($A12="","",IF(AND($U12="発射物",$DI12&lt;&gt;"パッシブ"),$BE12,0))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="W12" s="41" t="n">
         <x:f>IF($A12="","",IF(AND($U12="発射物",$DI12&lt;&gt;"パッシブ"),$BF12,0))</x:f>
-        <x:v>0</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="X12" s="41" t="str">
         <x:f>IF($A12="","",IF(AND($U12="発射物",$DI12&lt;&gt;"パッシブ"),IF($BG12="有効","有効","無効"),"無効"))</x:f>
@@ -4983,17 +5037,17 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="BE12" s="43" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF12" s="43" t="n">
-        <x:v>3</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="BG12" s="44" t="str">
-        <x:v>有効</x:v>
+        <x:v>無効</x:v>
       </x:c>
       <x:c r="BH12" s="45"/>
       <x:c r="BI12" s="45" t="str">
-        <x:v>無効</x:v>
+        <x:v>有効</x:v>
       </x:c>
       <x:c r="BJ12" s="45" t="str">
         <x:v>無効</x:v>
@@ -5023,7 +5077,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="BS12" s="45" t="str">
-        <x:v>直進</x:v>
+        <x:v>その場</x:v>
       </x:c>
       <x:c r="BT12" s="51" t="n">
         <x:v>8</x:v>
@@ -5128,7 +5182,7 @@
         <x:v>無効</x:v>
       </x:c>
       <x:c r="DB12" s="45" t="str">
-        <x:v>有効</x:v>
+        <x:v>無効</x:v>
       </x:c>
       <x:c r="DC12" s="51" t="n">
         <x:v>2</x:v>
@@ -5152,13 +5206,13 @@
         <x:v>アクティブ</x:v>
       </x:c>
       <x:c r="DJ12" s="88" t="str">
-        <x:v>使用者</x:v>
+        <x:v>対象</x:v>
       </x:c>
       <x:c r="DK12" s="88" t="str">
-        <x:v>追従なし</x:v>
+        <x:v>対象</x:v>
       </x:c>
       <x:c r="DL12" s="88" t="str">
-        <x:v>命中時</x:v>
+        <x:v>生成時</x:v>
       </x:c>
       <x:c r="DM12" s="88" t="n">
         <x:v>1</x:v>
@@ -5169,6 +5223,9 @@
       <x:c r="DQ12" s="88"/>
       <x:c r="DR12" s="88"/>
       <x:c r="DS12" s="88"/>
+      <x:c r="DT12" s="100" t="n">
+        <x:v>11</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="25" customHeight="1">
       <x:c r="A13" s="9" t="str">
@@ -5525,6 +5582,9 @@
       <x:c r="DQ13" s="88"/>
       <x:c r="DR13" s="88"/>
       <x:c r="DS13" s="88"/>
+      <x:c r="DT13" s="100" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="25" customHeight="1">
       <x:c r="A14" s="10" t="str">
@@ -5686,6 +5746,7 @@
       <x:c r="DS14" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT14" s="100"/>
     </x:row>
     <x:row r="15" ht="25" customHeight="1">
       <x:c r="A15" s="10" t="str">
@@ -5847,6 +5908,7 @@
       <x:c r="DS15" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT15" s="100"/>
     </x:row>
     <x:row r="16" ht="25" customHeight="1">
       <x:c r="A16" s="10" t="str">
@@ -6008,6 +6070,7 @@
       <x:c r="DS16" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT16" s="100"/>
     </x:row>
     <x:row r="17" ht="25" customHeight="1">
       <x:c r="A17" s="10" t="str">
@@ -6169,6 +6232,7 @@
       <x:c r="DS17" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT17" s="100"/>
     </x:row>
     <x:row r="18" ht="25" customHeight="1">
       <x:c r="A18" s="10" t="str">
@@ -6330,6 +6394,7 @@
       <x:c r="DS18" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT18" s="100"/>
     </x:row>
     <x:row r="19" ht="25" customHeight="1">
       <x:c r="A19" s="10" t="str">
@@ -6491,6 +6556,7 @@
       <x:c r="DS19" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT19" s="100"/>
     </x:row>
     <x:row r="20" ht="25" customHeight="1">
       <x:c r="A20" s="10" t="str">
@@ -6652,6 +6718,7 @@
       <x:c r="DS20" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT20" s="100"/>
     </x:row>
     <x:row r="21" ht="25" customHeight="1">
       <x:c r="A21" s="10" t="str">
@@ -6813,6 +6880,7 @@
       <x:c r="DS21" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT21" s="100"/>
     </x:row>
     <x:row r="22" ht="25" customHeight="1">
       <x:c r="A22" s="10" t="str">
@@ -6974,6 +7042,7 @@
       <x:c r="DS22" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT22" s="100"/>
     </x:row>
     <x:row r="23" ht="25" customHeight="1">
       <x:c r="A23" s="10" t="str">
@@ -7135,6 +7204,7 @@
       <x:c r="DS23" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT23" s="100"/>
     </x:row>
     <x:row r="24" ht="25" customHeight="1">
       <x:c r="A24" s="10" t="str">
@@ -7296,6 +7366,7 @@
       <x:c r="DS24" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT24" s="100"/>
     </x:row>
     <x:row r="25" ht="25" customHeight="1">
       <x:c r="A25" s="10" t="str">
@@ -7457,6 +7528,7 @@
       <x:c r="DS25" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT25" s="100"/>
     </x:row>
     <x:row r="26" ht="25" customHeight="1">
       <x:c r="A26" s="10" t="str">
@@ -7618,6 +7690,7 @@
       <x:c r="DS26" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT26" s="100"/>
     </x:row>
     <x:row r="27" ht="25" customHeight="1">
       <x:c r="A27" s="10" t="str">
@@ -7779,6 +7852,7 @@
       <x:c r="DS27" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT27" s="100"/>
     </x:row>
     <x:row r="28" ht="25" customHeight="1">
       <x:c r="A28" s="10" t="str">
@@ -7940,6 +8014,7 @@
       <x:c r="DS28" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT28" s="100"/>
     </x:row>
     <x:row r="29" ht="25" customHeight="1">
       <x:c r="A29" s="10" t="str">
@@ -8101,6 +8176,7 @@
       <x:c r="DS29" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT29" s="100"/>
     </x:row>
     <x:row r="30" ht="25" customHeight="1">
       <x:c r="A30" s="10" t="str">
@@ -8262,6 +8338,7 @@
       <x:c r="DS30" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT30" s="100"/>
     </x:row>
     <x:row r="31" ht="25" customHeight="1">
       <x:c r="A31" s="10" t="str">
@@ -8423,6 +8500,7 @@
       <x:c r="DS31" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT31" s="100"/>
     </x:row>
     <x:row r="32" ht="25" customHeight="1">
       <x:c r="A32" s="10" t="str">
@@ -8584,6 +8662,7 @@
       <x:c r="DS32" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT32" s="100"/>
     </x:row>
     <x:row r="33" ht="25" customHeight="1">
       <x:c r="A33" s="10" t="str">
@@ -8745,6 +8824,7 @@
       <x:c r="DS33" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT33" s="100"/>
     </x:row>
     <x:row r="34" ht="25" customHeight="1">
       <x:c r="A34" s="10" t="str">
@@ -8906,6 +8986,7 @@
       <x:c r="DS34" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT34" s="100"/>
     </x:row>
     <x:row r="35" ht="25" customHeight="1">
       <x:c r="A35" s="10" t="str">
@@ -9067,6 +9148,7 @@
       <x:c r="DS35" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT35" s="100"/>
     </x:row>
     <x:row r="36" ht="25" customHeight="1">
       <x:c r="A36" s="10" t="str">
@@ -9228,6 +9310,7 @@
       <x:c r="DS36" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT36" s="100"/>
     </x:row>
     <x:row r="37" ht="25" customHeight="1">
       <x:c r="A37" s="10" t="str">
@@ -9389,6 +9472,7 @@
       <x:c r="DS37" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT37" s="100"/>
     </x:row>
     <x:row r="38" ht="25" customHeight="1">
       <x:c r="A38" s="10" t="str">
@@ -9550,6 +9634,7 @@
       <x:c r="DS38" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT38" s="100"/>
     </x:row>
     <x:row r="39" ht="25" customHeight="1">
       <x:c r="A39" s="10" t="str">
@@ -9711,6 +9796,7 @@
       <x:c r="DS39" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT39" s="100"/>
     </x:row>
     <x:row r="40" ht="25" customHeight="1">
       <x:c r="A40" s="93" t="str">
@@ -10079,6 +10165,9 @@
       <x:c r="DS40" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT40" s="100" t="n">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="25" customHeight="1">
       <x:c r="A41" s="93" t="str">
@@ -10447,6 +10536,9 @@
       <x:c r="DS41" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="DT41" s="100" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="25" customHeight="1">
       <x:c r="A42" s="93" t="str">
@@ -10814,6 +10906,9 @@
       </x:c>
       <x:c r="DS42" s="88" t="n">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="DT42" s="100" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="25" customHeight="1">
@@ -11182,6 +11277,9 @@
       </x:c>
       <x:c r="DS43" s="88" t="n">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="DT43" s="100" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="25" customHeight="1">
@@ -11268,6 +11366,7 @@
       <x:c r="DQ44" s="88"/>
       <x:c r="DR44" s="88"/>
       <x:c r="DS44" s="88"/>
+      <x:c r="DT44" s="100"/>
     </x:row>
     <x:row r="45" ht="25" customHeight="1">
       <x:c r="A45" s="10"/>
@@ -11353,6 +11452,7 @@
       <x:c r="DQ45" s="88"/>
       <x:c r="DR45" s="88"/>
       <x:c r="DS45" s="88"/>
+      <x:c r="DT45" s="100"/>
     </x:row>
     <x:row r="46" ht="25" customHeight="1">
       <x:c r="A46" s="10"/>
@@ -11438,6 +11538,7 @@
       <x:c r="DQ46" s="88"/>
       <x:c r="DR46" s="88"/>
       <x:c r="DS46" s="88"/>
+      <x:c r="DT46" s="100"/>
     </x:row>
     <x:row r="47" ht="25" customHeight="1">
       <x:c r="A47" s="10"/>
@@ -11523,6 +11624,7 @@
       <x:c r="DQ47" s="88"/>
       <x:c r="DR47" s="88"/>
       <x:c r="DS47" s="88"/>
+      <x:c r="DT47" s="100"/>
     </x:row>
     <x:row r="48" ht="25" customHeight="1">
       <x:c r="A48" s="10"/>
@@ -11608,6 +11710,7 @@
       <x:c r="DQ48" s="88"/>
       <x:c r="DR48" s="88"/>
       <x:c r="DS48" s="88"/>
+      <x:c r="DT48" s="100"/>
     </x:row>
     <x:row r="49" ht="25" customHeight="1">
       <x:c r="A49" s="10"/>
@@ -11693,6 +11796,7 @@
       <x:c r="DQ49" s="88"/>
       <x:c r="DR49" s="88"/>
       <x:c r="DS49" s="88"/>
+      <x:c r="DT49" s="100"/>
     </x:row>
     <x:row r="50" ht="25" customHeight="1">
       <x:c r="A50" s="10"/>
@@ -11778,6 +11882,7 @@
       <x:c r="DQ50" s="88"/>
       <x:c r="DR50" s="88"/>
       <x:c r="DS50" s="88"/>
+      <x:c r="DT50" s="100"/>
     </x:row>
     <x:row r="51" ht="25" customHeight="1">
       <x:c r="A51" s="10"/>
@@ -11863,6 +11968,7 @@
       <x:c r="DQ51" s="88"/>
       <x:c r="DR51" s="88"/>
       <x:c r="DS51" s="88"/>
+      <x:c r="DT51" s="100"/>
     </x:row>
     <x:row r="52" ht="25" customHeight="1">
       <x:c r="A52" s="10"/>
@@ -11948,6 +12054,7 @@
       <x:c r="DQ52" s="88"/>
       <x:c r="DR52" s="88"/>
       <x:c r="DS52" s="88"/>
+      <x:c r="DT52" s="100"/>
     </x:row>
     <x:row r="53" ht="25" customHeight="1">
       <x:c r="A53" s="10"/>
@@ -12033,6 +12140,7 @@
       <x:c r="DQ53" s="88"/>
       <x:c r="DR53" s="88"/>
       <x:c r="DS53" s="88"/>
+      <x:c r="DT53" s="100"/>
     </x:row>
     <x:row r="54" ht="25" customHeight="1">
       <x:c r="A54" s="10"/>
@@ -12118,6 +12226,7 @@
       <x:c r="DQ54" s="88"/>
       <x:c r="DR54" s="88"/>
       <x:c r="DS54" s="88"/>
+      <x:c r="DT54" s="100"/>
     </x:row>
     <x:row r="55" ht="25" customHeight="1">
       <x:c r="A55" s="10"/>
@@ -12203,6 +12312,7 @@
       <x:c r="DQ55" s="88"/>
       <x:c r="DR55" s="88"/>
       <x:c r="DS55" s="88"/>
+      <x:c r="DT55" s="100"/>
     </x:row>
     <x:row r="56" ht="25" customHeight="1">
       <x:c r="A56" s="10"/>
@@ -12288,6 +12398,7 @@
       <x:c r="DQ56" s="88"/>
       <x:c r="DR56" s="88"/>
       <x:c r="DS56" s="88"/>
+      <x:c r="DT56" s="100"/>
     </x:row>
     <x:row r="57" ht="25" customHeight="1">
       <x:c r="A57" s="10"/>
@@ -12373,6 +12484,7 @@
       <x:c r="DQ57" s="88"/>
       <x:c r="DR57" s="88"/>
       <x:c r="DS57" s="88"/>
+      <x:c r="DT57" s="100"/>
     </x:row>
     <x:row r="58" ht="25" customHeight="1">
       <x:c r="A58" s="10"/>
@@ -12458,6 +12570,7 @@
       <x:c r="DQ58" s="88"/>
       <x:c r="DR58" s="88"/>
       <x:c r="DS58" s="88"/>
+      <x:c r="DT58" s="100"/>
     </x:row>
     <x:row r="59" ht="25" customHeight="1">
       <x:c r="A59" s="10"/>
@@ -12543,6 +12656,7 @@
       <x:c r="DQ59" s="88"/>
       <x:c r="DR59" s="88"/>
       <x:c r="DS59" s="88"/>
+      <x:c r="DT59" s="100"/>
     </x:row>
     <x:row r="60" ht="25" customHeight="1">
       <x:c r="A60" s="10"/>
@@ -12628,6 +12742,7 @@
       <x:c r="DQ60" s="88"/>
       <x:c r="DR60" s="88"/>
       <x:c r="DS60" s="88"/>
+      <x:c r="DT60" s="100"/>
     </x:row>
     <x:row r="61" ht="25" customHeight="1">
       <x:c r="A61" s="10"/>
@@ -12713,6 +12828,7 @@
       <x:c r="DQ61" s="88"/>
       <x:c r="DR61" s="88"/>
       <x:c r="DS61" s="88"/>
+      <x:c r="DT61" s="100"/>
     </x:row>
     <x:row r="62" ht="25" customHeight="1">
       <x:c r="A62" s="10"/>
@@ -12798,6 +12914,7 @@
       <x:c r="DQ62" s="88"/>
       <x:c r="DR62" s="88"/>
       <x:c r="DS62" s="88"/>
+      <x:c r="DT62" s="100"/>
     </x:row>
     <x:row r="63" ht="25" customHeight="1">
       <x:c r="A63" s="10"/>
@@ -12883,6 +13000,7 @@
       <x:c r="DQ63" s="88"/>
       <x:c r="DR63" s="88"/>
       <x:c r="DS63" s="88"/>
+      <x:c r="DT63" s="100"/>
     </x:row>
     <x:row r="64" ht="25" customHeight="1">
       <x:c r="A64" s="10"/>
@@ -12968,6 +13086,7 @@
       <x:c r="DQ64" s="88"/>
       <x:c r="DR64" s="88"/>
       <x:c r="DS64" s="88"/>
+      <x:c r="DT64" s="100"/>
     </x:row>
     <x:row r="65" ht="25" customHeight="1">
       <x:c r="A65" s="10"/>
@@ -13053,6 +13172,7 @@
       <x:c r="DQ65" s="88"/>
       <x:c r="DR65" s="88"/>
       <x:c r="DS65" s="88"/>
+      <x:c r="DT65" s="100"/>
     </x:row>
     <x:row r="66" ht="25" customHeight="1">
       <x:c r="A66" s="10"/>
@@ -13138,6 +13258,7 @@
       <x:c r="DQ66" s="88"/>
       <x:c r="DR66" s="88"/>
       <x:c r="DS66" s="88"/>
+      <x:c r="DT66" s="100"/>
     </x:row>
     <x:row r="67" ht="25" customHeight="1">
       <x:c r="A67" s="10"/>
@@ -13223,6 +13344,7 @@
       <x:c r="DQ67" s="88"/>
       <x:c r="DR67" s="88"/>
       <x:c r="DS67" s="88"/>
+      <x:c r="DT67" s="100"/>
     </x:row>
     <x:row r="68" ht="25" customHeight="1">
       <x:c r="A68" s="10"/>
@@ -13308,6 +13430,7 @@
       <x:c r="DQ68" s="88"/>
       <x:c r="DR68" s="88"/>
       <x:c r="DS68" s="88"/>
+      <x:c r="DT68" s="100"/>
     </x:row>
     <x:row r="69" ht="25" customHeight="1">
       <x:c r="A69" s="10"/>
@@ -13393,6 +13516,7 @@
       <x:c r="DQ69" s="88"/>
       <x:c r="DR69" s="88"/>
       <x:c r="DS69" s="88"/>
+      <x:c r="DT69" s="100"/>
     </x:row>
     <x:row r="70" ht="25" customHeight="1">
       <x:c r="A70" s="10"/>
@@ -13478,6 +13602,7 @@
       <x:c r="DQ70" s="88"/>
       <x:c r="DR70" s="88"/>
       <x:c r="DS70" s="88"/>
+      <x:c r="DT70" s="100"/>
     </x:row>
     <x:row r="71" ht="25" customHeight="1">
       <x:c r="A71" s="10"/>
@@ -13563,6 +13688,7 @@
       <x:c r="DQ71" s="88"/>
       <x:c r="DR71" s="88"/>
       <x:c r="DS71" s="88"/>
+      <x:c r="DT71" s="100"/>
     </x:row>
     <x:row r="72" ht="25" customHeight="1">
       <x:c r="A72" s="10"/>
@@ -13648,6 +13774,7 @@
       <x:c r="DQ72" s="88"/>
       <x:c r="DR72" s="88"/>
       <x:c r="DS72" s="88"/>
+      <x:c r="DT72" s="100"/>
     </x:row>
     <x:row r="73" ht="25" customHeight="1">
       <x:c r="A73" s="10"/>
@@ -13733,6 +13860,7 @@
       <x:c r="DQ73" s="88"/>
       <x:c r="DR73" s="88"/>
       <x:c r="DS73" s="88"/>
+      <x:c r="DT73" s="100"/>
     </x:row>
     <x:row r="74" ht="25" customHeight="1">
       <x:c r="A74" s="10"/>
@@ -13818,6 +13946,7 @@
       <x:c r="DQ74" s="88"/>
       <x:c r="DR74" s="88"/>
       <x:c r="DS74" s="88"/>
+      <x:c r="DT74" s="100"/>
     </x:row>
     <x:row r="75" ht="25" customHeight="1">
       <x:c r="A75" s="10"/>
@@ -13903,6 +14032,7 @@
       <x:c r="DQ75" s="88"/>
       <x:c r="DR75" s="88"/>
       <x:c r="DS75" s="88"/>
+      <x:c r="DT75" s="100"/>
     </x:row>
     <x:row r="76" ht="25" customHeight="1">
       <x:c r="A76" s="10"/>
@@ -13988,6 +14118,7 @@
       <x:c r="DQ76" s="88"/>
       <x:c r="DR76" s="88"/>
       <x:c r="DS76" s="88"/>
+      <x:c r="DT76" s="100"/>
     </x:row>
     <x:row r="77" ht="25" customHeight="1">
       <x:c r="A77" s="10"/>
@@ -14073,6 +14204,7 @@
       <x:c r="DQ77" s="88"/>
       <x:c r="DR77" s="88"/>
       <x:c r="DS77" s="88"/>
+      <x:c r="DT77" s="100"/>
     </x:row>
     <x:row r="78" ht="25" customHeight="1">
       <x:c r="A78" s="10"/>
@@ -14158,6 +14290,7 @@
       <x:c r="DQ78" s="88"/>
       <x:c r="DR78" s="88"/>
       <x:c r="DS78" s="88"/>
+      <x:c r="DT78" s="100"/>
     </x:row>
     <x:row r="79" ht="25" customHeight="1">
       <x:c r="A79" s="10"/>
@@ -14243,6 +14376,7 @@
       <x:c r="DQ79" s="88"/>
       <x:c r="DR79" s="88"/>
       <x:c r="DS79" s="88"/>
+      <x:c r="DT79" s="100"/>
     </x:row>
     <x:row r="80" ht="25" customHeight="1">
       <x:c r="A80" s="10"/>
@@ -14328,6 +14462,7 @@
       <x:c r="DQ80" s="88"/>
       <x:c r="DR80" s="88"/>
       <x:c r="DS80" s="88"/>
+      <x:c r="DT80" s="100"/>
     </x:row>
     <x:row r="81" ht="25" customHeight="1">
       <x:c r="A81" s="10"/>
@@ -14413,6 +14548,7 @@
       <x:c r="DQ81" s="88"/>
       <x:c r="DR81" s="88"/>
       <x:c r="DS81" s="88"/>
+      <x:c r="DT81" s="100"/>
     </x:row>
     <x:row r="82" ht="25" customHeight="1">
       <x:c r="A82" s="10"/>
@@ -14498,6 +14634,7 @@
       <x:c r="DQ82" s="88"/>
       <x:c r="DR82" s="88"/>
       <x:c r="DS82" s="88"/>
+      <x:c r="DT82" s="100"/>
     </x:row>
     <x:row r="83" ht="25" customHeight="1">
       <x:c r="A83" s="10"/>
@@ -14583,6 +14720,7 @@
       <x:c r="DQ83" s="88"/>
       <x:c r="DR83" s="88"/>
       <x:c r="DS83" s="88"/>
+      <x:c r="DT83" s="100"/>
     </x:row>
     <x:row r="84" ht="25" customHeight="1">
       <x:c r="A84" s="10"/>
@@ -14668,6 +14806,7 @@
       <x:c r="DQ84" s="88"/>
       <x:c r="DR84" s="88"/>
       <x:c r="DS84" s="88"/>
+      <x:c r="DT84" s="100"/>
     </x:row>
     <x:row r="85" ht="25" customHeight="1">
       <x:c r="A85" s="10"/>
@@ -14753,6 +14892,7 @@
       <x:c r="DQ85" s="88"/>
       <x:c r="DR85" s="88"/>
       <x:c r="DS85" s="88"/>
+      <x:c r="DT85" s="100"/>
     </x:row>
     <x:row r="86" ht="25" customHeight="1">
       <x:c r="A86" s="10"/>
@@ -14838,6 +14978,7 @@
       <x:c r="DQ86" s="88"/>
       <x:c r="DR86" s="88"/>
       <x:c r="DS86" s="88"/>
+      <x:c r="DT86" s="100"/>
     </x:row>
     <x:row r="87" ht="25" customHeight="1">
       <x:c r="A87" s="10"/>
@@ -14923,6 +15064,7 @@
       <x:c r="DQ87" s="88"/>
       <x:c r="DR87" s="88"/>
       <x:c r="DS87" s="88"/>
+      <x:c r="DT87" s="100"/>
     </x:row>
     <x:row r="88" ht="25" customHeight="1">
       <x:c r="A88" s="10"/>
@@ -15008,6 +15150,7 @@
       <x:c r="DQ88" s="88"/>
       <x:c r="DR88" s="88"/>
       <x:c r="DS88" s="88"/>
+      <x:c r="DT88" s="100"/>
     </x:row>
     <x:row r="89" ht="25" customHeight="1">
       <x:c r="A89" s="10"/>
@@ -15093,6 +15236,7 @@
       <x:c r="DQ89" s="88"/>
       <x:c r="DR89" s="88"/>
       <x:c r="DS89" s="88"/>
+      <x:c r="DT89" s="100"/>
     </x:row>
     <x:row r="90" ht="25" customHeight="1">
       <x:c r="A90" s="10"/>
@@ -15178,6 +15322,7 @@
       <x:c r="DQ90" s="88"/>
       <x:c r="DR90" s="88"/>
       <x:c r="DS90" s="88"/>
+      <x:c r="DT90" s="100"/>
     </x:row>
     <x:row r="91" ht="25" customHeight="1">
       <x:c r="A91" s="10"/>
@@ -15263,6 +15408,7 @@
       <x:c r="DQ91" s="88"/>
       <x:c r="DR91" s="88"/>
       <x:c r="DS91" s="88"/>
+      <x:c r="DT91" s="100"/>
     </x:row>
     <x:row r="92" ht="25" customHeight="1">
       <x:c r="A92" s="10"/>
@@ -15348,6 +15494,7 @@
       <x:c r="DQ92" s="88"/>
       <x:c r="DR92" s="88"/>
       <x:c r="DS92" s="88"/>
+      <x:c r="DT92" s="100"/>
     </x:row>
     <x:row r="93" ht="25" customHeight="1">
       <x:c r="A93" s="10"/>
@@ -15433,6 +15580,7 @@
       <x:c r="DQ93" s="88"/>
       <x:c r="DR93" s="88"/>
       <x:c r="DS93" s="88"/>
+      <x:c r="DT93" s="100"/>
     </x:row>
     <x:row r="94" ht="25" customHeight="1">
       <x:c r="A94" s="10"/>
@@ -15518,6 +15666,7 @@
       <x:c r="DQ94" s="88"/>
       <x:c r="DR94" s="88"/>
       <x:c r="DS94" s="88"/>
+      <x:c r="DT94" s="100"/>
     </x:row>
     <x:row r="95" ht="25" customHeight="1">
       <x:c r="A95" s="10"/>
@@ -15603,6 +15752,7 @@
       <x:c r="DQ95" s="88"/>
       <x:c r="DR95" s="88"/>
       <x:c r="DS95" s="88"/>
+      <x:c r="DT95" s="100"/>
     </x:row>
     <x:row r="96" ht="25" customHeight="1">
       <x:c r="A96" s="10"/>
@@ -15688,6 +15838,7 @@
       <x:c r="DQ96" s="88"/>
       <x:c r="DR96" s="88"/>
       <x:c r="DS96" s="88"/>
+      <x:c r="DT96" s="100"/>
     </x:row>
     <x:row r="97" ht="25" customHeight="1">
       <x:c r="A97" s="10"/>
@@ -15773,6 +15924,7 @@
       <x:c r="DQ97" s="88"/>
       <x:c r="DR97" s="88"/>
       <x:c r="DS97" s="88"/>
+      <x:c r="DT97" s="100"/>
     </x:row>
     <x:row r="98" ht="25" customHeight="1">
       <x:c r="A98" s="10"/>
@@ -15858,6 +16010,7 @@
       <x:c r="DQ98" s="88"/>
       <x:c r="DR98" s="88"/>
       <x:c r="DS98" s="88"/>
+      <x:c r="DT98" s="100"/>
     </x:row>
     <x:row r="99" ht="25" customHeight="1">
       <x:c r="A99" s="10"/>
@@ -15943,6 +16096,7 @@
       <x:c r="DQ99" s="88"/>
       <x:c r="DR99" s="88"/>
       <x:c r="DS99" s="88"/>
+      <x:c r="DT99" s="100"/>
     </x:row>
     <x:row r="100" ht="25" customHeight="1">
       <x:c r="A100" s="10"/>
@@ -16028,6 +16182,7 @@
       <x:c r="DQ100" s="88"/>
       <x:c r="DR100" s="88"/>
       <x:c r="DS100" s="88"/>
+      <x:c r="DT100" s="100"/>
     </x:row>
     <x:row r="101" ht="25" customHeight="1">
       <x:c r="A101" s="10"/>
@@ -16113,6 +16268,7 @@
       <x:c r="DQ101" s="88"/>
       <x:c r="DR101" s="88"/>
       <x:c r="DS101" s="88"/>
+      <x:c r="DT101" s="100"/>
     </x:row>
     <x:row r="102" ht="25" customHeight="1">
       <x:c r="A102" s="10"/>
@@ -16198,6 +16354,7 @@
       <x:c r="DQ102" s="88"/>
       <x:c r="DR102" s="88"/>
       <x:c r="DS102" s="88"/>
+      <x:c r="DT102" s="100"/>
     </x:row>
     <x:row r="103" ht="25" customHeight="1">
       <x:c r="A103" s="10"/>
@@ -16283,6 +16440,7 @@
       <x:c r="DQ103" s="88"/>
       <x:c r="DR103" s="88"/>
       <x:c r="DS103" s="88"/>
+      <x:c r="DT103" s="100"/>
     </x:row>
     <x:row r="104" ht="25" customHeight="1">
       <x:c r="A104" s="10"/>
@@ -16368,6 +16526,7 @@
       <x:c r="DQ104" s="88"/>
       <x:c r="DR104" s="88"/>
       <x:c r="DS104" s="88"/>
+      <x:c r="DT104" s="100"/>
     </x:row>
     <x:row r="105" ht="25" customHeight="1">
       <x:c r="A105" s="10"/>
@@ -16453,6 +16612,7 @@
       <x:c r="DQ105" s="88"/>
       <x:c r="DR105" s="88"/>
       <x:c r="DS105" s="88"/>
+      <x:c r="DT105" s="100"/>
     </x:row>
     <x:row r="106" ht="25" customHeight="1">
       <x:c r="A106" s="10"/>
@@ -16538,6 +16698,7 @@
       <x:c r="DQ106" s="88"/>
       <x:c r="DR106" s="88"/>
       <x:c r="DS106" s="88"/>
+      <x:c r="DT106" s="100"/>
     </x:row>
     <x:row r="107" ht="25" customHeight="1">
       <x:c r="A107" s="10"/>
@@ -16623,6 +16784,7 @@
       <x:c r="DQ107" s="88"/>
       <x:c r="DR107" s="88"/>
       <x:c r="DS107" s="88"/>
+      <x:c r="DT107" s="100"/>
     </x:row>
     <x:row r="108" ht="25" customHeight="1">
       <x:c r="A108" s="10"/>
@@ -16708,6 +16870,7 @@
       <x:c r="DQ108" s="88"/>
       <x:c r="DR108" s="88"/>
       <x:c r="DS108" s="88"/>
+      <x:c r="DT108" s="100"/>
     </x:row>
     <x:row r="109" ht="25" customHeight="1">
       <x:c r="A109" s="10"/>
@@ -16793,6 +16956,7 @@
       <x:c r="DQ109" s="88"/>
       <x:c r="DR109" s="88"/>
       <x:c r="DS109" s="88"/>
+      <x:c r="DT109" s="100"/>
     </x:row>
     <x:row r="110" ht="25" customHeight="1">
       <x:c r="A110" s="10"/>
@@ -16878,6 +17042,7 @@
       <x:c r="DQ110" s="88"/>
       <x:c r="DR110" s="88"/>
       <x:c r="DS110" s="88"/>
+      <x:c r="DT110" s="100"/>
     </x:row>
     <x:row r="111" ht="25" customHeight="1">
       <x:c r="A111" s="10"/>
@@ -16963,6 +17128,7 @@
       <x:c r="DQ111" s="88"/>
       <x:c r="DR111" s="88"/>
       <x:c r="DS111" s="88"/>
+      <x:c r="DT111" s="100"/>
     </x:row>
     <x:row r="112" ht="25" customHeight="1">
       <x:c r="A112" s="10"/>
@@ -17048,6 +17214,7 @@
       <x:c r="DQ112" s="88"/>
       <x:c r="DR112" s="88"/>
       <x:c r="DS112" s="88"/>
+      <x:c r="DT112" s="100"/>
     </x:row>
     <x:row r="113" ht="25" customHeight="1">
       <x:c r="A113" s="10"/>
@@ -17133,6 +17300,7 @@
       <x:c r="DQ113" s="88"/>
       <x:c r="DR113" s="88"/>
       <x:c r="DS113" s="88"/>
+      <x:c r="DT113" s="100"/>
     </x:row>
     <x:row r="114" ht="25" customHeight="1">
       <x:c r="A114" s="10"/>
@@ -17218,6 +17386,7 @@
       <x:c r="DQ114" s="88"/>
       <x:c r="DR114" s="88"/>
       <x:c r="DS114" s="88"/>
+      <x:c r="DT114" s="100"/>
     </x:row>
     <x:row r="115" ht="25" customHeight="1">
       <x:c r="A115" s="10"/>
@@ -17303,6 +17472,7 @@
       <x:c r="DQ115" s="88"/>
       <x:c r="DR115" s="88"/>
       <x:c r="DS115" s="88"/>
+      <x:c r="DT115" s="100"/>
     </x:row>
     <x:row r="116" ht="25" customHeight="1">
       <x:c r="A116" s="10"/>
@@ -17388,6 +17558,7 @@
       <x:c r="DQ116" s="88"/>
       <x:c r="DR116" s="88"/>
       <x:c r="DS116" s="88"/>
+      <x:c r="DT116" s="100"/>
     </x:row>
     <x:row r="117" ht="25" customHeight="1">
       <x:c r="A117" s="10"/>
@@ -17473,6 +17644,7 @@
       <x:c r="DQ117" s="88"/>
       <x:c r="DR117" s="88"/>
       <x:c r="DS117" s="88"/>
+      <x:c r="DT117" s="100"/>
     </x:row>
     <x:row r="118" ht="25" customHeight="1">
       <x:c r="A118" s="10"/>
@@ -17558,6 +17730,7 @@
       <x:c r="DQ118" s="88"/>
       <x:c r="DR118" s="88"/>
       <x:c r="DS118" s="88"/>
+      <x:c r="DT118" s="100"/>
     </x:row>
     <x:row r="119" ht="25" customHeight="1">
       <x:c r="A119" s="10"/>
@@ -17643,6 +17816,7 @@
       <x:c r="DQ119" s="88"/>
       <x:c r="DR119" s="88"/>
       <x:c r="DS119" s="88"/>
+      <x:c r="DT119" s="100"/>
     </x:row>
     <x:row r="120" ht="25" customHeight="1">
       <x:c r="A120" s="10"/>
@@ -17728,6 +17902,7 @@
       <x:c r="DQ120" s="88"/>
       <x:c r="DR120" s="88"/>
       <x:c r="DS120" s="88"/>
+      <x:c r="DT120" s="100"/>
     </x:row>
     <x:row r="121" ht="25" customHeight="1">
       <x:c r="A121" s="10"/>
@@ -17813,6 +17988,7 @@
       <x:c r="DQ121" s="88"/>
       <x:c r="DR121" s="88"/>
       <x:c r="DS121" s="88"/>
+      <x:c r="DT121" s="100"/>
     </x:row>
     <x:row r="122" ht="25" customHeight="1">
       <x:c r="A122" s="10"/>
@@ -17898,6 +18074,7 @@
       <x:c r="DQ122" s="88"/>
       <x:c r="DR122" s="88"/>
       <x:c r="DS122" s="88"/>
+      <x:c r="DT122" s="100"/>
     </x:row>
     <x:row r="123" ht="25" customHeight="1">
       <x:c r="A123" s="10"/>
@@ -17983,6 +18160,7 @@
       <x:c r="DQ123" s="88"/>
       <x:c r="DR123" s="88"/>
       <x:c r="DS123" s="88"/>
+      <x:c r="DT123" s="100"/>
     </x:row>
     <x:row r="124" ht="25" customHeight="1">
       <x:c r="A124" s="10"/>
@@ -18068,6 +18246,7 @@
       <x:c r="DQ124" s="88"/>
       <x:c r="DR124" s="88"/>
       <x:c r="DS124" s="88"/>
+      <x:c r="DT124" s="100"/>
     </x:row>
     <x:row r="125" ht="25" customHeight="1">
       <x:c r="A125" s="10"/>
@@ -18153,6 +18332,7 @@
       <x:c r="DQ125" s="88"/>
       <x:c r="DR125" s="88"/>
       <x:c r="DS125" s="88"/>
+      <x:c r="DT125" s="100"/>
     </x:row>
     <x:row r="126" ht="25" customHeight="1">
       <x:c r="A126" s="10"/>
@@ -18238,6 +18418,7 @@
       <x:c r="DQ126" s="88"/>
       <x:c r="DR126" s="88"/>
       <x:c r="DS126" s="88"/>
+      <x:c r="DT126" s="100"/>
     </x:row>
     <x:row r="127" ht="25" customHeight="1">
       <x:c r="A127" s="10"/>
@@ -18323,6 +18504,7 @@
       <x:c r="DQ127" s="88"/>
       <x:c r="DR127" s="88"/>
       <x:c r="DS127" s="88"/>
+      <x:c r="DT127" s="100"/>
     </x:row>
     <x:row r="128" ht="25" customHeight="1">
       <x:c r="A128" s="10"/>
@@ -18408,6 +18590,7 @@
       <x:c r="DQ128" s="88"/>
       <x:c r="DR128" s="88"/>
       <x:c r="DS128" s="88"/>
+      <x:c r="DT128" s="100"/>
     </x:row>
     <x:row r="129" ht="25" customHeight="1">
       <x:c r="A129" s="10"/>
@@ -18493,6 +18676,7 @@
       <x:c r="DQ129" s="88"/>
       <x:c r="DR129" s="88"/>
       <x:c r="DS129" s="88"/>
+      <x:c r="DT129" s="100"/>
     </x:row>
     <x:row r="130" ht="25" customHeight="1">
       <x:c r="A130" s="10"/>
@@ -18578,6 +18762,7 @@
       <x:c r="DQ130" s="88"/>
       <x:c r="DR130" s="88"/>
       <x:c r="DS130" s="88"/>
+      <x:c r="DT130" s="100"/>
     </x:row>
     <x:row r="131" ht="25" customHeight="1">
       <x:c r="A131" s="10"/>
@@ -18663,6 +18848,7 @@
       <x:c r="DQ131" s="88"/>
       <x:c r="DR131" s="88"/>
       <x:c r="DS131" s="88"/>
+      <x:c r="DT131" s="100"/>
     </x:row>
     <x:row r="132" ht="25" customHeight="1">
       <x:c r="A132" s="10"/>
@@ -18748,6 +18934,7 @@
       <x:c r="DQ132" s="88"/>
       <x:c r="DR132" s="88"/>
       <x:c r="DS132" s="88"/>
+      <x:c r="DT132" s="100"/>
     </x:row>
     <x:row r="133" ht="25" customHeight="1">
       <x:c r="A133" s="10"/>
@@ -18833,6 +19020,7 @@
       <x:c r="DQ133" s="88"/>
       <x:c r="DR133" s="88"/>
       <x:c r="DS133" s="88"/>
+      <x:c r="DT133" s="100"/>
     </x:row>
     <x:row r="134" ht="25" customHeight="1">
       <x:c r="A134" s="10"/>
@@ -18918,6 +19106,7 @@
       <x:c r="DQ134" s="88"/>
       <x:c r="DR134" s="88"/>
       <x:c r="DS134" s="88"/>
+      <x:c r="DT134" s="100"/>
     </x:row>
     <x:row r="135" ht="25" customHeight="1">
       <x:c r="A135" s="10"/>
@@ -19003,6 +19192,7 @@
       <x:c r="DQ135" s="88"/>
       <x:c r="DR135" s="88"/>
       <x:c r="DS135" s="88"/>
+      <x:c r="DT135" s="100"/>
     </x:row>
     <x:row r="136" ht="25" customHeight="1">
       <x:c r="A136" s="10"/>
@@ -19088,6 +19278,7 @@
       <x:c r="DQ136" s="88"/>
       <x:c r="DR136" s="88"/>
       <x:c r="DS136" s="88"/>
+      <x:c r="DT136" s="100"/>
     </x:row>
     <x:row r="137" ht="25" customHeight="1">
       <x:c r="A137" s="10"/>
@@ -19173,6 +19364,7 @@
       <x:c r="DQ137" s="88"/>
       <x:c r="DR137" s="88"/>
       <x:c r="DS137" s="88"/>
+      <x:c r="DT137" s="100"/>
     </x:row>
     <x:row r="138" ht="25" customHeight="1">
       <x:c r="A138" s="10"/>
@@ -19258,6 +19450,7 @@
       <x:c r="DQ138" s="88"/>
       <x:c r="DR138" s="88"/>
       <x:c r="DS138" s="88"/>
+      <x:c r="DT138" s="100"/>
     </x:row>
     <x:row r="139" ht="25" customHeight="1">
       <x:c r="A139" s="10"/>
@@ -19343,6 +19536,7 @@
       <x:c r="DQ139" s="88"/>
       <x:c r="DR139" s="88"/>
       <x:c r="DS139" s="88"/>
+      <x:c r="DT139" s="100"/>
     </x:row>
     <x:row r="140" ht="25" customHeight="1">
       <x:c r="A140" s="10"/>
@@ -19428,6 +19622,7 @@
       <x:c r="DQ140" s="88"/>
       <x:c r="DR140" s="88"/>
       <x:c r="DS140" s="88"/>
+      <x:c r="DT140" s="100"/>
     </x:row>
     <x:row r="141" ht="25" customHeight="1">
       <x:c r="A141" s="10"/>
@@ -19513,6 +19708,7 @@
       <x:c r="DQ141" s="88"/>
       <x:c r="DR141" s="88"/>
       <x:c r="DS141" s="88"/>
+      <x:c r="DT141" s="100"/>
     </x:row>
     <x:row r="142" ht="25" customHeight="1">
       <x:c r="A142" s="10"/>
@@ -19598,6 +19794,7 @@
       <x:c r="DQ142" s="88"/>
       <x:c r="DR142" s="88"/>
       <x:c r="DS142" s="88"/>
+      <x:c r="DT142" s="100"/>
     </x:row>
     <x:row r="143" ht="25" customHeight="1">
       <x:c r="A143" s="10"/>
@@ -19683,6 +19880,7 @@
       <x:c r="DQ143" s="88"/>
       <x:c r="DR143" s="88"/>
       <x:c r="DS143" s="88"/>
+      <x:c r="DT143" s="100"/>
     </x:row>
     <x:row r="144" ht="25" customHeight="1">
       <x:c r="A144" s="10"/>
@@ -19768,6 +19966,7 @@
       <x:c r="DQ144" s="88"/>
       <x:c r="DR144" s="88"/>
       <x:c r="DS144" s="88"/>
+      <x:c r="DT144" s="100"/>
     </x:row>
     <x:row r="145" ht="25" customHeight="1">
       <x:c r="A145" s="10"/>
@@ -19853,6 +20052,7 @@
       <x:c r="DQ145" s="88"/>
       <x:c r="DR145" s="88"/>
       <x:c r="DS145" s="88"/>
+      <x:c r="DT145" s="100"/>
     </x:row>
     <x:row r="146" ht="25" customHeight="1">
       <x:c r="A146" s="10"/>
@@ -19938,6 +20138,7 @@
       <x:c r="DQ146" s="88"/>
       <x:c r="DR146" s="88"/>
       <x:c r="DS146" s="88"/>
+      <x:c r="DT146" s="100"/>
     </x:row>
     <x:row r="147" ht="25" customHeight="1">
       <x:c r="A147" s="10"/>
@@ -20023,6 +20224,7 @@
       <x:c r="DQ147" s="88"/>
       <x:c r="DR147" s="88"/>
       <x:c r="DS147" s="88"/>
+      <x:c r="DT147" s="100"/>
     </x:row>
     <x:row r="148" ht="25" customHeight="1">
       <x:c r="A148" s="10"/>
@@ -20108,6 +20310,7 @@
       <x:c r="DQ148" s="88"/>
       <x:c r="DR148" s="88"/>
       <x:c r="DS148" s="88"/>
+      <x:c r="DT148" s="100"/>
     </x:row>
     <x:row r="149" ht="25" customHeight="1">
       <x:c r="A149" s="10"/>
@@ -20193,6 +20396,7 @@
       <x:c r="DQ149" s="88"/>
       <x:c r="DR149" s="88"/>
       <x:c r="DS149" s="88"/>
+      <x:c r="DT149" s="100"/>
     </x:row>
     <x:row r="150" ht="25" customHeight="1">
       <x:c r="A150" s="10"/>
@@ -20278,6 +20482,7 @@
       <x:c r="DQ150" s="88"/>
       <x:c r="DR150" s="88"/>
       <x:c r="DS150" s="88"/>
+      <x:c r="DT150" s="100"/>
     </x:row>
     <x:row r="151" ht="25" customHeight="1">
       <x:c r="A151" s="10"/>
@@ -20363,6 +20568,7 @@
       <x:c r="DQ151" s="88"/>
       <x:c r="DR151" s="88"/>
       <x:c r="DS151" s="88"/>
+      <x:c r="DT151" s="100"/>
     </x:row>
     <x:row r="152" ht="25" customHeight="1">
       <x:c r="A152" s="10"/>
@@ -20448,6 +20654,7 @@
       <x:c r="DQ152" s="88"/>
       <x:c r="DR152" s="88"/>
       <x:c r="DS152" s="88"/>
+      <x:c r="DT152" s="100"/>
     </x:row>
     <x:row r="153" ht="25" customHeight="1">
       <x:c r="A153" s="10"/>
@@ -20533,6 +20740,7 @@
       <x:c r="DQ153" s="88"/>
       <x:c r="DR153" s="88"/>
       <x:c r="DS153" s="88"/>
+      <x:c r="DT153" s="100"/>
     </x:row>
     <x:row r="154" ht="25" customHeight="1">
       <x:c r="A154" s="10"/>
@@ -20618,6 +20826,7 @@
       <x:c r="DQ154" s="88"/>
       <x:c r="DR154" s="88"/>
       <x:c r="DS154" s="88"/>
+      <x:c r="DT154" s="100"/>
     </x:row>
     <x:row r="155" ht="25" customHeight="1">
       <x:c r="A155" s="10"/>
@@ -20703,6 +20912,7 @@
       <x:c r="DQ155" s="88"/>
       <x:c r="DR155" s="88"/>
       <x:c r="DS155" s="88"/>
+      <x:c r="DT155" s="100"/>
     </x:row>
     <x:row r="156" ht="25" customHeight="1">
       <x:c r="A156" s="10"/>
@@ -20788,6 +20998,7 @@
       <x:c r="DQ156" s="88"/>
       <x:c r="DR156" s="88"/>
       <x:c r="DS156" s="88"/>
+      <x:c r="DT156" s="100"/>
     </x:row>
     <x:row r="157" ht="25" customHeight="1">
       <x:c r="A157" s="10"/>
@@ -20873,6 +21084,7 @@
       <x:c r="DQ157" s="88"/>
       <x:c r="DR157" s="88"/>
       <x:c r="DS157" s="88"/>
+      <x:c r="DT157" s="100"/>
     </x:row>
     <x:row r="158" ht="25" customHeight="1">
       <x:c r="A158" s="10"/>
@@ -20958,6 +21170,7 @@
       <x:c r="DQ158" s="88"/>
       <x:c r="DR158" s="88"/>
       <x:c r="DS158" s="88"/>
+      <x:c r="DT158" s="100"/>
     </x:row>
     <x:row r="159" ht="25" customHeight="1">
       <x:c r="A159" s="10"/>
@@ -21043,6 +21256,7 @@
       <x:c r="DQ159" s="88"/>
       <x:c r="DR159" s="88"/>
       <x:c r="DS159" s="88"/>
+      <x:c r="DT159" s="100"/>
     </x:row>
     <x:row r="160" ht="25" customHeight="1">
       <x:c r="A160" s="10"/>
@@ -21128,6 +21342,7 @@
       <x:c r="DQ160" s="88"/>
       <x:c r="DR160" s="88"/>
       <x:c r="DS160" s="88"/>
+      <x:c r="DT160" s="100"/>
     </x:row>
     <x:row r="161" ht="25" customHeight="1">
       <x:c r="A161" s="10"/>
@@ -21213,6 +21428,7 @@
       <x:c r="DQ161" s="88"/>
       <x:c r="DR161" s="88"/>
       <x:c r="DS161" s="88"/>
+      <x:c r="DT161" s="100"/>
     </x:row>
     <x:row r="162" ht="25" customHeight="1">
       <x:c r="A162" s="10"/>
@@ -21298,6 +21514,7 @@
       <x:c r="DQ162" s="88"/>
       <x:c r="DR162" s="88"/>
       <x:c r="DS162" s="88"/>
+      <x:c r="DT162" s="100"/>
     </x:row>
     <x:row r="163" ht="25" customHeight="1">
       <x:c r="A163" s="10"/>
@@ -21383,6 +21600,7 @@
       <x:c r="DQ163" s="88"/>
       <x:c r="DR163" s="88"/>
       <x:c r="DS163" s="88"/>
+      <x:c r="DT163" s="100"/>
     </x:row>
     <x:row r="164" ht="25" customHeight="1">
       <x:c r="A164" s="10"/>
@@ -21468,6 +21686,7 @@
       <x:c r="DQ164" s="88"/>
       <x:c r="DR164" s="88"/>
       <x:c r="DS164" s="88"/>
+      <x:c r="DT164" s="100"/>
     </x:row>
     <x:row r="165" ht="25" customHeight="1">
       <x:c r="A165" s="10"/>
@@ -21553,6 +21772,7 @@
       <x:c r="DQ165" s="88"/>
       <x:c r="DR165" s="88"/>
       <x:c r="DS165" s="88"/>
+      <x:c r="DT165" s="100"/>
     </x:row>
     <x:row r="166" ht="25" customHeight="1">
       <x:c r="A166" s="10"/>
@@ -21638,6 +21858,7 @@
       <x:c r="DQ166" s="88"/>
       <x:c r="DR166" s="88"/>
       <x:c r="DS166" s="88"/>
+      <x:c r="DT166" s="100"/>
     </x:row>
     <x:row r="167" ht="25" customHeight="1">
       <x:c r="A167" s="10"/>
@@ -21723,6 +21944,7 @@
       <x:c r="DQ167" s="88"/>
       <x:c r="DR167" s="88"/>
       <x:c r="DS167" s="88"/>
+      <x:c r="DT167" s="100"/>
     </x:row>
     <x:row r="168" ht="25" customHeight="1">
       <x:c r="A168" s="10"/>
@@ -21808,6 +22030,7 @@
       <x:c r="DQ168" s="88"/>
       <x:c r="DR168" s="88"/>
       <x:c r="DS168" s="88"/>
+      <x:c r="DT168" s="100"/>
     </x:row>
     <x:row r="169" ht="25" customHeight="1">
       <x:c r="A169" s="10"/>
@@ -21893,6 +22116,7 @@
       <x:c r="DQ169" s="88"/>
       <x:c r="DR169" s="88"/>
       <x:c r="DS169" s="88"/>
+      <x:c r="DT169" s="100"/>
     </x:row>
     <x:row r="170" ht="25" customHeight="1">
       <x:c r="A170" s="10"/>
@@ -21978,6 +22202,7 @@
       <x:c r="DQ170" s="88"/>
       <x:c r="DR170" s="88"/>
       <x:c r="DS170" s="88"/>
+      <x:c r="DT170" s="100"/>
     </x:row>
     <x:row r="171" ht="25" customHeight="1">
       <x:c r="A171" s="10"/>
@@ -22063,6 +22288,7 @@
       <x:c r="DQ171" s="88"/>
       <x:c r="DR171" s="88"/>
       <x:c r="DS171" s="88"/>
+      <x:c r="DT171" s="100"/>
     </x:row>
     <x:row r="172" ht="25" customHeight="1">
       <x:c r="A172" s="10"/>
@@ -22148,6 +22374,7 @@
       <x:c r="DQ172" s="88"/>
       <x:c r="DR172" s="88"/>
       <x:c r="DS172" s="88"/>
+      <x:c r="DT172" s="100"/>
     </x:row>
     <x:row r="173" ht="25" customHeight="1">
       <x:c r="A173" s="10"/>
@@ -22233,6 +22460,7 @@
       <x:c r="DQ173" s="88"/>
       <x:c r="DR173" s="88"/>
       <x:c r="DS173" s="88"/>
+      <x:c r="DT173" s="100"/>
     </x:row>
     <x:row r="174" ht="25" customHeight="1">
       <x:c r="A174" s="10"/>
@@ -22318,6 +22546,7 @@
       <x:c r="DQ174" s="88"/>
       <x:c r="DR174" s="88"/>
       <x:c r="DS174" s="88"/>
+      <x:c r="DT174" s="100"/>
     </x:row>
     <x:row r="175" ht="25" customHeight="1">
       <x:c r="A175" s="10"/>
@@ -22403,6 +22632,7 @@
       <x:c r="DQ175" s="88"/>
       <x:c r="DR175" s="88"/>
       <x:c r="DS175" s="88"/>
+      <x:c r="DT175" s="100"/>
     </x:row>
     <x:row r="176" ht="25" customHeight="1">
       <x:c r="A176" s="10"/>
@@ -22488,6 +22718,7 @@
       <x:c r="DQ176" s="88"/>
       <x:c r="DR176" s="88"/>
       <x:c r="DS176" s="88"/>
+      <x:c r="DT176" s="100"/>
     </x:row>
     <x:row r="177" ht="25" customHeight="1">
       <x:c r="A177" s="10"/>
@@ -22573,6 +22804,7 @@
       <x:c r="DQ177" s="88"/>
       <x:c r="DR177" s="88"/>
       <x:c r="DS177" s="88"/>
+      <x:c r="DT177" s="100"/>
     </x:row>
     <x:row r="178" ht="25" customHeight="1">
       <x:c r="A178" s="10"/>
@@ -22658,6 +22890,7 @@
       <x:c r="DQ178" s="88"/>
       <x:c r="DR178" s="88"/>
       <x:c r="DS178" s="88"/>
+      <x:c r="DT178" s="100"/>
     </x:row>
     <x:row r="179" ht="25" customHeight="1">
       <x:c r="A179" s="10"/>
@@ -22743,6 +22976,7 @@
       <x:c r="DQ179" s="88"/>
       <x:c r="DR179" s="88"/>
       <x:c r="DS179" s="88"/>
+      <x:c r="DT179" s="100"/>
     </x:row>
     <x:row r="180" ht="25" customHeight="1">
       <x:c r="A180" s="10"/>
@@ -22828,6 +23062,7 @@
       <x:c r="DQ180" s="88"/>
       <x:c r="DR180" s="88"/>
       <x:c r="DS180" s="88"/>
+      <x:c r="DT180" s="100"/>
     </x:row>
     <x:row r="181" ht="25" customHeight="1">
       <x:c r="A181" s="10"/>
@@ -22913,6 +23148,7 @@
       <x:c r="DQ181" s="88"/>
       <x:c r="DR181" s="88"/>
       <x:c r="DS181" s="88"/>
+      <x:c r="DT181" s="100"/>
     </x:row>
     <x:row r="182" ht="25" customHeight="1">
       <x:c r="A182" s="10"/>
@@ -22998,6 +23234,7 @@
       <x:c r="DQ182" s="88"/>
       <x:c r="DR182" s="88"/>
       <x:c r="DS182" s="88"/>
+      <x:c r="DT182" s="100"/>
     </x:row>
     <x:row r="183" ht="25" customHeight="1">
       <x:c r="A183" s="10"/>
@@ -23083,6 +23320,7 @@
       <x:c r="DQ183" s="88"/>
       <x:c r="DR183" s="88"/>
       <x:c r="DS183" s="88"/>
+      <x:c r="DT183" s="100"/>
     </x:row>
     <x:row r="184" ht="25" customHeight="1">
       <x:c r="A184" s="10"/>
@@ -23168,6 +23406,7 @@
       <x:c r="DQ184" s="88"/>
       <x:c r="DR184" s="88"/>
       <x:c r="DS184" s="88"/>
+      <x:c r="DT184" s="100"/>
     </x:row>
     <x:row r="185" ht="25" customHeight="1">
       <x:c r="A185" s="10"/>
@@ -23253,6 +23492,7 @@
       <x:c r="DQ185" s="88"/>
       <x:c r="DR185" s="88"/>
       <x:c r="DS185" s="88"/>
+      <x:c r="DT185" s="100"/>
     </x:row>
     <x:row r="186" ht="25" customHeight="1">
       <x:c r="A186" s="10"/>
@@ -23338,6 +23578,7 @@
       <x:c r="DQ186" s="88"/>
       <x:c r="DR186" s="88"/>
       <x:c r="DS186" s="88"/>
+      <x:c r="DT186" s="100"/>
     </x:row>
     <x:row r="187" ht="25" customHeight="1">
       <x:c r="A187" s="10"/>
@@ -23423,6 +23664,7 @@
       <x:c r="DQ187" s="88"/>
       <x:c r="DR187" s="88"/>
       <x:c r="DS187" s="88"/>
+      <x:c r="DT187" s="100"/>
     </x:row>
     <x:row r="188" ht="25" customHeight="1">
       <x:c r="A188" s="10"/>
@@ -23508,6 +23750,7 @@
       <x:c r="DQ188" s="88"/>
       <x:c r="DR188" s="88"/>
       <x:c r="DS188" s="88"/>
+      <x:c r="DT188" s="100"/>
     </x:row>
     <x:row r="189" ht="25" customHeight="1">
       <x:c r="A189" s="10"/>
@@ -23593,6 +23836,7 @@
       <x:c r="DQ189" s="88"/>
       <x:c r="DR189" s="88"/>
       <x:c r="DS189" s="88"/>
+      <x:c r="DT189" s="100"/>
     </x:row>
     <x:row r="190" ht="25" customHeight="1">
       <x:c r="A190" s="10"/>
@@ -23678,6 +23922,7 @@
       <x:c r="DQ190" s="88"/>
       <x:c r="DR190" s="88"/>
       <x:c r="DS190" s="88"/>
+      <x:c r="DT190" s="100"/>
     </x:row>
     <x:row r="191" ht="25" customHeight="1">
       <x:c r="A191" s="10"/>
@@ -23763,6 +24008,7 @@
       <x:c r="DQ191" s="88"/>
       <x:c r="DR191" s="88"/>
       <x:c r="DS191" s="88"/>
+      <x:c r="DT191" s="100"/>
     </x:row>
     <x:row r="192" ht="25" customHeight="1">
       <x:c r="A192" s="10"/>
@@ -23848,6 +24094,7 @@
       <x:c r="DQ192" s="88"/>
       <x:c r="DR192" s="88"/>
       <x:c r="DS192" s="88"/>
+      <x:c r="DT192" s="100"/>
     </x:row>
     <x:row r="193" ht="25" customHeight="1">
       <x:c r="A193" s="10"/>
@@ -23933,6 +24180,7 @@
       <x:c r="DQ193" s="88"/>
       <x:c r="DR193" s="88"/>
       <x:c r="DS193" s="88"/>
+      <x:c r="DT193" s="100"/>
     </x:row>
     <x:row r="194" ht="25" customHeight="1">
       <x:c r="A194" s="10"/>
@@ -24018,6 +24266,7 @@
       <x:c r="DQ194" s="88"/>
       <x:c r="DR194" s="88"/>
       <x:c r="DS194" s="88"/>
+      <x:c r="DT194" s="100"/>
     </x:row>
     <x:row r="195" ht="25" customHeight="1">
       <x:c r="A195" s="10"/>
@@ -24103,6 +24352,7 @@
       <x:c r="DQ195" s="88"/>
       <x:c r="DR195" s="88"/>
       <x:c r="DS195" s="88"/>
+      <x:c r="DT195" s="100"/>
     </x:row>
     <x:row r="196" ht="25" customHeight="1">
       <x:c r="A196" s="10"/>
@@ -24188,6 +24438,7 @@
       <x:c r="DQ196" s="88"/>
       <x:c r="DR196" s="88"/>
       <x:c r="DS196" s="88"/>
+      <x:c r="DT196" s="100"/>
     </x:row>
     <x:row r="197" ht="25" customHeight="1">
       <x:c r="A197" s="10"/>
@@ -24273,6 +24524,7 @@
       <x:c r="DQ197" s="88"/>
       <x:c r="DR197" s="88"/>
       <x:c r="DS197" s="88"/>
+      <x:c r="DT197" s="100"/>
     </x:row>
     <x:row r="198" ht="25" customHeight="1">
       <x:c r="A198" s="10"/>
@@ -24358,6 +24610,7 @@
       <x:c r="DQ198" s="88"/>
       <x:c r="DR198" s="88"/>
       <x:c r="DS198" s="88"/>
+      <x:c r="DT198" s="100"/>
     </x:row>
     <x:row r="199" ht="25" customHeight="1">
       <x:c r="A199" s="10"/>
@@ -24443,6 +24696,7 @@
       <x:c r="DQ199" s="88"/>
       <x:c r="DR199" s="88"/>
       <x:c r="DS199" s="88"/>
+      <x:c r="DT199" s="100"/>
     </x:row>
     <x:row r="200" ht="25" customHeight="1">
       <x:c r="A200" s="10"/>
@@ -24528,6 +24782,7 @@
       <x:c r="DQ200" s="88"/>
       <x:c r="DR200" s="88"/>
       <x:c r="DS200" s="88"/>
+      <x:c r="DT200" s="100"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="45">
@@ -24669,7 +24924,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R353538fd27764554"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77903f12c53f472d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24785,7 +25040,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59ed44e7d5184992"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb592899bc714783"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28091,10 +28346,150 @@
         <x:v>番号画像を配置後、Excelを取り込む</x:v>
       </x:c>
       <x:c r="C270" s="89" t="str">
-        <x:v>素材/Projectile/39.png～42.png（Sprite）</x:v>
+        <x:v>追加例39～42は画像番号3・7・2・4を使用</x:v>
       </x:c>
       <x:c r="D270" s="89" t="str">
-        <x:v>素材/Profectileでも可。画像不足時は取り込みが止まる</x:v>
+        <x:v>配置済み1～12のSpriteを利用。独自画像は右端の画像番号で変更</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" ht="32" customHeight="1">
+      <x:c r="A272" s="98" t="str">
+        <x:v>配置済み画像でエフェクト表示</x:v>
+      </x:c>
+      <x:c r="B272" s="98" t="str">
+        <x:v>項目</x:v>
+      </x:c>
+      <x:c r="C272" s="98" t="str">
+        <x:v>設定・値</x:v>
+      </x:c>
+      <x:c r="D272" s="98" t="str">
+        <x:v>反映手順</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" ht="58" customHeight="1">
+      <x:c r="A273" s="89" t="str">
+        <x:v>修正済み</x:v>
+      </x:c>
+      <x:c r="B273" s="89" t="str">
+        <x:v>ID3：衝撃波</x:v>
+      </x:c>
+      <x:c r="C273" s="89" t="str">
+        <x:v>発射物／その場／使用者生成／生成時に1回</x:v>
+      </x:c>
+      <x:c r="D273" s="89" t="str">
+        <x:v>3.pngを使い、0.45秒表示。範囲・威力は既存値を維持</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" ht="58" customHeight="1">
+      <x:c r="A274" s="89" t="str">
+        <x:v>修正済み</x:v>
+      </x:c>
+      <x:c r="B274" s="89" t="str">
+        <x:v>ID7：鈍足の陣</x:v>
+      </x:c>
+      <x:c r="C274" s="89" t="str">
+        <x:v>発射物／その場／追従なし／1秒ごと</x:v>
+      </x:c>
+      <x:c r="D274" s="89" t="str">
+        <x:v>7.pngを使い、使用地点に5秒表示。範囲内へ鈍足を付与</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" ht="58" customHeight="1">
+      <x:c r="A275" s="89" t="str">
+        <x:v>修正済み</x:v>
+      </x:c>
+      <x:c r="B275" s="89" t="str">
+        <x:v>ID11：封魔</x:v>
+      </x:c>
+      <x:c r="C275" s="89" t="str">
+        <x:v>発射物／その場／対象生成／対象追従／生成時</x:v>
+      </x:c>
+      <x:c r="D275" s="89" t="str">
+        <x:v>11.pngを使い、対象に0.8秒表示</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" ht="58" customHeight="1">
+      <x:c r="A276" s="89" t="str">
+        <x:v>画像設定</x:v>
+      </x:c>
+      <x:c r="B276" s="89" t="str">
+        <x:v>発射物_画像番号（右端DT列）</x:v>
+      </x:c>
+      <x:c r="C276" s="89" t="str">
+        <x:v>空欄ならスキルIDと同じ番号。別の正の整数も可</x:v>
+      </x:c>
+      <x:c r="D276" s="89" t="str">
+        <x:v>Prefab名はスキルIDのまま、指定した番号の画像を自動設定</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" ht="58" customHeight="1">
+      <x:c r="A277" s="89" t="str">
+        <x:v>画像共有</x:v>
+      </x:c>
+      <x:c r="B277" s="89" t="str">
+        <x:v>追加例39～42</x:v>
+      </x:c>
+      <x:c r="C277" s="89" t="str">
+        <x:v>39→3、40→7、41→2、42→4</x:v>
+      </x:c>
+      <x:c r="D277" s="89" t="str">
+        <x:v>配置済みの画像を使うため、39.png～42.pngの追加は不要</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" ht="58" customHeight="1">
+      <x:c r="A278" s="89" t="str">
+        <x:v>取り込み</x:v>
+      </x:c>
+      <x:c r="B278" s="89" t="str">
+        <x:v>更新Excelを再取り込み</x:v>
+      </x:c>
+      <x:c r="C278" s="89" t="str">
+        <x:v>MixMaster → スキル → Excel・CSVを選んで取り込む</x:v>
+      </x:c>
+      <x:c r="D278" s="89" t="str">
+        <x:v>新しいインポーターのコード反映後に実行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" ht="58" customHeight="1">
+      <x:c r="A279" s="89" t="str">
+        <x:v>生成先</x:v>
+      </x:c>
+      <x:c r="B279" s="89" t="str">
+        <x:v>Resources/Skills/Projectile/番号.prefab</x:v>
+      </x:c>
+      <x:c r="C279" s="89" t="str">
+        <x:v>ID3・7・11のPrefabも生成・更新</x:v>
+      </x:c>
+      <x:c r="D279" s="89" t="str">
+        <x:v>SkillDataも更新し、自動でPrefabを紐付け</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" ht="58" customHeight="1">
+      <x:c r="A280" s="89" t="str">
+        <x:v>独自画像</x:v>
+      </x:c>
+      <x:c r="B280" s="89" t="str">
+        <x:v>追加例に専用画像を使う場合</x:v>
+      </x:c>
+      <x:c r="C280" s="89" t="str">
+        <x:v>DT列を39～42へ変更して同番号画像を配置</x:v>
+      </x:c>
+      <x:c r="D280" s="89" t="str">
+        <x:v>画像はSprite (2D and UI)に設定。未配置番号は取り込みエラー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" ht="58" customHeight="1">
+      <x:c r="A281" s="89" t="str">
+        <x:v>表示の前提</x:v>
+      </x:c>
+      <x:c r="B281" s="89" t="str">
+        <x:v>即時発動のままでは画像を生成しない</x:v>
+      </x:c>
+      <x:c r="C281" s="89" t="str">
+        <x:v>基本的に発動形式＝発射物</x:v>
+      </x:c>
+      <x:c r="D281" s="89" t="str">
+        <x:v>その場タイプなら飛ばずにエフェクトとして表示する</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Docs/SkillTemplates/スキル定義テンプレート.xlsx
+++ b/Docs/SkillTemplates/スキル定義テンプレート.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル" sheetId="1" r:id="Raee5c59f0e494a22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="モンスター列追加例" sheetId="2" r:id="Rf54cb92c3ffe4a1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="3" r:id="Rf2b980a9d8f34ac1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル" sheetId="1" r:id="Rc2ad8614dddb470c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="モンスター列追加例" sheetId="2" r:id="R89d311b040f546f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="3" r:id="R0051bf4f84624bf4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,7 +91,7 @@
       <x:name val="Noto Sans JP"/>
     </x:font>
   </x:fonts>
-  <x:fills count="21">
+  <x:fills count="23">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -193,6 +193,16 @@
         <x:fgColor rgb="FFFFF3D5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF214E66"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3D5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border>
@@ -206,7 +216,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="102">
+  <x:cellXfs count="108">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -439,6 +449,16 @@
     <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="11" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -902,9 +922,12 @@
     <x:col min="122" max="122" width="22" hidden="0" customWidth="1"/>
     <x:col min="123" max="123" width="22" hidden="0" customWidth="1"/>
     <x:col min="124" max="124" width="22" hidden="0" customWidth="1"/>
+    <x:col min="125" max="125" width="26" hidden="0" customWidth="1"/>
+    <x:col min="126" max="126" width="26" hidden="0" customWidth="1"/>
+    <x:col min="127" max="127" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="42" customHeight="1">
+    <x:row r="1" ht="55" customHeight="1">
       <x:c r="A1" s="22" t="str">
         <x:v>ID</x:v>
       </x:c>
@@ -1276,6 +1299,15 @@
       </x:c>
       <x:c r="DT1" s="98" t="str">
         <x:v>発射物_画像番号</x:v>
+      </x:c>
+      <x:c r="DU1" s="104" t="str">
+        <x:v>発射物_範囲に表示を合わせる</x:v>
+      </x:c>
+      <x:c r="DV1" s="104" t="str">
+        <x:v>発射物_爆発拡大秒</x:v>
+      </x:c>
+      <x:c r="DW1" s="104" t="str">
+        <x:v>発射物_爆発開始倍率</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="25" customHeight="1">
@@ -1636,6 +1668,15 @@
       <x:c r="DT2" s="100" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="DU2" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV2" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW2" s="106" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="9" t="str">
@@ -1995,6 +2036,15 @@
       <x:c r="DT3" s="100" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="DU3" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV3" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW3" s="106" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
       <x:c r="A4" s="9" t="str">
@@ -2205,7 +2255,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="BS4" s="45" t="str">
-        <x:v>その場</x:v>
+        <x:v>爆発</x:v>
       </x:c>
       <x:c r="BT4" s="51" t="n">
         <x:v>8</x:v>
@@ -2354,6 +2404,15 @@
       <x:c r="DT4" s="100" t="n">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="DU4" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV4" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW4" s="106" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
       <x:c r="A5" s="9" t="str">
@@ -2713,6 +2772,15 @@
       <x:c r="DT5" s="100" t="n">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="DU5" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV5" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW5" s="106" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
       <x:c r="A6" s="9" t="str">
@@ -3072,6 +3140,15 @@
       <x:c r="DT6" s="100" t="n">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="DU6" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV6" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW6" s="106" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
       <x:c r="A7" s="9" t="str">
@@ -3431,6 +3508,15 @@
       <x:c r="DT7" s="100" t="n">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="DU7" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV7" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW7" s="106" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
       <x:c r="A8" s="9" t="str">
@@ -3790,6 +3876,15 @@
       <x:c r="DT8" s="100" t="n">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="DU8" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV8" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW8" s="106" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="25" customHeight="1">
       <x:c r="A9" s="9" t="str">
@@ -4149,6 +4244,15 @@
       <x:c r="DT9" s="100" t="n">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="DU9" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV9" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW9" s="106" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="25" customHeight="1">
       <x:c r="A10" s="9" t="str">
@@ -4508,6 +4612,15 @@
       <x:c r="DT10" s="100" t="n">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="DU10" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV10" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW10" s="106" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="25" customHeight="1">
       <x:c r="A11" s="9" t="str">
@@ -4867,6 +4980,15 @@
       <x:c r="DT11" s="100" t="n">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="DU11" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV11" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW11" s="106" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="25" customHeight="1">
       <x:c r="A12" s="9" t="str">
@@ -5226,6 +5348,15 @@
       <x:c r="DT12" s="100" t="n">
         <x:v>11</x:v>
       </x:c>
+      <x:c r="DU12" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV12" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW12" s="106" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="25" customHeight="1">
       <x:c r="A13" s="9" t="str">
@@ -5584,6 +5715,15 @@
       <x:c r="DS13" s="88"/>
       <x:c r="DT13" s="100" t="n">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="DU13" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV13" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW13" s="106" t="n">
+        <x:v>0.1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="25" customHeight="1">
@@ -5747,6 +5887,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT14" s="100"/>
+      <x:c r="DU14" s="106"/>
+      <x:c r="DV14" s="106"/>
+      <x:c r="DW14" s="106"/>
     </x:row>
     <x:row r="15" ht="25" customHeight="1">
       <x:c r="A15" s="10" t="str">
@@ -5909,6 +6052,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT15" s="100"/>
+      <x:c r="DU15" s="106"/>
+      <x:c r="DV15" s="106"/>
+      <x:c r="DW15" s="106"/>
     </x:row>
     <x:row r="16" ht="25" customHeight="1">
       <x:c r="A16" s="10" t="str">
@@ -6071,6 +6217,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT16" s="100"/>
+      <x:c r="DU16" s="106"/>
+      <x:c r="DV16" s="106"/>
+      <x:c r="DW16" s="106"/>
     </x:row>
     <x:row r="17" ht="25" customHeight="1">
       <x:c r="A17" s="10" t="str">
@@ -6233,6 +6382,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT17" s="100"/>
+      <x:c r="DU17" s="106"/>
+      <x:c r="DV17" s="106"/>
+      <x:c r="DW17" s="106"/>
     </x:row>
     <x:row r="18" ht="25" customHeight="1">
       <x:c r="A18" s="10" t="str">
@@ -6395,6 +6547,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT18" s="100"/>
+      <x:c r="DU18" s="106"/>
+      <x:c r="DV18" s="106"/>
+      <x:c r="DW18" s="106"/>
     </x:row>
     <x:row r="19" ht="25" customHeight="1">
       <x:c r="A19" s="10" t="str">
@@ -6557,6 +6712,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT19" s="100"/>
+      <x:c r="DU19" s="106"/>
+      <x:c r="DV19" s="106"/>
+      <x:c r="DW19" s="106"/>
     </x:row>
     <x:row r="20" ht="25" customHeight="1">
       <x:c r="A20" s="10" t="str">
@@ -6719,6 +6877,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT20" s="100"/>
+      <x:c r="DU20" s="106"/>
+      <x:c r="DV20" s="106"/>
+      <x:c r="DW20" s="106"/>
     </x:row>
     <x:row r="21" ht="25" customHeight="1">
       <x:c r="A21" s="10" t="str">
@@ -6881,6 +7042,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT21" s="100"/>
+      <x:c r="DU21" s="106"/>
+      <x:c r="DV21" s="106"/>
+      <x:c r="DW21" s="106"/>
     </x:row>
     <x:row r="22" ht="25" customHeight="1">
       <x:c r="A22" s="10" t="str">
@@ -7043,6 +7207,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT22" s="100"/>
+      <x:c r="DU22" s="106"/>
+      <x:c r="DV22" s="106"/>
+      <x:c r="DW22" s="106"/>
     </x:row>
     <x:row r="23" ht="25" customHeight="1">
       <x:c r="A23" s="10" t="str">
@@ -7205,6 +7372,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT23" s="100"/>
+      <x:c r="DU23" s="106"/>
+      <x:c r="DV23" s="106"/>
+      <x:c r="DW23" s="106"/>
     </x:row>
     <x:row r="24" ht="25" customHeight="1">
       <x:c r="A24" s="10" t="str">
@@ -7367,6 +7537,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT24" s="100"/>
+      <x:c r="DU24" s="106"/>
+      <x:c r="DV24" s="106"/>
+      <x:c r="DW24" s="106"/>
     </x:row>
     <x:row r="25" ht="25" customHeight="1">
       <x:c r="A25" s="10" t="str">
@@ -7529,6 +7702,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT25" s="100"/>
+      <x:c r="DU25" s="106"/>
+      <x:c r="DV25" s="106"/>
+      <x:c r="DW25" s="106"/>
     </x:row>
     <x:row r="26" ht="25" customHeight="1">
       <x:c r="A26" s="10" t="str">
@@ -7691,6 +7867,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT26" s="100"/>
+      <x:c r="DU26" s="106"/>
+      <x:c r="DV26" s="106"/>
+      <x:c r="DW26" s="106"/>
     </x:row>
     <x:row r="27" ht="25" customHeight="1">
       <x:c r="A27" s="10" t="str">
@@ -7853,6 +8032,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT27" s="100"/>
+      <x:c r="DU27" s="106"/>
+      <x:c r="DV27" s="106"/>
+      <x:c r="DW27" s="106"/>
     </x:row>
     <x:row r="28" ht="25" customHeight="1">
       <x:c r="A28" s="10" t="str">
@@ -8015,6 +8197,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT28" s="100"/>
+      <x:c r="DU28" s="106"/>
+      <x:c r="DV28" s="106"/>
+      <x:c r="DW28" s="106"/>
     </x:row>
     <x:row r="29" ht="25" customHeight="1">
       <x:c r="A29" s="10" t="str">
@@ -8177,6 +8362,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT29" s="100"/>
+      <x:c r="DU29" s="106"/>
+      <x:c r="DV29" s="106"/>
+      <x:c r="DW29" s="106"/>
     </x:row>
     <x:row r="30" ht="25" customHeight="1">
       <x:c r="A30" s="10" t="str">
@@ -8339,6 +8527,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT30" s="100"/>
+      <x:c r="DU30" s="106"/>
+      <x:c r="DV30" s="106"/>
+      <x:c r="DW30" s="106"/>
     </x:row>
     <x:row r="31" ht="25" customHeight="1">
       <x:c r="A31" s="10" t="str">
@@ -8501,6 +8692,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT31" s="100"/>
+      <x:c r="DU31" s="106"/>
+      <x:c r="DV31" s="106"/>
+      <x:c r="DW31" s="106"/>
     </x:row>
     <x:row r="32" ht="25" customHeight="1">
       <x:c r="A32" s="10" t="str">
@@ -8663,6 +8857,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT32" s="100"/>
+      <x:c r="DU32" s="106"/>
+      <x:c r="DV32" s="106"/>
+      <x:c r="DW32" s="106"/>
     </x:row>
     <x:row r="33" ht="25" customHeight="1">
       <x:c r="A33" s="10" t="str">
@@ -8825,6 +9022,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT33" s="100"/>
+      <x:c r="DU33" s="106"/>
+      <x:c r="DV33" s="106"/>
+      <x:c r="DW33" s="106"/>
     </x:row>
     <x:row r="34" ht="25" customHeight="1">
       <x:c r="A34" s="10" t="str">
@@ -8987,6 +9187,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT34" s="100"/>
+      <x:c r="DU34" s="106"/>
+      <x:c r="DV34" s="106"/>
+      <x:c r="DW34" s="106"/>
     </x:row>
     <x:row r="35" ht="25" customHeight="1">
       <x:c r="A35" s="10" t="str">
@@ -9149,6 +9352,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT35" s="100"/>
+      <x:c r="DU35" s="106"/>
+      <x:c r="DV35" s="106"/>
+      <x:c r="DW35" s="106"/>
     </x:row>
     <x:row r="36" ht="25" customHeight="1">
       <x:c r="A36" s="10" t="str">
@@ -9311,6 +9517,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT36" s="100"/>
+      <x:c r="DU36" s="106"/>
+      <x:c r="DV36" s="106"/>
+      <x:c r="DW36" s="106"/>
     </x:row>
     <x:row r="37" ht="25" customHeight="1">
       <x:c r="A37" s="10" t="str">
@@ -9473,6 +9682,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT37" s="100"/>
+      <x:c r="DU37" s="106"/>
+      <x:c r="DV37" s="106"/>
+      <x:c r="DW37" s="106"/>
     </x:row>
     <x:row r="38" ht="25" customHeight="1">
       <x:c r="A38" s="10" t="str">
@@ -9635,6 +9847,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT38" s="100"/>
+      <x:c r="DU38" s="106"/>
+      <x:c r="DV38" s="106"/>
+      <x:c r="DW38" s="106"/>
     </x:row>
     <x:row r="39" ht="25" customHeight="1">
       <x:c r="A39" s="10" t="str">
@@ -9797,6 +10012,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="DT39" s="100"/>
+      <x:c r="DU39" s="106"/>
+      <x:c r="DV39" s="106"/>
+      <x:c r="DW39" s="106"/>
     </x:row>
     <x:row r="40" ht="25" customHeight="1">
       <x:c r="A40" s="93" t="str">
@@ -10007,7 +10225,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="BS40" s="90" t="str">
-        <x:v>その場</x:v>
+        <x:v>爆発</x:v>
       </x:c>
       <x:c r="BT40" s="95" t="n">
         <x:v>8</x:v>
@@ -10167,6 +10385,15 @@
       </x:c>
       <x:c r="DT40" s="100" t="n">
         <x:v>3</x:v>
+      </x:c>
+      <x:c r="DU40" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV40" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW40" s="106" t="n">
+        <x:v>0.1</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="25" customHeight="1">
@@ -10539,6 +10766,15 @@
       <x:c r="DT41" s="100" t="n">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="DU41" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV41" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW41" s="106" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="25" customHeight="1">
       <x:c r="A42" s="93" t="str">
@@ -10909,6 +11145,15 @@
       </x:c>
       <x:c r="DT42" s="100" t="n">
         <x:v>2</x:v>
+      </x:c>
+      <x:c r="DU42" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV42" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW42" s="106" t="n">
+        <x:v>0.1</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="25" customHeight="1">
@@ -11280,6 +11525,15 @@
       </x:c>
       <x:c r="DT43" s="100" t="n">
         <x:v>4</x:v>
+      </x:c>
+      <x:c r="DU43" s="106" t="str">
+        <x:v>有効</x:v>
+      </x:c>
+      <x:c r="DV43" s="106" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="DW43" s="106" t="n">
+        <x:v>0.1</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="25" customHeight="1">
@@ -11367,6 +11621,9 @@
       <x:c r="DR44" s="88"/>
       <x:c r="DS44" s="88"/>
       <x:c r="DT44" s="100"/>
+      <x:c r="DU44" s="106"/>
+      <x:c r="DV44" s="106"/>
+      <x:c r="DW44" s="106"/>
     </x:row>
     <x:row r="45" ht="25" customHeight="1">
       <x:c r="A45" s="10"/>
@@ -11453,6 +11710,9 @@
       <x:c r="DR45" s="88"/>
       <x:c r="DS45" s="88"/>
       <x:c r="DT45" s="100"/>
+      <x:c r="DU45" s="106"/>
+      <x:c r="DV45" s="106"/>
+      <x:c r="DW45" s="106"/>
     </x:row>
     <x:row r="46" ht="25" customHeight="1">
       <x:c r="A46" s="10"/>
@@ -11539,6 +11799,9 @@
       <x:c r="DR46" s="88"/>
       <x:c r="DS46" s="88"/>
       <x:c r="DT46" s="100"/>
+      <x:c r="DU46" s="106"/>
+      <x:c r="DV46" s="106"/>
+      <x:c r="DW46" s="106"/>
     </x:row>
     <x:row r="47" ht="25" customHeight="1">
       <x:c r="A47" s="10"/>
@@ -11625,6 +11888,9 @@
       <x:c r="DR47" s="88"/>
       <x:c r="DS47" s="88"/>
       <x:c r="DT47" s="100"/>
+      <x:c r="DU47" s="106"/>
+      <x:c r="DV47" s="106"/>
+      <x:c r="DW47" s="106"/>
     </x:row>
     <x:row r="48" ht="25" customHeight="1">
       <x:c r="A48" s="10"/>
@@ -11711,6 +11977,9 @@
       <x:c r="DR48" s="88"/>
       <x:c r="DS48" s="88"/>
       <x:c r="DT48" s="100"/>
+      <x:c r="DU48" s="106"/>
+      <x:c r="DV48" s="106"/>
+      <x:c r="DW48" s="106"/>
     </x:row>
     <x:row r="49" ht="25" customHeight="1">
       <x:c r="A49" s="10"/>
@@ -11797,6 +12066,9 @@
       <x:c r="DR49" s="88"/>
       <x:c r="DS49" s="88"/>
       <x:c r="DT49" s="100"/>
+      <x:c r="DU49" s="106"/>
+      <x:c r="DV49" s="106"/>
+      <x:c r="DW49" s="106"/>
     </x:row>
     <x:row r="50" ht="25" customHeight="1">
       <x:c r="A50" s="10"/>
@@ -11883,6 +12155,9 @@
       <x:c r="DR50" s="88"/>
       <x:c r="DS50" s="88"/>
       <x:c r="DT50" s="100"/>
+      <x:c r="DU50" s="106"/>
+      <x:c r="DV50" s="106"/>
+      <x:c r="DW50" s="106"/>
     </x:row>
     <x:row r="51" ht="25" customHeight="1">
       <x:c r="A51" s="10"/>
@@ -11969,6 +12244,9 @@
       <x:c r="DR51" s="88"/>
       <x:c r="DS51" s="88"/>
       <x:c r="DT51" s="100"/>
+      <x:c r="DU51" s="106"/>
+      <x:c r="DV51" s="106"/>
+      <x:c r="DW51" s="106"/>
     </x:row>
     <x:row r="52" ht="25" customHeight="1">
       <x:c r="A52" s="10"/>
@@ -12055,6 +12333,9 @@
       <x:c r="DR52" s="88"/>
       <x:c r="DS52" s="88"/>
       <x:c r="DT52" s="100"/>
+      <x:c r="DU52" s="106"/>
+      <x:c r="DV52" s="106"/>
+      <x:c r="DW52" s="106"/>
     </x:row>
     <x:row r="53" ht="25" customHeight="1">
       <x:c r="A53" s="10"/>
@@ -12141,6 +12422,9 @@
       <x:c r="DR53" s="88"/>
       <x:c r="DS53" s="88"/>
       <x:c r="DT53" s="100"/>
+      <x:c r="DU53" s="106"/>
+      <x:c r="DV53" s="106"/>
+      <x:c r="DW53" s="106"/>
     </x:row>
     <x:row r="54" ht="25" customHeight="1">
       <x:c r="A54" s="10"/>
@@ -12227,6 +12511,9 @@
       <x:c r="DR54" s="88"/>
       <x:c r="DS54" s="88"/>
       <x:c r="DT54" s="100"/>
+      <x:c r="DU54" s="106"/>
+      <x:c r="DV54" s="106"/>
+      <x:c r="DW54" s="106"/>
     </x:row>
     <x:row r="55" ht="25" customHeight="1">
       <x:c r="A55" s="10"/>
@@ -12313,6 +12600,9 @@
       <x:c r="DR55" s="88"/>
       <x:c r="DS55" s="88"/>
       <x:c r="DT55" s="100"/>
+      <x:c r="DU55" s="106"/>
+      <x:c r="DV55" s="106"/>
+      <x:c r="DW55" s="106"/>
     </x:row>
     <x:row r="56" ht="25" customHeight="1">
       <x:c r="A56" s="10"/>
@@ -12399,6 +12689,9 @@
       <x:c r="DR56" s="88"/>
       <x:c r="DS56" s="88"/>
       <x:c r="DT56" s="100"/>
+      <x:c r="DU56" s="106"/>
+      <x:c r="DV56" s="106"/>
+      <x:c r="DW56" s="106"/>
     </x:row>
     <x:row r="57" ht="25" customHeight="1">
       <x:c r="A57" s="10"/>
@@ -12485,6 +12778,9 @@
       <x:c r="DR57" s="88"/>
       <x:c r="DS57" s="88"/>
       <x:c r="DT57" s="100"/>
+      <x:c r="DU57" s="106"/>
+      <x:c r="DV57" s="106"/>
+      <x:c r="DW57" s="106"/>
     </x:row>
     <x:row r="58" ht="25" customHeight="1">
       <x:c r="A58" s="10"/>
@@ -12571,6 +12867,9 @@
       <x:c r="DR58" s="88"/>
       <x:c r="DS58" s="88"/>
       <x:c r="DT58" s="100"/>
+      <x:c r="DU58" s="106"/>
+      <x:c r="DV58" s="106"/>
+      <x:c r="DW58" s="106"/>
     </x:row>
     <x:row r="59" ht="25" customHeight="1">
       <x:c r="A59" s="10"/>
@@ -12657,6 +12956,9 @@
       <x:c r="DR59" s="88"/>
       <x:c r="DS59" s="88"/>
       <x:c r="DT59" s="100"/>
+      <x:c r="DU59" s="106"/>
+      <x:c r="DV59" s="106"/>
+      <x:c r="DW59" s="106"/>
     </x:row>
     <x:row r="60" ht="25" customHeight="1">
       <x:c r="A60" s="10"/>
@@ -12743,6 +13045,9 @@
       <x:c r="DR60" s="88"/>
       <x:c r="DS60" s="88"/>
       <x:c r="DT60" s="100"/>
+      <x:c r="DU60" s="106"/>
+      <x:c r="DV60" s="106"/>
+      <x:c r="DW60" s="106"/>
     </x:row>
     <x:row r="61" ht="25" customHeight="1">
       <x:c r="A61" s="10"/>
@@ -12829,6 +13134,9 @@
       <x:c r="DR61" s="88"/>
       <x:c r="DS61" s="88"/>
       <x:c r="DT61" s="100"/>
+      <x:c r="DU61" s="106"/>
+      <x:c r="DV61" s="106"/>
+      <x:c r="DW61" s="106"/>
     </x:row>
     <x:row r="62" ht="25" customHeight="1">
       <x:c r="A62" s="10"/>
@@ -12915,6 +13223,9 @@
       <x:c r="DR62" s="88"/>
       <x:c r="DS62" s="88"/>
       <x:c r="DT62" s="100"/>
+      <x:c r="DU62" s="106"/>
+      <x:c r="DV62" s="106"/>
+      <x:c r="DW62" s="106"/>
     </x:row>
     <x:row r="63" ht="25" customHeight="1">
       <x:c r="A63" s="10"/>
@@ -13001,6 +13312,9 @@
       <x:c r="DR63" s="88"/>
       <x:c r="DS63" s="88"/>
       <x:c r="DT63" s="100"/>
+      <x:c r="DU63" s="106"/>
+      <x:c r="DV63" s="106"/>
+      <x:c r="DW63" s="106"/>
     </x:row>
     <x:row r="64" ht="25" customHeight="1">
       <x:c r="A64" s="10"/>
@@ -13087,6 +13401,9 @@
       <x:c r="DR64" s="88"/>
       <x:c r="DS64" s="88"/>
       <x:c r="DT64" s="100"/>
+      <x:c r="DU64" s="106"/>
+      <x:c r="DV64" s="106"/>
+      <x:c r="DW64" s="106"/>
     </x:row>
     <x:row r="65" ht="25" customHeight="1">
       <x:c r="A65" s="10"/>
@@ -13173,6 +13490,9 @@
       <x:c r="DR65" s="88"/>
       <x:c r="DS65" s="88"/>
       <x:c r="DT65" s="100"/>
+      <x:c r="DU65" s="106"/>
+      <x:c r="DV65" s="106"/>
+      <x:c r="DW65" s="106"/>
     </x:row>
     <x:row r="66" ht="25" customHeight="1">
       <x:c r="A66" s="10"/>
@@ -13259,6 +13579,9 @@
       <x:c r="DR66" s="88"/>
       <x:c r="DS66" s="88"/>
       <x:c r="DT66" s="100"/>
+      <x:c r="DU66" s="106"/>
+      <x:c r="DV66" s="106"/>
+      <x:c r="DW66" s="106"/>
     </x:row>
     <x:row r="67" ht="25" customHeight="1">
       <x:c r="A67" s="10"/>
@@ -13345,6 +13668,9 @@
       <x:c r="DR67" s="88"/>
       <x:c r="DS67" s="88"/>
       <x:c r="DT67" s="100"/>
+      <x:c r="DU67" s="106"/>
+      <x:c r="DV67" s="106"/>
+      <x:c r="DW67" s="106"/>
     </x:row>
     <x:row r="68" ht="25" customHeight="1">
       <x:c r="A68" s="10"/>
@@ -13431,6 +13757,9 @@
       <x:c r="DR68" s="88"/>
       <x:c r="DS68" s="88"/>
       <x:c r="DT68" s="100"/>
+      <x:c r="DU68" s="106"/>
+      <x:c r="DV68" s="106"/>
+      <x:c r="DW68" s="106"/>
     </x:row>
     <x:row r="69" ht="25" customHeight="1">
       <x:c r="A69" s="10"/>
@@ -13517,6 +13846,9 @@
       <x:c r="DR69" s="88"/>
       <x:c r="DS69" s="88"/>
       <x:c r="DT69" s="100"/>
+      <x:c r="DU69" s="106"/>
+      <x:c r="DV69" s="106"/>
+      <x:c r="DW69" s="106"/>
     </x:row>
     <x:row r="70" ht="25" customHeight="1">
       <x:c r="A70" s="10"/>
@@ -13603,6 +13935,9 @@
       <x:c r="DR70" s="88"/>
       <x:c r="DS70" s="88"/>
       <x:c r="DT70" s="100"/>
+      <x:c r="DU70" s="106"/>
+      <x:c r="DV70" s="106"/>
+      <x:c r="DW70" s="106"/>
     </x:row>
     <x:row r="71" ht="25" customHeight="1">
       <x:c r="A71" s="10"/>
@@ -13689,6 +14024,9 @@
       <x:c r="DR71" s="88"/>
       <x:c r="DS71" s="88"/>
       <x:c r="DT71" s="100"/>
+      <x:c r="DU71" s="106"/>
+      <x:c r="DV71" s="106"/>
+      <x:c r="DW71" s="106"/>
     </x:row>
     <x:row r="72" ht="25" customHeight="1">
       <x:c r="A72" s="10"/>
@@ -13775,6 +14113,9 @@
       <x:c r="DR72" s="88"/>
       <x:c r="DS72" s="88"/>
       <x:c r="DT72" s="100"/>
+      <x:c r="DU72" s="106"/>
+      <x:c r="DV72" s="106"/>
+      <x:c r="DW72" s="106"/>
     </x:row>
     <x:row r="73" ht="25" customHeight="1">
       <x:c r="A73" s="10"/>
@@ -13861,6 +14202,9 @@
       <x:c r="DR73" s="88"/>
       <x:c r="DS73" s="88"/>
       <x:c r="DT73" s="100"/>
+      <x:c r="DU73" s="106"/>
+      <x:c r="DV73" s="106"/>
+      <x:c r="DW73" s="106"/>
     </x:row>
     <x:row r="74" ht="25" customHeight="1">
       <x:c r="A74" s="10"/>
@@ -13947,6 +14291,9 @@
       <x:c r="DR74" s="88"/>
       <x:c r="DS74" s="88"/>
       <x:c r="DT74" s="100"/>
+      <x:c r="DU74" s="106"/>
+      <x:c r="DV74" s="106"/>
+      <x:c r="DW74" s="106"/>
     </x:row>
     <x:row r="75" ht="25" customHeight="1">
       <x:c r="A75" s="10"/>
@@ -14033,6 +14380,9 @@
       <x:c r="DR75" s="88"/>
       <x:c r="DS75" s="88"/>
       <x:c r="DT75" s="100"/>
+      <x:c r="DU75" s="106"/>
+      <x:c r="DV75" s="106"/>
+      <x:c r="DW75" s="106"/>
     </x:row>
     <x:row r="76" ht="25" customHeight="1">
       <x:c r="A76" s="10"/>
@@ -14119,6 +14469,9 @@
       <x:c r="DR76" s="88"/>
       <x:c r="DS76" s="88"/>
       <x:c r="DT76" s="100"/>
+      <x:c r="DU76" s="106"/>
+      <x:c r="DV76" s="106"/>
+      <x:c r="DW76" s="106"/>
     </x:row>
     <x:row r="77" ht="25" customHeight="1">
       <x:c r="A77" s="10"/>
@@ -14205,6 +14558,9 @@
       <x:c r="DR77" s="88"/>
       <x:c r="DS77" s="88"/>
       <x:c r="DT77" s="100"/>
+      <x:c r="DU77" s="106"/>
+      <x:c r="DV77" s="106"/>
+      <x:c r="DW77" s="106"/>
     </x:row>
     <x:row r="78" ht="25" customHeight="1">
       <x:c r="A78" s="10"/>
@@ -14291,6 +14647,9 @@
       <x:c r="DR78" s="88"/>
       <x:c r="DS78" s="88"/>
       <x:c r="DT78" s="100"/>
+      <x:c r="DU78" s="106"/>
+      <x:c r="DV78" s="106"/>
+      <x:c r="DW78" s="106"/>
     </x:row>
     <x:row r="79" ht="25" customHeight="1">
       <x:c r="A79" s="10"/>
@@ -14377,6 +14736,9 @@
       <x:c r="DR79" s="88"/>
       <x:c r="DS79" s="88"/>
       <x:c r="DT79" s="100"/>
+      <x:c r="DU79" s="106"/>
+      <x:c r="DV79" s="106"/>
+      <x:c r="DW79" s="106"/>
     </x:row>
     <x:row r="80" ht="25" customHeight="1">
       <x:c r="A80" s="10"/>
@@ -14463,6 +14825,9 @@
       <x:c r="DR80" s="88"/>
       <x:c r="DS80" s="88"/>
       <x:c r="DT80" s="100"/>
+      <x:c r="DU80" s="106"/>
+      <x:c r="DV80" s="106"/>
+      <x:c r="DW80" s="106"/>
     </x:row>
     <x:row r="81" ht="25" customHeight="1">
       <x:c r="A81" s="10"/>
@@ -14549,6 +14914,9 @@
       <x:c r="DR81" s="88"/>
       <x:c r="DS81" s="88"/>
       <x:c r="DT81" s="100"/>
+      <x:c r="DU81" s="106"/>
+      <x:c r="DV81" s="106"/>
+      <x:c r="DW81" s="106"/>
     </x:row>
     <x:row r="82" ht="25" customHeight="1">
       <x:c r="A82" s="10"/>
@@ -14635,6 +15003,9 @@
       <x:c r="DR82" s="88"/>
       <x:c r="DS82" s="88"/>
       <x:c r="DT82" s="100"/>
+      <x:c r="DU82" s="106"/>
+      <x:c r="DV82" s="106"/>
+      <x:c r="DW82" s="106"/>
     </x:row>
     <x:row r="83" ht="25" customHeight="1">
       <x:c r="A83" s="10"/>
@@ -14721,6 +15092,9 @@
       <x:c r="DR83" s="88"/>
       <x:c r="DS83" s="88"/>
       <x:c r="DT83" s="100"/>
+      <x:c r="DU83" s="106"/>
+      <x:c r="DV83" s="106"/>
+      <x:c r="DW83" s="106"/>
     </x:row>
     <x:row r="84" ht="25" customHeight="1">
       <x:c r="A84" s="10"/>
@@ -14807,6 +15181,9 @@
       <x:c r="DR84" s="88"/>
       <x:c r="DS84" s="88"/>
       <x:c r="DT84" s="100"/>
+      <x:c r="DU84" s="106"/>
+      <x:c r="DV84" s="106"/>
+      <x:c r="DW84" s="106"/>
     </x:row>
     <x:row r="85" ht="25" customHeight="1">
       <x:c r="A85" s="10"/>
@@ -14893,6 +15270,9 @@
       <x:c r="DR85" s="88"/>
       <x:c r="DS85" s="88"/>
       <x:c r="DT85" s="100"/>
+      <x:c r="DU85" s="106"/>
+      <x:c r="DV85" s="106"/>
+      <x:c r="DW85" s="106"/>
     </x:row>
     <x:row r="86" ht="25" customHeight="1">
       <x:c r="A86" s="10"/>
@@ -14979,6 +15359,9 @@
       <x:c r="DR86" s="88"/>
       <x:c r="DS86" s="88"/>
       <x:c r="DT86" s="100"/>
+      <x:c r="DU86" s="106"/>
+      <x:c r="DV86" s="106"/>
+      <x:c r="DW86" s="106"/>
     </x:row>
     <x:row r="87" ht="25" customHeight="1">
       <x:c r="A87" s="10"/>
@@ -15065,6 +15448,9 @@
       <x:c r="DR87" s="88"/>
       <x:c r="DS87" s="88"/>
       <x:c r="DT87" s="100"/>
+      <x:c r="DU87" s="106"/>
+      <x:c r="DV87" s="106"/>
+      <x:c r="DW87" s="106"/>
     </x:row>
     <x:row r="88" ht="25" customHeight="1">
       <x:c r="A88" s="10"/>
@@ -15151,6 +15537,9 @@
       <x:c r="DR88" s="88"/>
       <x:c r="DS88" s="88"/>
       <x:c r="DT88" s="100"/>
+      <x:c r="DU88" s="106"/>
+      <x:c r="DV88" s="106"/>
+      <x:c r="DW88" s="106"/>
     </x:row>
     <x:row r="89" ht="25" customHeight="1">
       <x:c r="A89" s="10"/>
@@ -15237,6 +15626,9 @@
       <x:c r="DR89" s="88"/>
       <x:c r="DS89" s="88"/>
       <x:c r="DT89" s="100"/>
+      <x:c r="DU89" s="106"/>
+      <x:c r="DV89" s="106"/>
+      <x:c r="DW89" s="106"/>
     </x:row>
     <x:row r="90" ht="25" customHeight="1">
       <x:c r="A90" s="10"/>
@@ -15323,6 +15715,9 @@
       <x:c r="DR90" s="88"/>
       <x:c r="DS90" s="88"/>
       <x:c r="DT90" s="100"/>
+      <x:c r="DU90" s="106"/>
+      <x:c r="DV90" s="106"/>
+      <x:c r="DW90" s="106"/>
     </x:row>
     <x:row r="91" ht="25" customHeight="1">
       <x:c r="A91" s="10"/>
@@ -15409,6 +15804,9 @@
       <x:c r="DR91" s="88"/>
       <x:c r="DS91" s="88"/>
       <x:c r="DT91" s="100"/>
+      <x:c r="DU91" s="106"/>
+      <x:c r="DV91" s="106"/>
+      <x:c r="DW91" s="106"/>
     </x:row>
     <x:row r="92" ht="25" customHeight="1">
       <x:c r="A92" s="10"/>
@@ -15495,6 +15893,9 @@
       <x:c r="DR92" s="88"/>
       <x:c r="DS92" s="88"/>
       <x:c r="DT92" s="100"/>
+      <x:c r="DU92" s="106"/>
+      <x:c r="DV92" s="106"/>
+      <x:c r="DW92" s="106"/>
     </x:row>
     <x:row r="93" ht="25" customHeight="1">
       <x:c r="A93" s="10"/>
@@ -15581,6 +15982,9 @@
       <x:c r="DR93" s="88"/>
       <x:c r="DS93" s="88"/>
       <x:c r="DT93" s="100"/>
+      <x:c r="DU93" s="106"/>
+      <x:c r="DV93" s="106"/>
+      <x:c r="DW93" s="106"/>
     </x:row>
     <x:row r="94" ht="25" customHeight="1">
       <x:c r="A94" s="10"/>
@@ -15667,6 +16071,9 @@
       <x:c r="DR94" s="88"/>
       <x:c r="DS94" s="88"/>
       <x:c r="DT94" s="100"/>
+      <x:c r="DU94" s="106"/>
+      <x:c r="DV94" s="106"/>
+      <x:c r="DW94" s="106"/>
     </x:row>
     <x:row r="95" ht="25" customHeight="1">
       <x:c r="A95" s="10"/>
@@ -15753,6 +16160,9 @@
       <x:c r="DR95" s="88"/>
       <x:c r="DS95" s="88"/>
       <x:c r="DT95" s="100"/>
+      <x:c r="DU95" s="106"/>
+      <x:c r="DV95" s="106"/>
+      <x:c r="DW95" s="106"/>
     </x:row>
     <x:row r="96" ht="25" customHeight="1">
       <x:c r="A96" s="10"/>
@@ -15839,6 +16249,9 @@
       <x:c r="DR96" s="88"/>
       <x:c r="DS96" s="88"/>
       <x:c r="DT96" s="100"/>
+      <x:c r="DU96" s="106"/>
+      <x:c r="DV96" s="106"/>
+      <x:c r="DW96" s="106"/>
     </x:row>
     <x:row r="97" ht="25" customHeight="1">
       <x:c r="A97" s="10"/>
@@ -15925,6 +16338,9 @@
       <x:c r="DR97" s="88"/>
       <x:c r="DS97" s="88"/>
       <x:c r="DT97" s="100"/>
+      <x:c r="DU97" s="106"/>
+      <x:c r="DV97" s="106"/>
+      <x:c r="DW97" s="106"/>
     </x:row>
     <x:row r="98" ht="25" customHeight="1">
       <x:c r="A98" s="10"/>
@@ -16011,6 +16427,9 @@
       <x:c r="DR98" s="88"/>
       <x:c r="DS98" s="88"/>
       <x:c r="DT98" s="100"/>
+      <x:c r="DU98" s="106"/>
+      <x:c r="DV98" s="106"/>
+      <x:c r="DW98" s="106"/>
     </x:row>
     <x:row r="99" ht="25" customHeight="1">
       <x:c r="A99" s="10"/>
@@ -16097,6 +16516,9 @@
       <x:c r="DR99" s="88"/>
       <x:c r="DS99" s="88"/>
       <x:c r="DT99" s="100"/>
+      <x:c r="DU99" s="106"/>
+      <x:c r="DV99" s="106"/>
+      <x:c r="DW99" s="106"/>
     </x:row>
     <x:row r="100" ht="25" customHeight="1">
       <x:c r="A100" s="10"/>
@@ -16183,6 +16605,9 @@
       <x:c r="DR100" s="88"/>
       <x:c r="DS100" s="88"/>
       <x:c r="DT100" s="100"/>
+      <x:c r="DU100" s="106"/>
+      <x:c r="DV100" s="106"/>
+      <x:c r="DW100" s="106"/>
     </x:row>
     <x:row r="101" ht="25" customHeight="1">
       <x:c r="A101" s="10"/>
@@ -16269,6 +16694,9 @@
       <x:c r="DR101" s="88"/>
       <x:c r="DS101" s="88"/>
       <x:c r="DT101" s="100"/>
+      <x:c r="DU101" s="106"/>
+      <x:c r="DV101" s="106"/>
+      <x:c r="DW101" s="106"/>
     </x:row>
     <x:row r="102" ht="25" customHeight="1">
       <x:c r="A102" s="10"/>
@@ -16355,6 +16783,9 @@
       <x:c r="DR102" s="88"/>
       <x:c r="DS102" s="88"/>
       <x:c r="DT102" s="100"/>
+      <x:c r="DU102" s="106"/>
+      <x:c r="DV102" s="106"/>
+      <x:c r="DW102" s="106"/>
     </x:row>
     <x:row r="103" ht="25" customHeight="1">
       <x:c r="A103" s="10"/>
@@ -16441,6 +16872,9 @@
       <x:c r="DR103" s="88"/>
       <x:c r="DS103" s="88"/>
       <x:c r="DT103" s="100"/>
+      <x:c r="DU103" s="106"/>
+      <x:c r="DV103" s="106"/>
+      <x:c r="DW103" s="106"/>
     </x:row>
     <x:row r="104" ht="25" customHeight="1">
       <x:c r="A104" s="10"/>
@@ -16527,6 +16961,9 @@
       <x:c r="DR104" s="88"/>
       <x:c r="DS104" s="88"/>
       <x:c r="DT104" s="100"/>
+      <x:c r="DU104" s="106"/>
+      <x:c r="DV104" s="106"/>
+      <x:c r="DW104" s="106"/>
     </x:row>
     <x:row r="105" ht="25" customHeight="1">
       <x:c r="A105" s="10"/>
@@ -16613,6 +17050,9 @@
       <x:c r="DR105" s="88"/>
       <x:c r="DS105" s="88"/>
       <x:c r="DT105" s="100"/>
+      <x:c r="DU105" s="106"/>
+      <x:c r="DV105" s="106"/>
+      <x:c r="DW105" s="106"/>
     </x:row>
     <x:row r="106" ht="25" customHeight="1">
       <x:c r="A106" s="10"/>
@@ -16699,6 +17139,9 @@
       <x:c r="DR106" s="88"/>
       <x:c r="DS106" s="88"/>
       <x:c r="DT106" s="100"/>
+      <x:c r="DU106" s="106"/>
+      <x:c r="DV106" s="106"/>
+      <x:c r="DW106" s="106"/>
     </x:row>
     <x:row r="107" ht="25" customHeight="1">
       <x:c r="A107" s="10"/>
@@ -16785,6 +17228,9 @@
       <x:c r="DR107" s="88"/>
       <x:c r="DS107" s="88"/>
       <x:c r="DT107" s="100"/>
+      <x:c r="DU107" s="106"/>
+      <x:c r="DV107" s="106"/>
+      <x:c r="DW107" s="106"/>
     </x:row>
     <x:row r="108" ht="25" customHeight="1">
       <x:c r="A108" s="10"/>
@@ -16871,6 +17317,9 @@
       <x:c r="DR108" s="88"/>
       <x:c r="DS108" s="88"/>
       <x:c r="DT108" s="100"/>
+      <x:c r="DU108" s="106"/>
+      <x:c r="DV108" s="106"/>
+      <x:c r="DW108" s="106"/>
     </x:row>
     <x:row r="109" ht="25" customHeight="1">
       <x:c r="A109" s="10"/>
@@ -16957,6 +17406,9 @@
       <x:c r="DR109" s="88"/>
       <x:c r="DS109" s="88"/>
       <x:c r="DT109" s="100"/>
+      <x:c r="DU109" s="106"/>
+      <x:c r="DV109" s="106"/>
+      <x:c r="DW109" s="106"/>
     </x:row>
     <x:row r="110" ht="25" customHeight="1">
       <x:c r="A110" s="10"/>
@@ -17043,6 +17495,9 @@
       <x:c r="DR110" s="88"/>
       <x:c r="DS110" s="88"/>
       <x:c r="DT110" s="100"/>
+      <x:c r="DU110" s="106"/>
+      <x:c r="DV110" s="106"/>
+      <x:c r="DW110" s="106"/>
     </x:row>
     <x:row r="111" ht="25" customHeight="1">
       <x:c r="A111" s="10"/>
@@ -17129,6 +17584,9 @@
       <x:c r="DR111" s="88"/>
       <x:c r="DS111" s="88"/>
       <x:c r="DT111" s="100"/>
+      <x:c r="DU111" s="106"/>
+      <x:c r="DV111" s="106"/>
+      <x:c r="DW111" s="106"/>
     </x:row>
     <x:row r="112" ht="25" customHeight="1">
       <x:c r="A112" s="10"/>
@@ -17215,6 +17673,9 @@
       <x:c r="DR112" s="88"/>
       <x:c r="DS112" s="88"/>
       <x:c r="DT112" s="100"/>
+      <x:c r="DU112" s="106"/>
+      <x:c r="DV112" s="106"/>
+      <x:c r="DW112" s="106"/>
     </x:row>
     <x:row r="113" ht="25" customHeight="1">
       <x:c r="A113" s="10"/>
@@ -17301,6 +17762,9 @@
       <x:c r="DR113" s="88"/>
       <x:c r="DS113" s="88"/>
       <x:c r="DT113" s="100"/>
+      <x:c r="DU113" s="106"/>
+      <x:c r="DV113" s="106"/>
+      <x:c r="DW113" s="106"/>
     </x:row>
     <x:row r="114" ht="25" customHeight="1">
       <x:c r="A114" s="10"/>
@@ -17387,6 +17851,9 @@
       <x:c r="DR114" s="88"/>
       <x:c r="DS114" s="88"/>
       <x:c r="DT114" s="100"/>
+      <x:c r="DU114" s="106"/>
+      <x:c r="DV114" s="106"/>
+      <x:c r="DW114" s="106"/>
     </x:row>
     <x:row r="115" ht="25" customHeight="1">
       <x:c r="A115" s="10"/>
@@ -17473,6 +17940,9 @@
       <x:c r="DR115" s="88"/>
       <x:c r="DS115" s="88"/>
       <x:c r="DT115" s="100"/>
+      <x:c r="DU115" s="106"/>
+      <x:c r="DV115" s="106"/>
+      <x:c r="DW115" s="106"/>
     </x:row>
     <x:row r="116" ht="25" customHeight="1">
       <x:c r="A116" s="10"/>
@@ -17559,6 +18029,9 @@
       <x:c r="DR116" s="88"/>
       <x:c r="DS116" s="88"/>
       <x:c r="DT116" s="100"/>
+      <x:c r="DU116" s="106"/>
+      <x:c r="DV116" s="106"/>
+      <x:c r="DW116" s="106"/>
     </x:row>
     <x:row r="117" ht="25" customHeight="1">
       <x:c r="A117" s="10"/>
@@ -17645,6 +18118,9 @@
       <x:c r="DR117" s="88"/>
       <x:c r="DS117" s="88"/>
       <x:c r="DT117" s="100"/>
+      <x:c r="DU117" s="106"/>
+      <x:c r="DV117" s="106"/>
+      <x:c r="DW117" s="106"/>
     </x:row>
     <x:row r="118" ht="25" customHeight="1">
       <x:c r="A118" s="10"/>
@@ -17731,6 +18207,9 @@
       <x:c r="DR118" s="88"/>
       <x:c r="DS118" s="88"/>
       <x:c r="DT118" s="100"/>
+      <x:c r="DU118" s="106"/>
+      <x:c r="DV118" s="106"/>
+      <x:c r="DW118" s="106"/>
     </x:row>
     <x:row r="119" ht="25" customHeight="1">
       <x:c r="A119" s="10"/>
@@ -17817,6 +18296,9 @@
       <x:c r="DR119" s="88"/>
       <x:c r="DS119" s="88"/>
       <x:c r="DT119" s="100"/>
+      <x:c r="DU119" s="106"/>
+      <x:c r="DV119" s="106"/>
+      <x:c r="DW119" s="106"/>
     </x:row>
     <x:row r="120" ht="25" customHeight="1">
       <x:c r="A120" s="10"/>
@@ -17903,6 +18385,9 @@
       <x:c r="DR120" s="88"/>
       <x:c r="DS120" s="88"/>
       <x:c r="DT120" s="100"/>
+      <x:c r="DU120" s="106"/>
+      <x:c r="DV120" s="106"/>
+      <x:c r="DW120" s="106"/>
     </x:row>
     <x:row r="121" ht="25" customHeight="1">
       <x:c r="A121" s="10"/>
@@ -17989,6 +18474,9 @@
       <x:c r="DR121" s="88"/>
       <x:c r="DS121" s="88"/>
       <x:c r="DT121" s="100"/>
+      <x:c r="DU121" s="106"/>
+      <x:c r="DV121" s="106"/>
+      <x:c r="DW121" s="106"/>
     </x:row>
     <x:row r="122" ht="25" customHeight="1">
       <x:c r="A122" s="10"/>
@@ -18075,6 +18563,9 @@
       <x:c r="DR122" s="88"/>
       <x:c r="DS122" s="88"/>
       <x:c r="DT122" s="100"/>
+      <x:c r="DU122" s="106"/>
+      <x:c r="DV122" s="106"/>
+      <x:c r="DW122" s="106"/>
     </x:row>
     <x:row r="123" ht="25" customHeight="1">
       <x:c r="A123" s="10"/>
@@ -18161,6 +18652,9 @@
       <x:c r="DR123" s="88"/>
       <x:c r="DS123" s="88"/>
       <x:c r="DT123" s="100"/>
+      <x:c r="DU123" s="106"/>
+      <x:c r="DV123" s="106"/>
+      <x:c r="DW123" s="106"/>
     </x:row>
     <x:row r="124" ht="25" customHeight="1">
       <x:c r="A124" s="10"/>
@@ -18247,6 +18741,9 @@
       <x:c r="DR124" s="88"/>
       <x:c r="DS124" s="88"/>
       <x:c r="DT124" s="100"/>
+      <x:c r="DU124" s="106"/>
+      <x:c r="DV124" s="106"/>
+      <x:c r="DW124" s="106"/>
     </x:row>
     <x:row r="125" ht="25" customHeight="1">
       <x:c r="A125" s="10"/>
@@ -18333,6 +18830,9 @@
       <x:c r="DR125" s="88"/>
       <x:c r="DS125" s="88"/>
       <x:c r="DT125" s="100"/>
+      <x:c r="DU125" s="106"/>
+      <x:c r="DV125" s="106"/>
+      <x:c r="DW125" s="106"/>
     </x:row>
     <x:row r="126" ht="25" customHeight="1">
       <x:c r="A126" s="10"/>
@@ -18419,6 +18919,9 @@
       <x:c r="DR126" s="88"/>
       <x:c r="DS126" s="88"/>
       <x:c r="DT126" s="100"/>
+      <x:c r="DU126" s="106"/>
+      <x:c r="DV126" s="106"/>
+      <x:c r="DW126" s="106"/>
     </x:row>
     <x:row r="127" ht="25" customHeight="1">
       <x:c r="A127" s="10"/>
@@ -18505,6 +19008,9 @@
       <x:c r="DR127" s="88"/>
       <x:c r="DS127" s="88"/>
       <x:c r="DT127" s="100"/>
+      <x:c r="DU127" s="106"/>
+      <x:c r="DV127" s="106"/>
+      <x:c r="DW127" s="106"/>
     </x:row>
     <x:row r="128" ht="25" customHeight="1">
       <x:c r="A128" s="10"/>
@@ -18591,6 +19097,9 @@
       <x:c r="DR128" s="88"/>
       <x:c r="DS128" s="88"/>
       <x:c r="DT128" s="100"/>
+      <x:c r="DU128" s="106"/>
+      <x:c r="DV128" s="106"/>
+      <x:c r="DW128" s="106"/>
     </x:row>
     <x:row r="129" ht="25" customHeight="1">
       <x:c r="A129" s="10"/>
@@ -18677,6 +19186,9 @@
       <x:c r="DR129" s="88"/>
       <x:c r="DS129" s="88"/>
       <x:c r="DT129" s="100"/>
+      <x:c r="DU129" s="106"/>
+      <x:c r="DV129" s="106"/>
+      <x:c r="DW129" s="106"/>
     </x:row>
     <x:row r="130" ht="25" customHeight="1">
       <x:c r="A130" s="10"/>
@@ -18763,6 +19275,9 @@
       <x:c r="DR130" s="88"/>
       <x:c r="DS130" s="88"/>
       <x:c r="DT130" s="100"/>
+      <x:c r="DU130" s="106"/>
+      <x:c r="DV130" s="106"/>
+      <x:c r="DW130" s="106"/>
     </x:row>
     <x:row r="131" ht="25" customHeight="1">
       <x:c r="A131" s="10"/>
@@ -18849,6 +19364,9 @@
       <x:c r="DR131" s="88"/>
       <x:c r="DS131" s="88"/>
       <x:c r="DT131" s="100"/>
+      <x:c r="DU131" s="106"/>
+      <x:c r="DV131" s="106"/>
+      <x:c r="DW131" s="106"/>
     </x:row>
     <x:row r="132" ht="25" customHeight="1">
       <x:c r="A132" s="10"/>
@@ -18935,6 +19453,9 @@
       <x:c r="DR132" s="88"/>
       <x:c r="DS132" s="88"/>
       <x:c r="DT132" s="100"/>
+      <x:c r="DU132" s="106"/>
+      <x:c r="DV132" s="106"/>
+      <x:c r="DW132" s="106"/>
     </x:row>
     <x:row r="133" ht="25" customHeight="1">
       <x:c r="A133" s="10"/>
@@ -19021,6 +19542,9 @@
       <x:c r="DR133" s="88"/>
       <x:c r="DS133" s="88"/>
       <x:c r="DT133" s="100"/>
+      <x:c r="DU133" s="106"/>
+      <x:c r="DV133" s="106"/>
+      <x:c r="DW133" s="106"/>
     </x:row>
     <x:row r="134" ht="25" customHeight="1">
       <x:c r="A134" s="10"/>
@@ -19107,6 +19631,9 @@
       <x:c r="DR134" s="88"/>
       <x:c r="DS134" s="88"/>
       <x:c r="DT134" s="100"/>
+      <x:c r="DU134" s="106"/>
+      <x:c r="DV134" s="106"/>
+      <x:c r="DW134" s="106"/>
     </x:row>
     <x:row r="135" ht="25" customHeight="1">
       <x:c r="A135" s="10"/>
@@ -19193,6 +19720,9 @@
       <x:c r="DR135" s="88"/>
       <x:c r="DS135" s="88"/>
       <x:c r="DT135" s="100"/>
+      <x:c r="DU135" s="106"/>
+      <x:c r="DV135" s="106"/>
+      <x:c r="DW135" s="106"/>
     </x:row>
     <x:row r="136" ht="25" customHeight="1">
       <x:c r="A136" s="10"/>
@@ -19279,6 +19809,9 @@
       <x:c r="DR136" s="88"/>
       <x:c r="DS136" s="88"/>
       <x:c r="DT136" s="100"/>
+      <x:c r="DU136" s="106"/>
+      <x:c r="DV136" s="106"/>
+      <x:c r="DW136" s="106"/>
     </x:row>
     <x:row r="137" ht="25" customHeight="1">
       <x:c r="A137" s="10"/>
@@ -19365,6 +19898,9 @@
       <x:c r="DR137" s="88"/>
       <x:c r="DS137" s="88"/>
       <x:c r="DT137" s="100"/>
+      <x:c r="DU137" s="106"/>
+      <x:c r="DV137" s="106"/>
+      <x:c r="DW137" s="106"/>
     </x:row>
     <x:row r="138" ht="25" customHeight="1">
       <x:c r="A138" s="10"/>
@@ -19451,6 +19987,9 @@
       <x:c r="DR138" s="88"/>
       <x:c r="DS138" s="88"/>
       <x:c r="DT138" s="100"/>
+      <x:c r="DU138" s="106"/>
+      <x:c r="DV138" s="106"/>
+      <x:c r="DW138" s="106"/>
     </x:row>
     <x:row r="139" ht="25" customHeight="1">
       <x:c r="A139" s="10"/>
@@ -19537,6 +20076,9 @@
       <x:c r="DR139" s="88"/>
       <x:c r="DS139" s="88"/>
       <x:c r="DT139" s="100"/>
+      <x:c r="DU139" s="106"/>
+      <x:c r="DV139" s="106"/>
+      <x:c r="DW139" s="106"/>
     </x:row>
     <x:row r="140" ht="25" customHeight="1">
       <x:c r="A140" s="10"/>
@@ -19623,6 +20165,9 @@
       <x:c r="DR140" s="88"/>
       <x:c r="DS140" s="88"/>
       <x:c r="DT140" s="100"/>
+      <x:c r="DU140" s="106"/>
+      <x:c r="DV140" s="106"/>
+      <x:c r="DW140" s="106"/>
     </x:row>
     <x:row r="141" ht="25" customHeight="1">
       <x:c r="A141" s="10"/>
@@ -19709,6 +20254,9 @@
       <x:c r="DR141" s="88"/>
       <x:c r="DS141" s="88"/>
       <x:c r="DT141" s="100"/>
+      <x:c r="DU141" s="106"/>
+      <x:c r="DV141" s="106"/>
+      <x:c r="DW141" s="106"/>
     </x:row>
     <x:row r="142" ht="25" customHeight="1">
       <x:c r="A142" s="10"/>
@@ -19795,6 +20343,9 @@
       <x:c r="DR142" s="88"/>
       <x:c r="DS142" s="88"/>
       <x:c r="DT142" s="100"/>
+      <x:c r="DU142" s="106"/>
+      <x:c r="DV142" s="106"/>
+      <x:c r="DW142" s="106"/>
     </x:row>
     <x:row r="143" ht="25" customHeight="1">
       <x:c r="A143" s="10"/>
@@ -19881,6 +20432,9 @@
       <x:c r="DR143" s="88"/>
       <x:c r="DS143" s="88"/>
       <x:c r="DT143" s="100"/>
+      <x:c r="DU143" s="106"/>
+      <x:c r="DV143" s="106"/>
+      <x:c r="DW143" s="106"/>
     </x:row>
     <x:row r="144" ht="25" customHeight="1">
       <x:c r="A144" s="10"/>
@@ -19967,6 +20521,9 @@
       <x:c r="DR144" s="88"/>
       <x:c r="DS144" s="88"/>
       <x:c r="DT144" s="100"/>
+      <x:c r="DU144" s="106"/>
+      <x:c r="DV144" s="106"/>
+      <x:c r="DW144" s="106"/>
     </x:row>
     <x:row r="145" ht="25" customHeight="1">
       <x:c r="A145" s="10"/>
@@ -20053,6 +20610,9 @@
       <x:c r="DR145" s="88"/>
       <x:c r="DS145" s="88"/>
       <x:c r="DT145" s="100"/>
+      <x:c r="DU145" s="106"/>
+      <x:c r="DV145" s="106"/>
+      <x:c r="DW145" s="106"/>
     </x:row>
     <x:row r="146" ht="25" customHeight="1">
       <x:c r="A146" s="10"/>
@@ -20139,6 +20699,9 @@
       <x:c r="DR146" s="88"/>
       <x:c r="DS146" s="88"/>
       <x:c r="DT146" s="100"/>
+      <x:c r="DU146" s="106"/>
+      <x:c r="DV146" s="106"/>
+      <x:c r="DW146" s="106"/>
     </x:row>
     <x:row r="147" ht="25" customHeight="1">
       <x:c r="A147" s="10"/>
@@ -20225,6 +20788,9 @@
       <x:c r="DR147" s="88"/>
       <x:c r="DS147" s="88"/>
       <x:c r="DT147" s="100"/>
+      <x:c r="DU147" s="106"/>
+      <x:c r="DV147" s="106"/>
+      <x:c r="DW147" s="106"/>
     </x:row>
     <x:row r="148" ht="25" customHeight="1">
       <x:c r="A148" s="10"/>
@@ -20311,6 +20877,9 @@
       <x:c r="DR148" s="88"/>
       <x:c r="DS148" s="88"/>
       <x:c r="DT148" s="100"/>
+      <x:c r="DU148" s="106"/>
+      <x:c r="DV148" s="106"/>
+      <x:c r="DW148" s="106"/>
     </x:row>
     <x:row r="149" ht="25" customHeight="1">
       <x:c r="A149" s="10"/>
@@ -20397,6 +20966,9 @@
       <x:c r="DR149" s="88"/>
       <x:c r="DS149" s="88"/>
       <x:c r="DT149" s="100"/>
+      <x:c r="DU149" s="106"/>
+      <x:c r="DV149" s="106"/>
+      <x:c r="DW149" s="106"/>
     </x:row>
     <x:row r="150" ht="25" customHeight="1">
       <x:c r="A150" s="10"/>
@@ -20483,6 +21055,9 @@
       <x:c r="DR150" s="88"/>
       <x:c r="DS150" s="88"/>
       <x:c r="DT150" s="100"/>
+      <x:c r="DU150" s="106"/>
+      <x:c r="DV150" s="106"/>
+      <x:c r="DW150" s="106"/>
     </x:row>
     <x:row r="151" ht="25" customHeight="1">
       <x:c r="A151" s="10"/>
@@ -20569,6 +21144,9 @@
       <x:c r="DR151" s="88"/>
       <x:c r="DS151" s="88"/>
       <x:c r="DT151" s="100"/>
+      <x:c r="DU151" s="106"/>
+      <x:c r="DV151" s="106"/>
+      <x:c r="DW151" s="106"/>
     </x:row>
     <x:row r="152" ht="25" customHeight="1">
       <x:c r="A152" s="10"/>
@@ -20655,6 +21233,9 @@
       <x:c r="DR152" s="88"/>
       <x:c r="DS152" s="88"/>
       <x:c r="DT152" s="100"/>
+      <x:c r="DU152" s="106"/>
+      <x:c r="DV152" s="106"/>
+      <x:c r="DW152" s="106"/>
     </x:row>
     <x:row r="153" ht="25" customHeight="1">
       <x:c r="A153" s="10"/>
@@ -20741,6 +21322,9 @@
       <x:c r="DR153" s="88"/>
       <x:c r="DS153" s="88"/>
       <x:c r="DT153" s="100"/>
+      <x:c r="DU153" s="106"/>
+      <x:c r="DV153" s="106"/>
+      <x:c r="DW153" s="106"/>
     </x:row>
     <x:row r="154" ht="25" customHeight="1">
       <x:c r="A154" s="10"/>
@@ -20827,6 +21411,9 @@
       <x:c r="DR154" s="88"/>
       <x:c r="DS154" s="88"/>
       <x:c r="DT154" s="100"/>
+      <x:c r="DU154" s="106"/>
+      <x:c r="DV154" s="106"/>
+      <x:c r="DW154" s="106"/>
     </x:row>
     <x:row r="155" ht="25" customHeight="1">
       <x:c r="A155" s="10"/>
@@ -20913,6 +21500,9 @@
       <x:c r="DR155" s="88"/>
       <x:c r="DS155" s="88"/>
       <x:c r="DT155" s="100"/>
+      <x:c r="DU155" s="106"/>
+      <x:c r="DV155" s="106"/>
+      <x:c r="DW155" s="106"/>
     </x:row>
     <x:row r="156" ht="25" customHeight="1">
       <x:c r="A156" s="10"/>
@@ -20999,6 +21589,9 @@
       <x:c r="DR156" s="88"/>
       <x:c r="DS156" s="88"/>
       <x:c r="DT156" s="100"/>
+      <x:c r="DU156" s="106"/>
+      <x:c r="DV156" s="106"/>
+      <x:c r="DW156" s="106"/>
     </x:row>
     <x:row r="157" ht="25" customHeight="1">
       <x:c r="A157" s="10"/>
@@ -21085,6 +21678,9 @@
       <x:c r="DR157" s="88"/>
       <x:c r="DS157" s="88"/>
       <x:c r="DT157" s="100"/>
+      <x:c r="DU157" s="106"/>
+      <x:c r="DV157" s="106"/>
+      <x:c r="DW157" s="106"/>
     </x:row>
     <x:row r="158" ht="25" customHeight="1">
       <x:c r="A158" s="10"/>
@@ -21171,6 +21767,9 @@
       <x:c r="DR158" s="88"/>
       <x:c r="DS158" s="88"/>
       <x:c r="DT158" s="100"/>
+      <x:c r="DU158" s="106"/>
+      <x:c r="DV158" s="106"/>
+      <x:c r="DW158" s="106"/>
     </x:row>
     <x:row r="159" ht="25" customHeight="1">
       <x:c r="A159" s="10"/>
@@ -21257,6 +21856,9 @@
       <x:c r="DR159" s="88"/>
       <x:c r="DS159" s="88"/>
       <x:c r="DT159" s="100"/>
+      <x:c r="DU159" s="106"/>
+      <x:c r="DV159" s="106"/>
+      <x:c r="DW159" s="106"/>
     </x:row>
     <x:row r="160" ht="25" customHeight="1">
       <x:c r="A160" s="10"/>
@@ -21343,6 +21945,9 @@
       <x:c r="DR160" s="88"/>
       <x:c r="DS160" s="88"/>
       <x:c r="DT160" s="100"/>
+      <x:c r="DU160" s="106"/>
+      <x:c r="DV160" s="106"/>
+      <x:c r="DW160" s="106"/>
     </x:row>
     <x:row r="161" ht="25" customHeight="1">
       <x:c r="A161" s="10"/>
@@ -21429,6 +22034,9 @@
       <x:c r="DR161" s="88"/>
       <x:c r="DS161" s="88"/>
       <x:c r="DT161" s="100"/>
+      <x:c r="DU161" s="106"/>
+      <x:c r="DV161" s="106"/>
+      <x:c r="DW161" s="106"/>
     </x:row>
     <x:row r="162" ht="25" customHeight="1">
       <x:c r="A162" s="10"/>
@@ -21515,6 +22123,9 @@
       <x:c r="DR162" s="88"/>
       <x:c r="DS162" s="88"/>
       <x:c r="DT162" s="100"/>
+      <x:c r="DU162" s="106"/>
+      <x:c r="DV162" s="106"/>
+      <x:c r="DW162" s="106"/>
     </x:row>
     <x:row r="163" ht="25" customHeight="1">
       <x:c r="A163" s="10"/>
@@ -21601,6 +22212,9 @@
       <x:c r="DR163" s="88"/>
       <x:c r="DS163" s="88"/>
       <x:c r="DT163" s="100"/>
+      <x:c r="DU163" s="106"/>
+      <x:c r="DV163" s="106"/>
+      <x:c r="DW163" s="106"/>
     </x:row>
     <x:row r="164" ht="25" customHeight="1">
       <x:c r="A164" s="10"/>
@@ -21687,6 +22301,9 @@
       <x:c r="DR164" s="88"/>
       <x:c r="DS164" s="88"/>
       <x:c r="DT164" s="100"/>
+      <x:c r="DU164" s="106"/>
+      <x:c r="DV164" s="106"/>
+      <x:c r="DW164" s="106"/>
     </x:row>
     <x:row r="165" ht="25" customHeight="1">
       <x:c r="A165" s="10"/>
@@ -21773,6 +22390,9 @@
       <x:c r="DR165" s="88"/>
       <x:c r="DS165" s="88"/>
       <x:c r="DT165" s="100"/>
+      <x:c r="DU165" s="106"/>
+      <x:c r="DV165" s="106"/>
+      <x:c r="DW165" s="106"/>
     </x:row>
     <x:row r="166" ht="25" customHeight="1">
       <x:c r="A166" s="10"/>
@@ -21859,6 +22479,9 @@
       <x:c r="DR166" s="88"/>
       <x:c r="DS166" s="88"/>
       <x:c r="DT166" s="100"/>
+      <x:c r="DU166" s="106"/>
+      <x:c r="DV166" s="106"/>
+      <x:c r="DW166" s="106"/>
     </x:row>
     <x:row r="167" ht="25" customHeight="1">
       <x:c r="A167" s="10"/>
@@ -21945,6 +22568,9 @@
       <x:c r="DR167" s="88"/>
       <x:c r="DS167" s="88"/>
       <x:c r="DT167" s="100"/>
+      <x:c r="DU167" s="106"/>
+      <x:c r="DV167" s="106"/>
+      <x:c r="DW167" s="106"/>
     </x:row>
     <x:row r="168" ht="25" customHeight="1">
       <x:c r="A168" s="10"/>
@@ -22031,6 +22657,9 @@
       <x:c r="DR168" s="88"/>
       <x:c r="DS168" s="88"/>
       <x:c r="DT168" s="100"/>
+      <x:c r="DU168" s="106"/>
+      <x:c r="DV168" s="106"/>
+      <x:c r="DW168" s="106"/>
     </x:row>
     <x:row r="169" ht="25" customHeight="1">
       <x:c r="A169" s="10"/>
@@ -22117,6 +22746,9 @@
       <x:c r="DR169" s="88"/>
       <x:c r="DS169" s="88"/>
       <x:c r="DT169" s="100"/>
+      <x:c r="DU169" s="106"/>
+      <x:c r="DV169" s="106"/>
+      <x:c r="DW169" s="106"/>
     </x:row>
     <x:row r="170" ht="25" customHeight="1">
       <x:c r="A170" s="10"/>
@@ -22203,6 +22835,9 @@
       <x:c r="DR170" s="88"/>
       <x:c r="DS170" s="88"/>
       <x:c r="DT170" s="100"/>
+      <x:c r="DU170" s="106"/>
+      <x:c r="DV170" s="106"/>
+      <x:c r="DW170" s="106"/>
     </x:row>
     <x:row r="171" ht="25" customHeight="1">
       <x:c r="A171" s="10"/>
@@ -22289,6 +22924,9 @@
       <x:c r="DR171" s="88"/>
       <x:c r="DS171" s="88"/>
       <x:c r="DT171" s="100"/>
+      <x:c r="DU171" s="106"/>
+      <x:c r="DV171" s="106"/>
+      <x:c r="DW171" s="106"/>
     </x:row>
     <x:row r="172" ht="25" customHeight="1">
       <x:c r="A172" s="10"/>
@@ -22375,6 +23013,9 @@
       <x:c r="DR172" s="88"/>
       <x:c r="DS172" s="88"/>
       <x:c r="DT172" s="100"/>
+      <x:c r="DU172" s="106"/>
+      <x:c r="DV172" s="106"/>
+      <x:c r="DW172" s="106"/>
     </x:row>
     <x:row r="173" ht="25" customHeight="1">
       <x:c r="A173" s="10"/>
@@ -22461,6 +23102,9 @@
       <x:c r="DR173" s="88"/>
       <x:c r="DS173" s="88"/>
       <x:c r="DT173" s="100"/>
+      <x:c r="DU173" s="106"/>
+      <x:c r="DV173" s="106"/>
+      <x:c r="DW173" s="106"/>
     </x:row>
     <x:row r="174" ht="25" customHeight="1">
       <x:c r="A174" s="10"/>
@@ -22547,6 +23191,9 @@
       <x:c r="DR174" s="88"/>
       <x:c r="DS174" s="88"/>
       <x:c r="DT174" s="100"/>
+      <x:c r="DU174" s="106"/>
+      <x:c r="DV174" s="106"/>
+      <x:c r="DW174" s="106"/>
     </x:row>
     <x:row r="175" ht="25" customHeight="1">
       <x:c r="A175" s="10"/>
@@ -22633,6 +23280,9 @@
       <x:c r="DR175" s="88"/>
       <x:c r="DS175" s="88"/>
       <x:c r="DT175" s="100"/>
+      <x:c r="DU175" s="106"/>
+      <x:c r="DV175" s="106"/>
+      <x:c r="DW175" s="106"/>
     </x:row>
     <x:row r="176" ht="25" customHeight="1">
       <x:c r="A176" s="10"/>
@@ -22719,6 +23369,9 @@
       <x:c r="DR176" s="88"/>
       <x:c r="DS176" s="88"/>
       <x:c r="DT176" s="100"/>
+      <x:c r="DU176" s="106"/>
+      <x:c r="DV176" s="106"/>
+      <x:c r="DW176" s="106"/>
     </x:row>
     <x:row r="177" ht="25" customHeight="1">
       <x:c r="A177" s="10"/>
@@ -22805,6 +23458,9 @@
       <x:c r="DR177" s="88"/>
       <x:c r="DS177" s="88"/>
       <x:c r="DT177" s="100"/>
+      <x:c r="DU177" s="106"/>
+      <x:c r="DV177" s="106"/>
+      <x:c r="DW177" s="106"/>
     </x:row>
     <x:row r="178" ht="25" customHeight="1">
       <x:c r="A178" s="10"/>
@@ -22891,6 +23547,9 @@
       <x:c r="DR178" s="88"/>
       <x:c r="DS178" s="88"/>
       <x:c r="DT178" s="100"/>
+      <x:c r="DU178" s="106"/>
+      <x:c r="DV178" s="106"/>
+      <x:c r="DW178" s="106"/>
     </x:row>
     <x:row r="179" ht="25" customHeight="1">
       <x:c r="A179" s="10"/>
@@ -22977,6 +23636,9 @@
       <x:c r="DR179" s="88"/>
       <x:c r="DS179" s="88"/>
       <x:c r="DT179" s="100"/>
+      <x:c r="DU179" s="106"/>
+      <x:c r="DV179" s="106"/>
+      <x:c r="DW179" s="106"/>
     </x:row>
     <x:row r="180" ht="25" customHeight="1">
       <x:c r="A180" s="10"/>
@@ -23063,6 +23725,9 @@
       <x:c r="DR180" s="88"/>
       <x:c r="DS180" s="88"/>
       <x:c r="DT180" s="100"/>
+      <x:c r="DU180" s="106"/>
+      <x:c r="DV180" s="106"/>
+      <x:c r="DW180" s="106"/>
     </x:row>
     <x:row r="181" ht="25" customHeight="1">
       <x:c r="A181" s="10"/>
@@ -23149,6 +23814,9 @@
       <x:c r="DR181" s="88"/>
       <x:c r="DS181" s="88"/>
       <x:c r="DT181" s="100"/>
+      <x:c r="DU181" s="106"/>
+      <x:c r="DV181" s="106"/>
+      <x:c r="DW181" s="106"/>
     </x:row>
     <x:row r="182" ht="25" customHeight="1">
       <x:c r="A182" s="10"/>
@@ -23235,6 +23903,9 @@
       <x:c r="DR182" s="88"/>
       <x:c r="DS182" s="88"/>
       <x:c r="DT182" s="100"/>
+      <x:c r="DU182" s="106"/>
+      <x:c r="DV182" s="106"/>
+      <x:c r="DW182" s="106"/>
     </x:row>
     <x:row r="183" ht="25" customHeight="1">
       <x:c r="A183" s="10"/>
@@ -23321,6 +23992,9 @@
       <x:c r="DR183" s="88"/>
       <x:c r="DS183" s="88"/>
       <x:c r="DT183" s="100"/>
+      <x:c r="DU183" s="106"/>
+      <x:c r="DV183" s="106"/>
+      <x:c r="DW183" s="106"/>
     </x:row>
     <x:row r="184" ht="25" customHeight="1">
       <x:c r="A184" s="10"/>
@@ -23407,6 +24081,9 @@
       <x:c r="DR184" s="88"/>
       <x:c r="DS184" s="88"/>
       <x:c r="DT184" s="100"/>
+      <x:c r="DU184" s="106"/>
+      <x:c r="DV184" s="106"/>
+      <x:c r="DW184" s="106"/>
     </x:row>
     <x:row r="185" ht="25" customHeight="1">
       <x:c r="A185" s="10"/>
@@ -23493,6 +24170,9 @@
       <x:c r="DR185" s="88"/>
       <x:c r="DS185" s="88"/>
       <x:c r="DT185" s="100"/>
+      <x:c r="DU185" s="106"/>
+      <x:c r="DV185" s="106"/>
+      <x:c r="DW185" s="106"/>
     </x:row>
     <x:row r="186" ht="25" customHeight="1">
       <x:c r="A186" s="10"/>
@@ -23579,6 +24259,9 @@
       <x:c r="DR186" s="88"/>
       <x:c r="DS186" s="88"/>
       <x:c r="DT186" s="100"/>
+      <x:c r="DU186" s="106"/>
+      <x:c r="DV186" s="106"/>
+      <x:c r="DW186" s="106"/>
     </x:row>
     <x:row r="187" ht="25" customHeight="1">
       <x:c r="A187" s="10"/>
@@ -23665,6 +24348,9 @@
       <x:c r="DR187" s="88"/>
       <x:c r="DS187" s="88"/>
       <x:c r="DT187" s="100"/>
+      <x:c r="DU187" s="106"/>
+      <x:c r="DV187" s="106"/>
+      <x:c r="DW187" s="106"/>
     </x:row>
     <x:row r="188" ht="25" customHeight="1">
       <x:c r="A188" s="10"/>
@@ -23751,6 +24437,9 @@
       <x:c r="DR188" s="88"/>
       <x:c r="DS188" s="88"/>
       <x:c r="DT188" s="100"/>
+      <x:c r="DU188" s="106"/>
+      <x:c r="DV188" s="106"/>
+      <x:c r="DW188" s="106"/>
     </x:row>
     <x:row r="189" ht="25" customHeight="1">
       <x:c r="A189" s="10"/>
@@ -23837,6 +24526,9 @@
       <x:c r="DR189" s="88"/>
       <x:c r="DS189" s="88"/>
       <x:c r="DT189" s="100"/>
+      <x:c r="DU189" s="106"/>
+      <x:c r="DV189" s="106"/>
+      <x:c r="DW189" s="106"/>
     </x:row>
     <x:row r="190" ht="25" customHeight="1">
       <x:c r="A190" s="10"/>
@@ -23923,6 +24615,9 @@
       <x:c r="DR190" s="88"/>
       <x:c r="DS190" s="88"/>
       <x:c r="DT190" s="100"/>
+      <x:c r="DU190" s="106"/>
+      <x:c r="DV190" s="106"/>
+      <x:c r="DW190" s="106"/>
     </x:row>
     <x:row r="191" ht="25" customHeight="1">
       <x:c r="A191" s="10"/>
@@ -24009,6 +24704,9 @@
       <x:c r="DR191" s="88"/>
       <x:c r="DS191" s="88"/>
       <x:c r="DT191" s="100"/>
+      <x:c r="DU191" s="106"/>
+      <x:c r="DV191" s="106"/>
+      <x:c r="DW191" s="106"/>
     </x:row>
     <x:row r="192" ht="25" customHeight="1">
       <x:c r="A192" s="10"/>
@@ -24095,6 +24793,9 @@
       <x:c r="DR192" s="88"/>
       <x:c r="DS192" s="88"/>
       <x:c r="DT192" s="100"/>
+      <x:c r="DU192" s="106"/>
+      <x:c r="DV192" s="106"/>
+      <x:c r="DW192" s="106"/>
     </x:row>
     <x:row r="193" ht="25" customHeight="1">
       <x:c r="A193" s="10"/>
@@ -24181,6 +24882,9 @@
       <x:c r="DR193" s="88"/>
       <x:c r="DS193" s="88"/>
       <x:c r="DT193" s="100"/>
+      <x:c r="DU193" s="106"/>
+      <x:c r="DV193" s="106"/>
+      <x:c r="DW193" s="106"/>
     </x:row>
     <x:row r="194" ht="25" customHeight="1">
       <x:c r="A194" s="10"/>
@@ -24267,6 +24971,9 @@
       <x:c r="DR194" s="88"/>
       <x:c r="DS194" s="88"/>
       <x:c r="DT194" s="100"/>
+      <x:c r="DU194" s="106"/>
+      <x:c r="DV194" s="106"/>
+      <x:c r="DW194" s="106"/>
     </x:row>
     <x:row r="195" ht="25" customHeight="1">
       <x:c r="A195" s="10"/>
@@ -24353,6 +25060,9 @@
       <x:c r="DR195" s="88"/>
       <x:c r="DS195" s="88"/>
       <x:c r="DT195" s="100"/>
+      <x:c r="DU195" s="106"/>
+      <x:c r="DV195" s="106"/>
+      <x:c r="DW195" s="106"/>
     </x:row>
     <x:row r="196" ht="25" customHeight="1">
       <x:c r="A196" s="10"/>
@@ -24439,6 +25149,9 @@
       <x:c r="DR196" s="88"/>
       <x:c r="DS196" s="88"/>
       <x:c r="DT196" s="100"/>
+      <x:c r="DU196" s="106"/>
+      <x:c r="DV196" s="106"/>
+      <x:c r="DW196" s="106"/>
     </x:row>
     <x:row r="197" ht="25" customHeight="1">
       <x:c r="A197" s="10"/>
@@ -24525,6 +25238,9 @@
       <x:c r="DR197" s="88"/>
       <x:c r="DS197" s="88"/>
       <x:c r="DT197" s="100"/>
+      <x:c r="DU197" s="106"/>
+      <x:c r="DV197" s="106"/>
+      <x:c r="DW197" s="106"/>
     </x:row>
     <x:row r="198" ht="25" customHeight="1">
       <x:c r="A198" s="10"/>
@@ -24611,6 +25327,9 @@
       <x:c r="DR198" s="88"/>
       <x:c r="DS198" s="88"/>
       <x:c r="DT198" s="100"/>
+      <x:c r="DU198" s="106"/>
+      <x:c r="DV198" s="106"/>
+      <x:c r="DW198" s="106"/>
     </x:row>
     <x:row r="199" ht="25" customHeight="1">
       <x:c r="A199" s="10"/>
@@ -24697,6 +25416,9 @@
       <x:c r="DR199" s="88"/>
       <x:c r="DS199" s="88"/>
       <x:c r="DT199" s="100"/>
+      <x:c r="DU199" s="106"/>
+      <x:c r="DV199" s="106"/>
+      <x:c r="DW199" s="106"/>
     </x:row>
     <x:row r="200" ht="25" customHeight="1">
       <x:c r="A200" s="10"/>
@@ -24783,9 +25505,12 @@
       <x:c r="DR200" s="88"/>
       <x:c r="DS200" s="88"/>
       <x:c r="DT200" s="100"/>
+      <x:c r="DU200" s="106"/>
+      <x:c r="DV200" s="106"/>
+      <x:c r="DW200" s="106"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="45">
+  <x:dataValidations count="48">
     <x:dataValidation type="list" sqref="K2:K200">
       <x:formula1>"自身,敵一体,味方一体,自身中心,敵中心"</x:formula1>
     </x:dataValidation>
@@ -24871,7 +25596,7 @@
       <x:formula1>"有効,無効"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="BS2:BS200">
-      <x:formula1>"直進,追尾,拡大直進,その場,ブーメラン,周回後に射出,蛇行,加速,減速停止,遅延追尾,螺旋,往復,感応地雷,収束成長"</x:formula1>
+      <x:formula1>"直進,追尾,拡大直進,その場,ブーメラン,周回後に射出,蛇行,加速,減速停止,遅延追尾,螺旋,往復,感応地雷,収束成長,爆発"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="CG2:CG200">
       <x:formula1>"有効,無効"</x:formula1>
@@ -24886,7 +25611,7 @@
       <x:formula1>"有効,無効"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="CP2:CP200">
-      <x:formula1>"直進,追尾,拡大直進,その場,ブーメラン,周回後に射出,蛇行,加速,減速停止,遅延追尾,螺旋,往復,感応地雷,収束成長"</x:formula1>
+      <x:formula1>"直進,追尾,拡大直進,その場,ブーメラン,周回後に射出,蛇行,加速,減速停止,遅延追尾,螺旋,往復,感応地雷,収束成長,爆発"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="CR2:CR200">
       <x:formula1>"有効,無効"</x:formula1>
@@ -24921,10 +25646,21 @@
     <x:dataValidation type="list" sqref="DR2:DR200">
       <x:formula1>"なし,最大HP,最大MP,攻撃力,魔法攻撃力,防御力,魔法防御力,移動速度,攻撃速度,攻撃範囲,会心率,会心倍率,素材ドロップ率,装備ドロップ率,火属性耐性,水属性耐性,風属性耐性,雷属性耐性,光属性耐性,闇属性耐性,全属性耐性,近接攻撃タイプ,遠距離攻撃タイプ,配合確率,武器取得数,称号抽選回数,敵リスポーン速度"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="DU2:DU200">
+      <x:formula1>"有効,無効"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="DV2:DV200">
+      <x:formula1>0.02</x:formula1>
+      <x:formula2>60</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="DW2:DW200">
+      <x:formula1>0.01</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77903f12c53f472d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6846b5e35f994260"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25040,7 +25776,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb592899bc714783"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7276936c4c154f83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28290,10 +29026,10 @@
         <x:v>表示倍率＝3は仮値</x:v>
       </x:c>
       <x:c r="C266" s="89" t="str">
-        <x:v>スプライトのサイズ・PPUに合わせて調整</x:v>
+        <x:v>範囲への表示自動調整が有効なら、表示倍率にかかわらず効果範囲へ合わせる</x:v>
       </x:c>
       <x:c r="D266" s="89" t="str">
-        <x:v>見た目の倍率を変えても効果範囲は変わらない</x:v>
+        <x:v>手動で画像サイズを調整したい場合は自動調整を無効にする</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="58" customHeight="1">
@@ -28374,10 +29110,10 @@
         <x:v>ID3：衝撃波</x:v>
       </x:c>
       <x:c r="C273" s="89" t="str">
-        <x:v>発射物／その場／使用者生成／生成時に1回</x:v>
+        <x:v>発射物／爆発／使用者生成／生成時に1回</x:v>
       </x:c>
       <x:c r="D273" s="89" t="str">
-        <x:v>3.pngを使い、0.45秒表示。範囲・威力は既存値を維持</x:v>
+        <x:v>3.pngで範囲いっぱいまで拡大・フェード。ダメージは既存値</x:v>
       </x:c>
     </x:row>
     <x:row r="274" ht="58" customHeight="1">
@@ -28490,6 +29226,188 @@
       </x:c>
       <x:c r="D281" s="89" t="str">
         <x:v>その場タイプなら飛ばずにエフェクトとして表示する</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" ht="32" customHeight="1">
+      <x:c r="A283" s="104" t="str">
+        <x:v>範囲表示・爆発の動き</x:v>
+      </x:c>
+      <x:c r="B283" s="104" t="str">
+        <x:v>設定項目</x:v>
+      </x:c>
+      <x:c r="C283" s="104" t="str">
+        <x:v>動作・入力例</x:v>
+      </x:c>
+      <x:c r="D283" s="104" t="str">
+        <x:v>注意</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" ht="58" customHeight="1">
+      <x:c r="A284" s="89" t="str">
+        <x:v>範囲表示</x:v>
+      </x:c>
+      <x:c r="B284" s="89" t="str">
+        <x:v>発射物_範囲に表示を合わせる</x:v>
+      </x:c>
+      <x:c r="C284" s="89" t="str">
+        <x:v>有効（空欄も有効）：範囲半径×2の直径に自動調整</x:v>
+      </x:c>
+      <x:c r="D284" s="89" t="str">
+        <x:v>画像の寸法・PPU・親の倍率を考慮。スプライトだけ拡大</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" ht="58" customHeight="1">
+      <x:c r="A285" s="89" t="str">
+        <x:v>対象</x:v>
+      </x:c>
+      <x:c r="B285" s="89" t="str">
+        <x:v>範囲内の敵／味方＋範囲半径</x:v>
+      </x:c>
+      <x:c r="C285" s="89" t="str">
+        <x:v>例：半径3なら直径6の表示</x:v>
+      </x:c>
+      <x:c r="D285" s="89" t="str">
+        <x:v>通常の弾や単体効果は表示倍率を維持</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" ht="58" customHeight="1">
+      <x:c r="A286" s="89" t="str">
+        <x:v>陣</x:v>
+      </x:c>
+      <x:c r="B286" s="89" t="str">
+        <x:v>その場＋一定間隔</x:v>
+      </x:c>
+      <x:c r="C286" s="89" t="str">
+        <x:v>発動時から指定範囲いっぱいに表示</x:v>
+      </x:c>
+      <x:c r="D286" s="89" t="str">
+        <x:v>寿命まで表示。通常の陣は爆発のように消えない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" ht="58" customHeight="1">
+      <x:c r="A287" s="89" t="str">
+        <x:v>爆発</x:v>
+      </x:c>
+      <x:c r="B287" s="89" t="str">
+        <x:v>発射物_移動タイプ＝爆発</x:v>
+      </x:c>
+      <x:c r="C287" s="89" t="str">
+        <x:v>使用地点で急速に拡大し、薄くなって消える</x:v>
+      </x:c>
+      <x:c r="D287" s="89" t="str">
+        <x:v>既存の移動タイプ番号0～13は維持、爆発は14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" ht="58" customHeight="1">
+      <x:c r="A288" s="89" t="str">
+        <x:v>拡大時間</x:v>
+      </x:c>
+      <x:c r="B288" s="89" t="str">
+        <x:v>発射物_爆発拡大秒</x:v>
+      </x:c>
+      <x:c r="C288" s="89" t="str">
+        <x:v>0.35秒（0.02秒以上）</x:v>
+      </x:c>
+      <x:c r="D288" s="89" t="str">
+        <x:v>発射物寿命の方が短い場合は寿命内に完了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" ht="58" customHeight="1">
+      <x:c r="A289" s="89" t="str">
+        <x:v>開始倍率</x:v>
+      </x:c>
+      <x:c r="B289" s="89" t="str">
+        <x:v>発射物_爆発開始倍率</x:v>
+      </x:c>
+      <x:c r="C289" s="89" t="str">
+        <x:v>0.1：範囲直径の10％から広がる</x:v>
+      </x:c>
+      <x:c r="D289" s="89" t="str">
+        <x:v>0より大きく1以下。終点は範囲いっぱい</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" ht="58" customHeight="1">
+      <x:c r="A290" s="89" t="str">
+        <x:v>衝撃波</x:v>
+      </x:c>
+      <x:c r="B290" s="89" t="str">
+        <x:v>ID3と39を爆発に設定済み</x:v>
+      </x:c>
+      <x:c r="C290" s="89" t="str">
+        <x:v>生成時のダメージは一度だけ</x:v>
+      </x:c>
+      <x:c r="D290" s="89" t="str">
+        <x:v>見た目の拡大による追加ダメージはなし</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" ht="58" customHeight="1">
+      <x:c r="A291" s="89" t="str">
+        <x:v>自動演出</x:v>
+      </x:c>
+      <x:c r="B291" s="89" t="str">
+        <x:v>その場＋範囲ダメージ＋生成時</x:v>
+      </x:c>
+      <x:c r="C291" s="89" t="str">
+        <x:v>既存の衝撃波設定でも自動的に拡大・フェード</x:v>
+      </x:c>
+      <x:c r="D291" s="89" t="str">
+        <x:v>移動タイプを変えなくても既存アセットへ適用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" ht="58" customHeight="1">
+      <x:c r="A292" s="89" t="str">
+        <x:v>命中時爆発</x:v>
+      </x:c>
+      <x:c r="B292" s="89" t="str">
+        <x:v>既存の命中時爆発・停止時爆発</x:v>
+      </x:c>
+      <x:c r="C292" s="89" t="str">
+        <x:v>爆発半径に表示を合わせ、拡大・フェード</x:v>
+      </x:c>
+      <x:c r="D292" s="89" t="str">
+        <x:v>爆発表示秒は既存の設定を使用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" ht="58" customHeight="1">
+      <x:c r="A293" s="89" t="str">
+        <x:v>独立した範囲</x:v>
+      </x:c>
+      <x:c r="B293" s="89" t="str">
+        <x:v>見た目とダメージ判定</x:v>
+      </x:c>
+      <x:c r="C293" s="89" t="str">
+        <x:v>表示サイズの補正は画像側だけ</x:v>
+      </x:c>
+      <x:c r="D293" s="89" t="str">
+        <x:v>当たり判定・威力・効果範囲の数値は変えない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" ht="58" customHeight="1">
+      <x:c r="A294" s="89" t="str">
+        <x:v>従来の表示倍率</x:v>
+      </x:c>
+      <x:c r="B294" s="89" t="str">
+        <x:v>自動調整を無効にする</x:v>
+      </x:c>
+      <x:c r="C294" s="89" t="str">
+        <x:v>表示倍率と画像本来のサイズを使用</x:v>
+      </x:c>
+      <x:c r="D294" s="89" t="str">
+        <x:v>範囲へ自動で合わせたい場合は有効のまま使用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" ht="58" customHeight="1">
+      <x:c r="A295" s="89" t="str">
+        <x:v>反映</x:v>
+      </x:c>
+      <x:c r="B295" s="89" t="str">
+        <x:v>更新Excelを再取り込み</x:v>
+      </x:c>
+      <x:c r="C295" s="89" t="str">
+        <x:v>新しい表示項目をSkillDataへ反映</x:v>
+      </x:c>
+      <x:c r="D295" s="89" t="str">
+        <x:v>既存範囲スキルの自動調整はコード反映後から有効</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Docs/SkillTemplates/スキル定義テンプレート.xlsx
+++ b/Docs/SkillTemplates/スキル定義テンプレート.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル" sheetId="1" r:id="Rc2ad8614dddb470c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="モンスター列追加例" sheetId="2" r:id="R89d311b040f546f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="3" r:id="R0051bf4f84624bf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル" sheetId="1" r:id="R0bfbeb24d8554b70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="モンスター列追加例" sheetId="2" r:id="R854b05576e3b4dc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="3" r:id="Rac2abcb45beb43fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +20,7 @@
     <x:numFmt numFmtId="201" formatCode="0"/>
     <x:numFmt numFmtId="202" formatCode="0.0##"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -90,8 +90,18 @@
       <x:sz val="11"/>
       <x:name val="Noto Sans JP"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF203864"/>
+      <x:name val="Noto Sans JP"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF172033"/>
+      <x:name val="Noto Sans JP"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="23">
+  <x:fills count="40">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -203,6 +213,91 @@
         <x:fgColor rgb="FFFFF3D5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFF703F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF76FFB0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFE6A6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFBE55"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF8EEDCF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE3A15C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFB492FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF9DFF57"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFF5030"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF72DBFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC18AFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFBD70FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFF6B38"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF70FFAC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF83BCFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF203864"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border>
@@ -216,7 +311,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="108">
+  <x:cellXfs count="143">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -459,6 +554,91 @@
     <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -921,10 +1101,11 @@
     <x:col min="121" max="121" width="22" hidden="0" customWidth="1"/>
     <x:col min="122" max="122" width="22" hidden="0" customWidth="1"/>
     <x:col min="123" max="123" width="22" hidden="0" customWidth="1"/>
-    <x:col min="124" max="124" width="22" hidden="0" customWidth="1"/>
+    <x:col min="124" max="124" width="24" hidden="0" customWidth="1"/>
     <x:col min="125" max="125" width="26" hidden="0" customWidth="1"/>
     <x:col min="126" max="126" width="26" hidden="0" customWidth="1"/>
     <x:col min="127" max="127" width="26" hidden="0" customWidth="1"/>
+    <x:col min="128" max="128" width="52" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="55" customHeight="1">
@@ -1297,17 +1478,20 @@
       <x:c r="DS1" s="87" t="str">
         <x:v>パッシブ3_効果量</x:v>
       </x:c>
-      <x:c r="DT1" s="98" t="str">
-        <x:v>発射物_画像番号</x:v>
-      </x:c>
-      <x:c r="DU1" s="104" t="str">
+      <x:c r="DT1" s="87" t="str">
+        <x:v>発射物_素材</x:v>
+      </x:c>
+      <x:c r="DU1" s="87" t="str">
         <x:v>発射物_範囲に表示を合わせる</x:v>
       </x:c>
-      <x:c r="DV1" s="104" t="str">
+      <x:c r="DV1" s="87" t="str">
         <x:v>発射物_爆発拡大秒</x:v>
       </x:c>
-      <x:c r="DW1" s="104" t="str">
+      <x:c r="DW1" s="87" t="str">
         <x:v>発射物_爆発開始倍率</x:v>
+      </x:c>
+      <x:c r="DX1" s="87" t="str">
+        <x:v>発射物_固有スプライト</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="25" customHeight="1">
@@ -1635,8 +1819,8 @@
       <x:c r="DE2" s="45" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="DF2" s="77" t="str">
-        <x:v>#FFFFFFFF</x:v>
+      <x:c r="DF2" s="111" t="str">
+        <x:v>#FF703FFF</x:v>
       </x:c>
       <x:c r="DG2" s="45" t="n">
         <x:v>60</x:v>
@@ -1665,8 +1849,8 @@
       <x:c r="DQ2" s="88"/>
       <x:c r="DR2" s="88"/>
       <x:c r="DS2" s="88"/>
-      <x:c r="DT2" s="100" t="n">
-        <x:v>1</x:v>
+      <x:c r="DT2" s="100" t="str">
+        <x:v>光の弾</x:v>
       </x:c>
       <x:c r="DU2" s="106" t="str">
         <x:v>有効</x:v>
@@ -1677,6 +1861,7 @@
       <x:c r="DW2" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX2" s="109"/>
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="9" t="str">
@@ -2003,8 +2188,8 @@
       <x:c r="DE3" s="45" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="DF3" s="77" t="str">
-        <x:v>#FFFFFFFF</x:v>
+      <x:c r="DF3" s="113" t="str">
+        <x:v>#76FFB0FF</x:v>
       </x:c>
       <x:c r="DG3" s="45" t="n">
         <x:v>60</x:v>
@@ -2033,8 +2218,8 @@
       <x:c r="DQ3" s="88"/>
       <x:c r="DR3" s="88"/>
       <x:c r="DS3" s="88"/>
-      <x:c r="DT3" s="100" t="n">
-        <x:v>2</x:v>
+      <x:c r="DT3" s="100" t="str">
+        <x:v>光の弾</x:v>
       </x:c>
       <x:c r="DU3" s="106" t="str">
         <x:v>有効</x:v>
@@ -2045,6 +2230,7 @@
       <x:c r="DW3" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX3" s="109"/>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
       <x:c r="A4" s="9" t="str">
@@ -2371,8 +2557,8 @@
       <x:c r="DE4" s="45" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="DF4" s="77" t="str">
-        <x:v>#FFFFFFFF</x:v>
+      <x:c r="DF4" s="115" t="str">
+        <x:v>#FFE6A6FF</x:v>
       </x:c>
       <x:c r="DG4" s="45" t="n">
         <x:v>60</x:v>
@@ -2401,8 +2587,8 @@
       <x:c r="DQ4" s="88"/>
       <x:c r="DR4" s="88"/>
       <x:c r="DS4" s="88"/>
-      <x:c r="DT4" s="100" t="n">
-        <x:v>3</x:v>
+      <x:c r="DT4" s="100" t="str">
+        <x:v>衝撃波</x:v>
       </x:c>
       <x:c r="DU4" s="106" t="str">
         <x:v>有効</x:v>
@@ -2413,6 +2599,7 @@
       <x:c r="DW4" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX4" s="109"/>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
       <x:c r="A5" s="9" t="str">
@@ -2739,8 +2926,8 @@
       <x:c r="DE5" s="45" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="DF5" s="77" t="str">
-        <x:v>#FFFFFFFF</x:v>
+      <x:c r="DF5" s="117" t="str">
+        <x:v>#FFBE55FF</x:v>
       </x:c>
       <x:c r="DG5" s="45" t="n">
         <x:v>60</x:v>
@@ -2769,8 +2956,8 @@
       <x:c r="DQ5" s="88"/>
       <x:c r="DR5" s="88"/>
       <x:c r="DS5" s="88"/>
-      <x:c r="DT5" s="100" t="n">
-        <x:v>4</x:v>
+      <x:c r="DT5" s="100" t="str">
+        <x:v>光の弾</x:v>
       </x:c>
       <x:c r="DU5" s="106" t="str">
         <x:v>有効</x:v>
@@ -2781,6 +2968,7 @@
       <x:c r="DW5" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX5" s="109"/>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
       <x:c r="A6" s="9" t="str">
@@ -3107,8 +3295,8 @@
       <x:c r="DE6" s="45" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="DF6" s="77" t="str">
-        <x:v>#FFFFFFFF</x:v>
+      <x:c r="DF6" s="119" t="str">
+        <x:v>#8EEDCFFF</x:v>
       </x:c>
       <x:c r="DG6" s="45" t="n">
         <x:v>60</x:v>
@@ -3137,8 +3325,8 @@
       <x:c r="DQ6" s="88"/>
       <x:c r="DR6" s="88"/>
       <x:c r="DS6" s="88"/>
-      <x:c r="DT6" s="100" t="n">
-        <x:v>5</x:v>
+      <x:c r="DT6" s="100" t="str">
+        <x:v>光の弾</x:v>
       </x:c>
       <x:c r="DU6" s="106" t="str">
         <x:v>有効</x:v>
@@ -3149,6 +3337,7 @@
       <x:c r="DW6" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX6" s="109"/>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
       <x:c r="A7" s="9" t="str">
@@ -3475,8 +3664,8 @@
       <x:c r="DE7" s="45" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="DF7" s="77" t="str">
-        <x:v>#FFFFFFFF</x:v>
+      <x:c r="DF7" s="121" t="str">
+        <x:v>#E3A15CFF</x:v>
       </x:c>
       <x:c r="DG7" s="45" t="n">
         <x:v>60</x:v>
@@ -3505,8 +3694,8 @@
       <x:c r="DQ7" s="88"/>
       <x:c r="DR7" s="88"/>
       <x:c r="DS7" s="88"/>
-      <x:c r="DT7" s="100" t="n">
-        <x:v>6</x:v>
+      <x:c r="DT7" s="100" t="str">
+        <x:v>光の弾</x:v>
       </x:c>
       <x:c r="DU7" s="106" t="str">
         <x:v>有効</x:v>
@@ -3517,6 +3706,7 @@
       <x:c r="DW7" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX7" s="109"/>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
       <x:c r="A8" s="9" t="str">
@@ -3843,8 +4033,8 @@
       <x:c r="DE8" s="45" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="DF8" s="77" t="str">
-        <x:v>#FFFFFFFF</x:v>
+      <x:c r="DF8" s="123" t="str">
+        <x:v>#B492FFB3</x:v>
       </x:c>
       <x:c r="DG8" s="45" t="n">
         <x:v>60</x:v>
@@ -3873,8 +4063,8 @@
       <x:c r="DQ8" s="88"/>
       <x:c r="DR8" s="88"/>
       <x:c r="DS8" s="88"/>
-      <x:c r="DT8" s="100" t="n">
-        <x:v>7</x:v>
+      <x:c r="DT8" s="100" t="str">
+        <x:v>魔方陣</x:v>
       </x:c>
       <x:c r="DU8" s="106" t="str">
         <x:v>有効</x:v>
@@ -3885,6 +4075,7 @@
       <x:c r="DW8" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX8" s="109"/>
     </x:row>
     <x:row r="9" ht="25" customHeight="1">
       <x:c r="A9" s="9" t="str">
@@ -4211,8 +4402,8 @@
       <x:c r="DE9" s="45" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="DF9" s="77" t="str">
-        <x:v>#FFFFFFFF</x:v>
+      <x:c r="DF9" s="125" t="str">
+        <x:v>#9DFF57FF</x:v>
       </x:c>
       <x:c r="DG9" s="45" t="n">
         <x:v>60</x:v>
@@ -4241,8 +4432,8 @@
       <x:c r="DQ9" s="88"/>
       <x:c r="DR9" s="88"/>
       <x:c r="DS9" s="88"/>
-      <x:c r="DT9" s="100" t="n">
-        <x:v>8</x:v>
+      <x:c r="DT9" s="100" t="str">
+        <x:v>光の弾</x:v>
       </x:c>
       <x:c r="DU9" s="106" t="str">
         <x:v>有効</x:v>
@@ -4253,6 +4444,7 @@
       <x:c r="DW9" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX9" s="109"/>
     </x:row>
     <x:row r="10" ht="25" customHeight="1">
       <x:c r="A10" s="9" t="str">
@@ -4579,8 +4771,8 @@
       <x:c r="DE10" s="45" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="DF10" s="77" t="str">
-        <x:v>#FFFFFFFF</x:v>
+      <x:c r="DF10" s="127" t="str">
+        <x:v>#FF5030FF</x:v>
       </x:c>
       <x:c r="DG10" s="45" t="n">
         <x:v>60</x:v>
@@ -4609,8 +4801,8 @@
       <x:c r="DQ10" s="88"/>
       <x:c r="DR10" s="88"/>
       <x:c r="DS10" s="88"/>
-      <x:c r="DT10" s="100" t="n">
-        <x:v>9</x:v>
+      <x:c r="DT10" s="100" t="str">
+        <x:v>光の弾</x:v>
       </x:c>
       <x:c r="DU10" s="106" t="str">
         <x:v>有効</x:v>
@@ -4621,6 +4813,7 @@
       <x:c r="DW10" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX10" s="109"/>
     </x:row>
     <x:row r="11" ht="25" customHeight="1">
       <x:c r="A11" s="9" t="str">
@@ -4947,8 +5140,8 @@
       <x:c r="DE11" s="45" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="DF11" s="77" t="str">
-        <x:v>#FFFFFFFF</x:v>
+      <x:c r="DF11" s="129" t="str">
+        <x:v>#72DBFFFF</x:v>
       </x:c>
       <x:c r="DG11" s="45" t="n">
         <x:v>60</x:v>
@@ -4977,8 +5170,8 @@
       <x:c r="DQ11" s="88"/>
       <x:c r="DR11" s="88"/>
       <x:c r="DS11" s="88"/>
-      <x:c r="DT11" s="100" t="n">
-        <x:v>10</x:v>
+      <x:c r="DT11" s="100" t="str">
+        <x:v>光の弾</x:v>
       </x:c>
       <x:c r="DU11" s="106" t="str">
         <x:v>有効</x:v>
@@ -4989,6 +5182,7 @@
       <x:c r="DW11" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX11" s="109"/>
     </x:row>
     <x:row r="12" ht="25" customHeight="1">
       <x:c r="A12" s="9" t="str">
@@ -5315,8 +5509,8 @@
       <x:c r="DE12" s="45" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="DF12" s="77" t="str">
-        <x:v>#FFFFFFFF</x:v>
+      <x:c r="DF12" s="131" t="str">
+        <x:v>#C18AFFCC</x:v>
       </x:c>
       <x:c r="DG12" s="45" t="n">
         <x:v>60</x:v>
@@ -5345,8 +5539,8 @@
       <x:c r="DQ12" s="88"/>
       <x:c r="DR12" s="88"/>
       <x:c r="DS12" s="88"/>
-      <x:c r="DT12" s="100" t="n">
-        <x:v>11</x:v>
+      <x:c r="DT12" s="100" t="str">
+        <x:v>魔方陣</x:v>
       </x:c>
       <x:c r="DU12" s="106" t="str">
         <x:v>有効</x:v>
@@ -5357,6 +5551,7 @@
       <x:c r="DW12" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX12" s="109"/>
     </x:row>
     <x:row r="13" ht="25" customHeight="1">
       <x:c r="A13" s="9" t="str">
@@ -5683,8 +5878,8 @@
       <x:c r="DE13" s="45" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="DF13" s="77" t="str">
-        <x:v>#FFFFFFFF</x:v>
+      <x:c r="DF13" s="133" t="str">
+        <x:v>#BD70FFFF</x:v>
       </x:c>
       <x:c r="DG13" s="45" t="n">
         <x:v>60</x:v>
@@ -5713,8 +5908,8 @@
       <x:c r="DQ13" s="88"/>
       <x:c r="DR13" s="88"/>
       <x:c r="DS13" s="88"/>
-      <x:c r="DT13" s="100" t="n">
-        <x:v>12</x:v>
+      <x:c r="DT13" s="100" t="str">
+        <x:v>光の弾</x:v>
       </x:c>
       <x:c r="DU13" s="106" t="str">
         <x:v>有効</x:v>
@@ -5725,6 +5920,7 @@
       <x:c r="DW13" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX13" s="109"/>
     </x:row>
     <x:row r="14" ht="25" customHeight="1">
       <x:c r="A14" s="10" t="str">
@@ -5890,6 +6086,7 @@
       <x:c r="DU14" s="106"/>
       <x:c r="DV14" s="106"/>
       <x:c r="DW14" s="106"/>
+      <x:c r="DX14" s="109"/>
     </x:row>
     <x:row r="15" ht="25" customHeight="1">
       <x:c r="A15" s="10" t="str">
@@ -6055,6 +6252,7 @@
       <x:c r="DU15" s="106"/>
       <x:c r="DV15" s="106"/>
       <x:c r="DW15" s="106"/>
+      <x:c r="DX15" s="109"/>
     </x:row>
     <x:row r="16" ht="25" customHeight="1">
       <x:c r="A16" s="10" t="str">
@@ -6220,6 +6418,7 @@
       <x:c r="DU16" s="106"/>
       <x:c r="DV16" s="106"/>
       <x:c r="DW16" s="106"/>
+      <x:c r="DX16" s="109"/>
     </x:row>
     <x:row r="17" ht="25" customHeight="1">
       <x:c r="A17" s="10" t="str">
@@ -6385,6 +6584,7 @@
       <x:c r="DU17" s="106"/>
       <x:c r="DV17" s="106"/>
       <x:c r="DW17" s="106"/>
+      <x:c r="DX17" s="109"/>
     </x:row>
     <x:row r="18" ht="25" customHeight="1">
       <x:c r="A18" s="10" t="str">
@@ -6550,6 +6750,7 @@
       <x:c r="DU18" s="106"/>
       <x:c r="DV18" s="106"/>
       <x:c r="DW18" s="106"/>
+      <x:c r="DX18" s="109"/>
     </x:row>
     <x:row r="19" ht="25" customHeight="1">
       <x:c r="A19" s="10" t="str">
@@ -6715,6 +6916,7 @@
       <x:c r="DU19" s="106"/>
       <x:c r="DV19" s="106"/>
       <x:c r="DW19" s="106"/>
+      <x:c r="DX19" s="109"/>
     </x:row>
     <x:row r="20" ht="25" customHeight="1">
       <x:c r="A20" s="10" t="str">
@@ -6880,6 +7082,7 @@
       <x:c r="DU20" s="106"/>
       <x:c r="DV20" s="106"/>
       <x:c r="DW20" s="106"/>
+      <x:c r="DX20" s="109"/>
     </x:row>
     <x:row r="21" ht="25" customHeight="1">
       <x:c r="A21" s="10" t="str">
@@ -7045,6 +7248,7 @@
       <x:c r="DU21" s="106"/>
       <x:c r="DV21" s="106"/>
       <x:c r="DW21" s="106"/>
+      <x:c r="DX21" s="109"/>
     </x:row>
     <x:row r="22" ht="25" customHeight="1">
       <x:c r="A22" s="10" t="str">
@@ -7210,6 +7414,7 @@
       <x:c r="DU22" s="106"/>
       <x:c r="DV22" s="106"/>
       <x:c r="DW22" s="106"/>
+      <x:c r="DX22" s="109"/>
     </x:row>
     <x:row r="23" ht="25" customHeight="1">
       <x:c r="A23" s="10" t="str">
@@ -7375,6 +7580,7 @@
       <x:c r="DU23" s="106"/>
       <x:c r="DV23" s="106"/>
       <x:c r="DW23" s="106"/>
+      <x:c r="DX23" s="109"/>
     </x:row>
     <x:row r="24" ht="25" customHeight="1">
       <x:c r="A24" s="10" t="str">
@@ -7540,6 +7746,7 @@
       <x:c r="DU24" s="106"/>
       <x:c r="DV24" s="106"/>
       <x:c r="DW24" s="106"/>
+      <x:c r="DX24" s="109"/>
     </x:row>
     <x:row r="25" ht="25" customHeight="1">
       <x:c r="A25" s="10" t="str">
@@ -7705,6 +7912,7 @@
       <x:c r="DU25" s="106"/>
       <x:c r="DV25" s="106"/>
       <x:c r="DW25" s="106"/>
+      <x:c r="DX25" s="109"/>
     </x:row>
     <x:row r="26" ht="25" customHeight="1">
       <x:c r="A26" s="10" t="str">
@@ -7870,6 +8078,7 @@
       <x:c r="DU26" s="106"/>
       <x:c r="DV26" s="106"/>
       <x:c r="DW26" s="106"/>
+      <x:c r="DX26" s="109"/>
     </x:row>
     <x:row r="27" ht="25" customHeight="1">
       <x:c r="A27" s="10" t="str">
@@ -8035,6 +8244,7 @@
       <x:c r="DU27" s="106"/>
       <x:c r="DV27" s="106"/>
       <x:c r="DW27" s="106"/>
+      <x:c r="DX27" s="109"/>
     </x:row>
     <x:row r="28" ht="25" customHeight="1">
       <x:c r="A28" s="10" t="str">
@@ -8200,6 +8410,7 @@
       <x:c r="DU28" s="106"/>
       <x:c r="DV28" s="106"/>
       <x:c r="DW28" s="106"/>
+      <x:c r="DX28" s="109"/>
     </x:row>
     <x:row r="29" ht="25" customHeight="1">
       <x:c r="A29" s="10" t="str">
@@ -8365,6 +8576,7 @@
       <x:c r="DU29" s="106"/>
       <x:c r="DV29" s="106"/>
       <x:c r="DW29" s="106"/>
+      <x:c r="DX29" s="109"/>
     </x:row>
     <x:row r="30" ht="25" customHeight="1">
       <x:c r="A30" s="10" t="str">
@@ -8530,6 +8742,7 @@
       <x:c r="DU30" s="106"/>
       <x:c r="DV30" s="106"/>
       <x:c r="DW30" s="106"/>
+      <x:c r="DX30" s="109"/>
     </x:row>
     <x:row r="31" ht="25" customHeight="1">
       <x:c r="A31" s="10" t="str">
@@ -8695,6 +8908,7 @@
       <x:c r="DU31" s="106"/>
       <x:c r="DV31" s="106"/>
       <x:c r="DW31" s="106"/>
+      <x:c r="DX31" s="109"/>
     </x:row>
     <x:row r="32" ht="25" customHeight="1">
       <x:c r="A32" s="10" t="str">
@@ -8860,6 +9074,7 @@
       <x:c r="DU32" s="106"/>
       <x:c r="DV32" s="106"/>
       <x:c r="DW32" s="106"/>
+      <x:c r="DX32" s="109"/>
     </x:row>
     <x:row r="33" ht="25" customHeight="1">
       <x:c r="A33" s="10" t="str">
@@ -9025,6 +9240,7 @@
       <x:c r="DU33" s="106"/>
       <x:c r="DV33" s="106"/>
       <x:c r="DW33" s="106"/>
+      <x:c r="DX33" s="109"/>
     </x:row>
     <x:row r="34" ht="25" customHeight="1">
       <x:c r="A34" s="10" t="str">
@@ -9190,6 +9406,7 @@
       <x:c r="DU34" s="106"/>
       <x:c r="DV34" s="106"/>
       <x:c r="DW34" s="106"/>
+      <x:c r="DX34" s="109"/>
     </x:row>
     <x:row r="35" ht="25" customHeight="1">
       <x:c r="A35" s="10" t="str">
@@ -9355,6 +9572,7 @@
       <x:c r="DU35" s="106"/>
       <x:c r="DV35" s="106"/>
       <x:c r="DW35" s="106"/>
+      <x:c r="DX35" s="109"/>
     </x:row>
     <x:row r="36" ht="25" customHeight="1">
       <x:c r="A36" s="10" t="str">
@@ -9520,6 +9738,7 @@
       <x:c r="DU36" s="106"/>
       <x:c r="DV36" s="106"/>
       <x:c r="DW36" s="106"/>
+      <x:c r="DX36" s="109"/>
     </x:row>
     <x:row r="37" ht="25" customHeight="1">
       <x:c r="A37" s="10" t="str">
@@ -9685,6 +9904,7 @@
       <x:c r="DU37" s="106"/>
       <x:c r="DV37" s="106"/>
       <x:c r="DW37" s="106"/>
+      <x:c r="DX37" s="109"/>
     </x:row>
     <x:row r="38" ht="25" customHeight="1">
       <x:c r="A38" s="10" t="str">
@@ -9850,6 +10070,7 @@
       <x:c r="DU38" s="106"/>
       <x:c r="DV38" s="106"/>
       <x:c r="DW38" s="106"/>
+      <x:c r="DX38" s="109"/>
     </x:row>
     <x:row r="39" ht="25" customHeight="1">
       <x:c r="A39" s="10" t="str">
@@ -10015,6 +10236,7 @@
       <x:c r="DU39" s="106"/>
       <x:c r="DV39" s="106"/>
       <x:c r="DW39" s="106"/>
+      <x:c r="DX39" s="109"/>
     </x:row>
     <x:row r="40" ht="25" customHeight="1">
       <x:c r="A40" s="93" t="str">
@@ -10341,8 +10563,8 @@
       <x:c r="DE40" s="90" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="DF40" s="90" t="str">
-        <x:v>#B4ECFFFF</x:v>
+      <x:c r="DF40" s="135" t="str">
+        <x:v>#FFE6A6FF</x:v>
       </x:c>
       <x:c r="DG40" s="90" t="n">
         <x:v>60</x:v>
@@ -10383,8 +10605,8 @@
       <x:c r="DS40" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="DT40" s="100" t="n">
-        <x:v>3</x:v>
+      <x:c r="DT40" s="100" t="str">
+        <x:v>衝撃波</x:v>
       </x:c>
       <x:c r="DU40" s="106" t="str">
         <x:v>有効</x:v>
@@ -10395,6 +10617,7 @@
       <x:c r="DW40" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX40" s="109"/>
     </x:row>
     <x:row r="41" ht="25" customHeight="1">
       <x:c r="A41" s="93" t="str">
@@ -10721,8 +10944,8 @@
       <x:c r="DE41" s="90" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="DF41" s="90" t="str">
-        <x:v>#FFAA66FF</x:v>
+      <x:c r="DF41" s="137" t="str">
+        <x:v>#FF6B38CC</x:v>
       </x:c>
       <x:c r="DG41" s="90" t="n">
         <x:v>60</x:v>
@@ -10763,8 +10986,8 @@
       <x:c r="DS41" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="DT41" s="100" t="n">
-        <x:v>7</x:v>
+      <x:c r="DT41" s="100" t="str">
+        <x:v>魔方陣</x:v>
       </x:c>
       <x:c r="DU41" s="106" t="str">
         <x:v>有効</x:v>
@@ -10775,6 +10998,7 @@
       <x:c r="DW41" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX41" s="109"/>
     </x:row>
     <x:row r="42" ht="25" customHeight="1">
       <x:c r="A42" s="93" t="str">
@@ -11101,8 +11325,8 @@
       <x:c r="DE42" s="90" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="DF42" s="90" t="str">
-        <x:v>#8AFFBFFF</x:v>
+      <x:c r="DF42" s="139" t="str">
+        <x:v>#70FFACB3</x:v>
       </x:c>
       <x:c r="DG42" s="90" t="n">
         <x:v>60</x:v>
@@ -11143,8 +11367,8 @@
       <x:c r="DS42" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="DT42" s="100" t="n">
-        <x:v>2</x:v>
+      <x:c r="DT42" s="100" t="str">
+        <x:v>魔方陣</x:v>
       </x:c>
       <x:c r="DU42" s="106" t="str">
         <x:v>有効</x:v>
@@ -11155,6 +11379,7 @@
       <x:c r="DW42" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX42" s="109"/>
     </x:row>
     <x:row r="43" ht="25" customHeight="1">
       <x:c r="A43" s="93" t="str">
@@ -11481,8 +11706,8 @@
       <x:c r="DE43" s="90" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="DF43" s="90" t="str">
-        <x:v>#BDA8FFFF</x:v>
+      <x:c r="DF43" s="141" t="str">
+        <x:v>#83BCFFB3</x:v>
       </x:c>
       <x:c r="DG43" s="90" t="n">
         <x:v>60</x:v>
@@ -11523,8 +11748,8 @@
       <x:c r="DS43" s="88" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="DT43" s="100" t="n">
-        <x:v>4</x:v>
+      <x:c r="DT43" s="100" t="str">
+        <x:v>魔方陣</x:v>
       </x:c>
       <x:c r="DU43" s="106" t="str">
         <x:v>有効</x:v>
@@ -11535,6 +11760,7 @@
       <x:c r="DW43" s="106" t="n">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="DX43" s="109"/>
     </x:row>
     <x:row r="44" ht="25" customHeight="1">
       <x:c r="A44" s="10"/>
@@ -11624,6 +11850,7 @@
       <x:c r="DU44" s="106"/>
       <x:c r="DV44" s="106"/>
       <x:c r="DW44" s="106"/>
+      <x:c r="DX44" s="109"/>
     </x:row>
     <x:row r="45" ht="25" customHeight="1">
       <x:c r="A45" s="10"/>
@@ -11713,6 +11940,7 @@
       <x:c r="DU45" s="106"/>
       <x:c r="DV45" s="106"/>
       <x:c r="DW45" s="106"/>
+      <x:c r="DX45" s="109"/>
     </x:row>
     <x:row r="46" ht="25" customHeight="1">
       <x:c r="A46" s="10"/>
@@ -11802,6 +12030,7 @@
       <x:c r="DU46" s="106"/>
       <x:c r="DV46" s="106"/>
       <x:c r="DW46" s="106"/>
+      <x:c r="DX46" s="109"/>
     </x:row>
     <x:row r="47" ht="25" customHeight="1">
       <x:c r="A47" s="10"/>
@@ -11891,6 +12120,7 @@
       <x:c r="DU47" s="106"/>
       <x:c r="DV47" s="106"/>
       <x:c r="DW47" s="106"/>
+      <x:c r="DX47" s="109"/>
     </x:row>
     <x:row r="48" ht="25" customHeight="1">
       <x:c r="A48" s="10"/>
@@ -11980,6 +12210,7 @@
       <x:c r="DU48" s="106"/>
       <x:c r="DV48" s="106"/>
       <x:c r="DW48" s="106"/>
+      <x:c r="DX48" s="109"/>
     </x:row>
     <x:row r="49" ht="25" customHeight="1">
       <x:c r="A49" s="10"/>
@@ -12069,6 +12300,7 @@
       <x:c r="DU49" s="106"/>
       <x:c r="DV49" s="106"/>
       <x:c r="DW49" s="106"/>
+      <x:c r="DX49" s="109"/>
     </x:row>
     <x:row r="50" ht="25" customHeight="1">
       <x:c r="A50" s="10"/>
@@ -12158,6 +12390,7 @@
       <x:c r="DU50" s="106"/>
       <x:c r="DV50" s="106"/>
       <x:c r="DW50" s="106"/>
+      <x:c r="DX50" s="109"/>
     </x:row>
     <x:row r="51" ht="25" customHeight="1">
       <x:c r="A51" s="10"/>
@@ -12247,6 +12480,7 @@
       <x:c r="DU51" s="106"/>
       <x:c r="DV51" s="106"/>
       <x:c r="DW51" s="106"/>
+      <x:c r="DX51" s="109"/>
     </x:row>
     <x:row r="52" ht="25" customHeight="1">
       <x:c r="A52" s="10"/>
@@ -12336,6 +12570,7 @@
       <x:c r="DU52" s="106"/>
       <x:c r="DV52" s="106"/>
       <x:c r="DW52" s="106"/>
+      <x:c r="DX52" s="109"/>
     </x:row>
     <x:row r="53" ht="25" customHeight="1">
       <x:c r="A53" s="10"/>
@@ -12425,6 +12660,7 @@
       <x:c r="DU53" s="106"/>
       <x:c r="DV53" s="106"/>
       <x:c r="DW53" s="106"/>
+      <x:c r="DX53" s="109"/>
     </x:row>
     <x:row r="54" ht="25" customHeight="1">
       <x:c r="A54" s="10"/>
@@ -12514,6 +12750,7 @@
       <x:c r="DU54" s="106"/>
       <x:c r="DV54" s="106"/>
       <x:c r="DW54" s="106"/>
+      <x:c r="DX54" s="109"/>
     </x:row>
     <x:row r="55" ht="25" customHeight="1">
       <x:c r="A55" s="10"/>
@@ -12603,6 +12840,7 @@
       <x:c r="DU55" s="106"/>
       <x:c r="DV55" s="106"/>
       <x:c r="DW55" s="106"/>
+      <x:c r="DX55" s="109"/>
     </x:row>
     <x:row r="56" ht="25" customHeight="1">
       <x:c r="A56" s="10"/>
@@ -12692,6 +12930,7 @@
       <x:c r="DU56" s="106"/>
       <x:c r="DV56" s="106"/>
       <x:c r="DW56" s="106"/>
+      <x:c r="DX56" s="109"/>
     </x:row>
     <x:row r="57" ht="25" customHeight="1">
       <x:c r="A57" s="10"/>
@@ -12781,6 +13020,7 @@
       <x:c r="DU57" s="106"/>
       <x:c r="DV57" s="106"/>
       <x:c r="DW57" s="106"/>
+      <x:c r="DX57" s="109"/>
     </x:row>
     <x:row r="58" ht="25" customHeight="1">
       <x:c r="A58" s="10"/>
@@ -12870,6 +13110,7 @@
       <x:c r="DU58" s="106"/>
       <x:c r="DV58" s="106"/>
       <x:c r="DW58" s="106"/>
+      <x:c r="DX58" s="109"/>
     </x:row>
     <x:row r="59" ht="25" customHeight="1">
       <x:c r="A59" s="10"/>
@@ -12959,6 +13200,7 @@
       <x:c r="DU59" s="106"/>
       <x:c r="DV59" s="106"/>
       <x:c r="DW59" s="106"/>
+      <x:c r="DX59" s="109"/>
     </x:row>
     <x:row r="60" ht="25" customHeight="1">
       <x:c r="A60" s="10"/>
@@ -13048,6 +13290,7 @@
       <x:c r="DU60" s="106"/>
       <x:c r="DV60" s="106"/>
       <x:c r="DW60" s="106"/>
+      <x:c r="DX60" s="109"/>
     </x:row>
     <x:row r="61" ht="25" customHeight="1">
       <x:c r="A61" s="10"/>
@@ -13137,6 +13380,7 @@
       <x:c r="DU61" s="106"/>
       <x:c r="DV61" s="106"/>
       <x:c r="DW61" s="106"/>
+      <x:c r="DX61" s="109"/>
     </x:row>
     <x:row r="62" ht="25" customHeight="1">
       <x:c r="A62" s="10"/>
@@ -13226,6 +13470,7 @@
       <x:c r="DU62" s="106"/>
       <x:c r="DV62" s="106"/>
       <x:c r="DW62" s="106"/>
+      <x:c r="DX62" s="109"/>
     </x:row>
     <x:row r="63" ht="25" customHeight="1">
       <x:c r="A63" s="10"/>
@@ -13315,6 +13560,7 @@
       <x:c r="DU63" s="106"/>
       <x:c r="DV63" s="106"/>
       <x:c r="DW63" s="106"/>
+      <x:c r="DX63" s="109"/>
     </x:row>
     <x:row r="64" ht="25" customHeight="1">
       <x:c r="A64" s="10"/>
@@ -13404,6 +13650,7 @@
       <x:c r="DU64" s="106"/>
       <x:c r="DV64" s="106"/>
       <x:c r="DW64" s="106"/>
+      <x:c r="DX64" s="109"/>
     </x:row>
     <x:row r="65" ht="25" customHeight="1">
       <x:c r="A65" s="10"/>
@@ -13493,6 +13740,7 @@
       <x:c r="DU65" s="106"/>
       <x:c r="DV65" s="106"/>
       <x:c r="DW65" s="106"/>
+      <x:c r="DX65" s="109"/>
     </x:row>
     <x:row r="66" ht="25" customHeight="1">
       <x:c r="A66" s="10"/>
@@ -13582,6 +13830,7 @@
       <x:c r="DU66" s="106"/>
       <x:c r="DV66" s="106"/>
       <x:c r="DW66" s="106"/>
+      <x:c r="DX66" s="109"/>
     </x:row>
     <x:row r="67" ht="25" customHeight="1">
       <x:c r="A67" s="10"/>
@@ -13671,6 +13920,7 @@
       <x:c r="DU67" s="106"/>
       <x:c r="DV67" s="106"/>
       <x:c r="DW67" s="106"/>
+      <x:c r="DX67" s="109"/>
     </x:row>
     <x:row r="68" ht="25" customHeight="1">
       <x:c r="A68" s="10"/>
@@ -13760,6 +14010,7 @@
       <x:c r="DU68" s="106"/>
       <x:c r="DV68" s="106"/>
       <x:c r="DW68" s="106"/>
+      <x:c r="DX68" s="109"/>
     </x:row>
     <x:row r="69" ht="25" customHeight="1">
       <x:c r="A69" s="10"/>
@@ -13849,6 +14100,7 @@
       <x:c r="DU69" s="106"/>
       <x:c r="DV69" s="106"/>
       <x:c r="DW69" s="106"/>
+      <x:c r="DX69" s="109"/>
     </x:row>
     <x:row r="70" ht="25" customHeight="1">
       <x:c r="A70" s="10"/>
@@ -13938,6 +14190,7 @@
       <x:c r="DU70" s="106"/>
       <x:c r="DV70" s="106"/>
       <x:c r="DW70" s="106"/>
+      <x:c r="DX70" s="109"/>
     </x:row>
     <x:row r="71" ht="25" customHeight="1">
       <x:c r="A71" s="10"/>
@@ -14027,6 +14280,7 @@
       <x:c r="DU71" s="106"/>
       <x:c r="DV71" s="106"/>
       <x:c r="DW71" s="106"/>
+      <x:c r="DX71" s="109"/>
     </x:row>
     <x:row r="72" ht="25" customHeight="1">
       <x:c r="A72" s="10"/>
@@ -14116,6 +14370,7 @@
       <x:c r="DU72" s="106"/>
       <x:c r="DV72" s="106"/>
       <x:c r="DW72" s="106"/>
+      <x:c r="DX72" s="109"/>
     </x:row>
     <x:row r="73" ht="25" customHeight="1">
       <x:c r="A73" s="10"/>
@@ -14205,6 +14460,7 @@
       <x:c r="DU73" s="106"/>
       <x:c r="DV73" s="106"/>
       <x:c r="DW73" s="106"/>
+      <x:c r="DX73" s="109"/>
     </x:row>
     <x:row r="74" ht="25" customHeight="1">
       <x:c r="A74" s="10"/>
@@ -14294,6 +14550,7 @@
       <x:c r="DU74" s="106"/>
       <x:c r="DV74" s="106"/>
       <x:c r="DW74" s="106"/>
+      <x:c r="DX74" s="109"/>
     </x:row>
     <x:row r="75" ht="25" customHeight="1">
       <x:c r="A75" s="10"/>
@@ -14383,6 +14640,7 @@
       <x:c r="DU75" s="106"/>
       <x:c r="DV75" s="106"/>
       <x:c r="DW75" s="106"/>
+      <x:c r="DX75" s="109"/>
     </x:row>
     <x:row r="76" ht="25" customHeight="1">
       <x:c r="A76" s="10"/>
@@ -14472,6 +14730,7 @@
       <x:c r="DU76" s="106"/>
       <x:c r="DV76" s="106"/>
       <x:c r="DW76" s="106"/>
+      <x:c r="DX76" s="109"/>
     </x:row>
     <x:row r="77" ht="25" customHeight="1">
       <x:c r="A77" s="10"/>
@@ -14561,6 +14820,7 @@
       <x:c r="DU77" s="106"/>
       <x:c r="DV77" s="106"/>
       <x:c r="DW77" s="106"/>
+      <x:c r="DX77" s="109"/>
     </x:row>
     <x:row r="78" ht="25" customHeight="1">
       <x:c r="A78" s="10"/>
@@ -14650,6 +14910,7 @@
       <x:c r="DU78" s="106"/>
       <x:c r="DV78" s="106"/>
       <x:c r="DW78" s="106"/>
+      <x:c r="DX78" s="109"/>
     </x:row>
     <x:row r="79" ht="25" customHeight="1">
       <x:c r="A79" s="10"/>
@@ -14739,6 +15000,7 @@
       <x:c r="DU79" s="106"/>
       <x:c r="DV79" s="106"/>
       <x:c r="DW79" s="106"/>
+      <x:c r="DX79" s="109"/>
     </x:row>
     <x:row r="80" ht="25" customHeight="1">
       <x:c r="A80" s="10"/>
@@ -14828,6 +15090,7 @@
       <x:c r="DU80" s="106"/>
       <x:c r="DV80" s="106"/>
       <x:c r="DW80" s="106"/>
+      <x:c r="DX80" s="109"/>
     </x:row>
     <x:row r="81" ht="25" customHeight="1">
       <x:c r="A81" s="10"/>
@@ -14917,6 +15180,7 @@
       <x:c r="DU81" s="106"/>
       <x:c r="DV81" s="106"/>
       <x:c r="DW81" s="106"/>
+      <x:c r="DX81" s="109"/>
     </x:row>
     <x:row r="82" ht="25" customHeight="1">
       <x:c r="A82" s="10"/>
@@ -15006,6 +15270,7 @@
       <x:c r="DU82" s="106"/>
       <x:c r="DV82" s="106"/>
       <x:c r="DW82" s="106"/>
+      <x:c r="DX82" s="109"/>
     </x:row>
     <x:row r="83" ht="25" customHeight="1">
       <x:c r="A83" s="10"/>
@@ -15095,6 +15360,7 @@
       <x:c r="DU83" s="106"/>
       <x:c r="DV83" s="106"/>
       <x:c r="DW83" s="106"/>
+      <x:c r="DX83" s="109"/>
     </x:row>
     <x:row r="84" ht="25" customHeight="1">
       <x:c r="A84" s="10"/>
@@ -15184,6 +15450,7 @@
       <x:c r="DU84" s="106"/>
       <x:c r="DV84" s="106"/>
       <x:c r="DW84" s="106"/>
+      <x:c r="DX84" s="109"/>
     </x:row>
     <x:row r="85" ht="25" customHeight="1">
       <x:c r="A85" s="10"/>
@@ -15273,6 +15540,7 @@
       <x:c r="DU85" s="106"/>
       <x:c r="DV85" s="106"/>
       <x:c r="DW85" s="106"/>
+      <x:c r="DX85" s="109"/>
     </x:row>
     <x:row r="86" ht="25" customHeight="1">
       <x:c r="A86" s="10"/>
@@ -15362,6 +15630,7 @@
       <x:c r="DU86" s="106"/>
       <x:c r="DV86" s="106"/>
       <x:c r="DW86" s="106"/>
+      <x:c r="DX86" s="109"/>
     </x:row>
     <x:row r="87" ht="25" customHeight="1">
       <x:c r="A87" s="10"/>
@@ -15451,6 +15720,7 @@
       <x:c r="DU87" s="106"/>
       <x:c r="DV87" s="106"/>
       <x:c r="DW87" s="106"/>
+      <x:c r="DX87" s="109"/>
     </x:row>
     <x:row r="88" ht="25" customHeight="1">
       <x:c r="A88" s="10"/>
@@ -15540,6 +15810,7 @@
       <x:c r="DU88" s="106"/>
       <x:c r="DV88" s="106"/>
       <x:c r="DW88" s="106"/>
+      <x:c r="DX88" s="109"/>
     </x:row>
     <x:row r="89" ht="25" customHeight="1">
       <x:c r="A89" s="10"/>
@@ -15629,6 +15900,7 @@
       <x:c r="DU89" s="106"/>
       <x:c r="DV89" s="106"/>
       <x:c r="DW89" s="106"/>
+      <x:c r="DX89" s="109"/>
     </x:row>
     <x:row r="90" ht="25" customHeight="1">
       <x:c r="A90" s="10"/>
@@ -15718,6 +15990,7 @@
       <x:c r="DU90" s="106"/>
       <x:c r="DV90" s="106"/>
       <x:c r="DW90" s="106"/>
+      <x:c r="DX90" s="109"/>
     </x:row>
     <x:row r="91" ht="25" customHeight="1">
       <x:c r="A91" s="10"/>
@@ -15807,6 +16080,7 @@
       <x:c r="DU91" s="106"/>
       <x:c r="DV91" s="106"/>
       <x:c r="DW91" s="106"/>
+      <x:c r="DX91" s="109"/>
     </x:row>
     <x:row r="92" ht="25" customHeight="1">
       <x:c r="A92" s="10"/>
@@ -15896,6 +16170,7 @@
       <x:c r="DU92" s="106"/>
       <x:c r="DV92" s="106"/>
       <x:c r="DW92" s="106"/>
+      <x:c r="DX92" s="109"/>
     </x:row>
     <x:row r="93" ht="25" customHeight="1">
       <x:c r="A93" s="10"/>
@@ -15985,6 +16260,7 @@
       <x:c r="DU93" s="106"/>
       <x:c r="DV93" s="106"/>
       <x:c r="DW93" s="106"/>
+      <x:c r="DX93" s="109"/>
     </x:row>
     <x:row r="94" ht="25" customHeight="1">
       <x:c r="A94" s="10"/>
@@ -16074,6 +16350,7 @@
       <x:c r="DU94" s="106"/>
       <x:c r="DV94" s="106"/>
       <x:c r="DW94" s="106"/>
+      <x:c r="DX94" s="109"/>
     </x:row>
     <x:row r="95" ht="25" customHeight="1">
       <x:c r="A95" s="10"/>
@@ -16163,6 +16440,7 @@
       <x:c r="DU95" s="106"/>
       <x:c r="DV95" s="106"/>
       <x:c r="DW95" s="106"/>
+      <x:c r="DX95" s="109"/>
     </x:row>
     <x:row r="96" ht="25" customHeight="1">
       <x:c r="A96" s="10"/>
@@ -16252,6 +16530,7 @@
       <x:c r="DU96" s="106"/>
       <x:c r="DV96" s="106"/>
       <x:c r="DW96" s="106"/>
+      <x:c r="DX96" s="109"/>
     </x:row>
     <x:row r="97" ht="25" customHeight="1">
       <x:c r="A97" s="10"/>
@@ -16341,6 +16620,7 @@
       <x:c r="DU97" s="106"/>
       <x:c r="DV97" s="106"/>
       <x:c r="DW97" s="106"/>
+      <x:c r="DX97" s="109"/>
     </x:row>
     <x:row r="98" ht="25" customHeight="1">
       <x:c r="A98" s="10"/>
@@ -16430,6 +16710,7 @@
       <x:c r="DU98" s="106"/>
       <x:c r="DV98" s="106"/>
       <x:c r="DW98" s="106"/>
+      <x:c r="DX98" s="109"/>
     </x:row>
     <x:row r="99" ht="25" customHeight="1">
       <x:c r="A99" s="10"/>
@@ -16519,6 +16800,7 @@
       <x:c r="DU99" s="106"/>
       <x:c r="DV99" s="106"/>
       <x:c r="DW99" s="106"/>
+      <x:c r="DX99" s="109"/>
     </x:row>
     <x:row r="100" ht="25" customHeight="1">
       <x:c r="A100" s="10"/>
@@ -16608,6 +16890,7 @@
       <x:c r="DU100" s="106"/>
       <x:c r="DV100" s="106"/>
       <x:c r="DW100" s="106"/>
+      <x:c r="DX100" s="109"/>
     </x:row>
     <x:row r="101" ht="25" customHeight="1">
       <x:c r="A101" s="10"/>
@@ -16697,6 +16980,7 @@
       <x:c r="DU101" s="106"/>
       <x:c r="DV101" s="106"/>
       <x:c r="DW101" s="106"/>
+      <x:c r="DX101" s="109"/>
     </x:row>
     <x:row r="102" ht="25" customHeight="1">
       <x:c r="A102" s="10"/>
@@ -16786,6 +17070,7 @@
       <x:c r="DU102" s="106"/>
       <x:c r="DV102" s="106"/>
       <x:c r="DW102" s="106"/>
+      <x:c r="DX102" s="109"/>
     </x:row>
     <x:row r="103" ht="25" customHeight="1">
       <x:c r="A103" s="10"/>
@@ -16875,6 +17160,7 @@
       <x:c r="DU103" s="106"/>
       <x:c r="DV103" s="106"/>
       <x:c r="DW103" s="106"/>
+      <x:c r="DX103" s="109"/>
     </x:row>
     <x:row r="104" ht="25" customHeight="1">
       <x:c r="A104" s="10"/>
@@ -16964,6 +17250,7 @@
       <x:c r="DU104" s="106"/>
       <x:c r="DV104" s="106"/>
       <x:c r="DW104" s="106"/>
+      <x:c r="DX104" s="109"/>
     </x:row>
     <x:row r="105" ht="25" customHeight="1">
       <x:c r="A105" s="10"/>
@@ -17053,6 +17340,7 @@
       <x:c r="DU105" s="106"/>
       <x:c r="DV105" s="106"/>
       <x:c r="DW105" s="106"/>
+      <x:c r="DX105" s="109"/>
     </x:row>
     <x:row r="106" ht="25" customHeight="1">
       <x:c r="A106" s="10"/>
@@ -17142,6 +17430,7 @@
       <x:c r="DU106" s="106"/>
       <x:c r="DV106" s="106"/>
       <x:c r="DW106" s="106"/>
+      <x:c r="DX106" s="109"/>
     </x:row>
     <x:row r="107" ht="25" customHeight="1">
       <x:c r="A107" s="10"/>
@@ -17231,6 +17520,7 @@
       <x:c r="DU107" s="106"/>
       <x:c r="DV107" s="106"/>
       <x:c r="DW107" s="106"/>
+      <x:c r="DX107" s="109"/>
     </x:row>
     <x:row r="108" ht="25" customHeight="1">
       <x:c r="A108" s="10"/>
@@ -17320,6 +17610,7 @@
       <x:c r="DU108" s="106"/>
       <x:c r="DV108" s="106"/>
       <x:c r="DW108" s="106"/>
+      <x:c r="DX108" s="109"/>
     </x:row>
     <x:row r="109" ht="25" customHeight="1">
       <x:c r="A109" s="10"/>
@@ -17409,6 +17700,7 @@
       <x:c r="DU109" s="106"/>
       <x:c r="DV109" s="106"/>
       <x:c r="DW109" s="106"/>
+      <x:c r="DX109" s="109"/>
     </x:row>
     <x:row r="110" ht="25" customHeight="1">
       <x:c r="A110" s="10"/>
@@ -17498,6 +17790,7 @@
       <x:c r="DU110" s="106"/>
       <x:c r="DV110" s="106"/>
       <x:c r="DW110" s="106"/>
+      <x:c r="DX110" s="109"/>
     </x:row>
     <x:row r="111" ht="25" customHeight="1">
       <x:c r="A111" s="10"/>
@@ -17587,6 +17880,7 @@
       <x:c r="DU111" s="106"/>
       <x:c r="DV111" s="106"/>
       <x:c r="DW111" s="106"/>
+      <x:c r="DX111" s="109"/>
     </x:row>
     <x:row r="112" ht="25" customHeight="1">
       <x:c r="A112" s="10"/>
@@ -17676,6 +17970,7 @@
       <x:c r="DU112" s="106"/>
       <x:c r="DV112" s="106"/>
       <x:c r="DW112" s="106"/>
+      <x:c r="DX112" s="109"/>
     </x:row>
     <x:row r="113" ht="25" customHeight="1">
       <x:c r="A113" s="10"/>
@@ -17765,6 +18060,7 @@
       <x:c r="DU113" s="106"/>
       <x:c r="DV113" s="106"/>
       <x:c r="DW113" s="106"/>
+      <x:c r="DX113" s="109"/>
     </x:row>
     <x:row r="114" ht="25" customHeight="1">
       <x:c r="A114" s="10"/>
@@ -17854,6 +18150,7 @@
       <x:c r="DU114" s="106"/>
       <x:c r="DV114" s="106"/>
       <x:c r="DW114" s="106"/>
+      <x:c r="DX114" s="109"/>
     </x:row>
     <x:row r="115" ht="25" customHeight="1">
       <x:c r="A115" s="10"/>
@@ -17943,6 +18240,7 @@
       <x:c r="DU115" s="106"/>
       <x:c r="DV115" s="106"/>
       <x:c r="DW115" s="106"/>
+      <x:c r="DX115" s="109"/>
     </x:row>
     <x:row r="116" ht="25" customHeight="1">
       <x:c r="A116" s="10"/>
@@ -18032,6 +18330,7 @@
       <x:c r="DU116" s="106"/>
       <x:c r="DV116" s="106"/>
       <x:c r="DW116" s="106"/>
+      <x:c r="DX116" s="109"/>
     </x:row>
     <x:row r="117" ht="25" customHeight="1">
       <x:c r="A117" s="10"/>
@@ -18121,6 +18420,7 @@
       <x:c r="DU117" s="106"/>
       <x:c r="DV117" s="106"/>
       <x:c r="DW117" s="106"/>
+      <x:c r="DX117" s="109"/>
     </x:row>
     <x:row r="118" ht="25" customHeight="1">
       <x:c r="A118" s="10"/>
@@ -18210,6 +18510,7 @@
       <x:c r="DU118" s="106"/>
       <x:c r="DV118" s="106"/>
       <x:c r="DW118" s="106"/>
+      <x:c r="DX118" s="109"/>
     </x:row>
     <x:row r="119" ht="25" customHeight="1">
       <x:c r="A119" s="10"/>
@@ -18299,6 +18600,7 @@
       <x:c r="DU119" s="106"/>
       <x:c r="DV119" s="106"/>
       <x:c r="DW119" s="106"/>
+      <x:c r="DX119" s="109"/>
     </x:row>
     <x:row r="120" ht="25" customHeight="1">
       <x:c r="A120" s="10"/>
@@ -18388,6 +18690,7 @@
       <x:c r="DU120" s="106"/>
       <x:c r="DV120" s="106"/>
       <x:c r="DW120" s="106"/>
+      <x:c r="DX120" s="109"/>
     </x:row>
     <x:row r="121" ht="25" customHeight="1">
       <x:c r="A121" s="10"/>
@@ -18477,6 +18780,7 @@
       <x:c r="DU121" s="106"/>
       <x:c r="DV121" s="106"/>
       <x:c r="DW121" s="106"/>
+      <x:c r="DX121" s="109"/>
     </x:row>
     <x:row r="122" ht="25" customHeight="1">
       <x:c r="A122" s="10"/>
@@ -18566,6 +18870,7 @@
       <x:c r="DU122" s="106"/>
       <x:c r="DV122" s="106"/>
       <x:c r="DW122" s="106"/>
+      <x:c r="DX122" s="109"/>
     </x:row>
     <x:row r="123" ht="25" customHeight="1">
       <x:c r="A123" s="10"/>
@@ -18655,6 +18960,7 @@
       <x:c r="DU123" s="106"/>
       <x:c r="DV123" s="106"/>
       <x:c r="DW123" s="106"/>
+      <x:c r="DX123" s="109"/>
     </x:row>
     <x:row r="124" ht="25" customHeight="1">
       <x:c r="A124" s="10"/>
@@ -18744,6 +19050,7 @@
       <x:c r="DU124" s="106"/>
       <x:c r="DV124" s="106"/>
       <x:c r="DW124" s="106"/>
+      <x:c r="DX124" s="109"/>
     </x:row>
     <x:row r="125" ht="25" customHeight="1">
       <x:c r="A125" s="10"/>
@@ -18833,6 +19140,7 @@
       <x:c r="DU125" s="106"/>
       <x:c r="DV125" s="106"/>
       <x:c r="DW125" s="106"/>
+      <x:c r="DX125" s="109"/>
     </x:row>
     <x:row r="126" ht="25" customHeight="1">
       <x:c r="A126" s="10"/>
@@ -18922,6 +19230,7 @@
       <x:c r="DU126" s="106"/>
       <x:c r="DV126" s="106"/>
       <x:c r="DW126" s="106"/>
+      <x:c r="DX126" s="109"/>
     </x:row>
     <x:row r="127" ht="25" customHeight="1">
       <x:c r="A127" s="10"/>
@@ -19011,6 +19320,7 @@
       <x:c r="DU127" s="106"/>
       <x:c r="DV127" s="106"/>
       <x:c r="DW127" s="106"/>
+      <x:c r="DX127" s="109"/>
     </x:row>
     <x:row r="128" ht="25" customHeight="1">
       <x:c r="A128" s="10"/>
@@ -19100,6 +19410,7 @@
       <x:c r="DU128" s="106"/>
       <x:c r="DV128" s="106"/>
       <x:c r="DW128" s="106"/>
+      <x:c r="DX128" s="109"/>
     </x:row>
     <x:row r="129" ht="25" customHeight="1">
       <x:c r="A129" s="10"/>
@@ -19189,6 +19500,7 @@
       <x:c r="DU129" s="106"/>
       <x:c r="DV129" s="106"/>
       <x:c r="DW129" s="106"/>
+      <x:c r="DX129" s="109"/>
     </x:row>
     <x:row r="130" ht="25" customHeight="1">
       <x:c r="A130" s="10"/>
@@ -19278,6 +19590,7 @@
       <x:c r="DU130" s="106"/>
       <x:c r="DV130" s="106"/>
       <x:c r="DW130" s="106"/>
+      <x:c r="DX130" s="109"/>
     </x:row>
     <x:row r="131" ht="25" customHeight="1">
       <x:c r="A131" s="10"/>
@@ -19367,6 +19680,7 @@
       <x:c r="DU131" s="106"/>
       <x:c r="DV131" s="106"/>
       <x:c r="DW131" s="106"/>
+      <x:c r="DX131" s="109"/>
     </x:row>
     <x:row r="132" ht="25" customHeight="1">
       <x:c r="A132" s="10"/>
@@ -19456,6 +19770,7 @@
       <x:c r="DU132" s="106"/>
       <x:c r="DV132" s="106"/>
       <x:c r="DW132" s="106"/>
+      <x:c r="DX132" s="109"/>
     </x:row>
     <x:row r="133" ht="25" customHeight="1">
       <x:c r="A133" s="10"/>
@@ -19545,6 +19860,7 @@
       <x:c r="DU133" s="106"/>
       <x:c r="DV133" s="106"/>
       <x:c r="DW133" s="106"/>
+      <x:c r="DX133" s="109"/>
     </x:row>
     <x:row r="134" ht="25" customHeight="1">
       <x:c r="A134" s="10"/>
@@ -19634,6 +19950,7 @@
       <x:c r="DU134" s="106"/>
       <x:c r="DV134" s="106"/>
       <x:c r="DW134" s="106"/>
+      <x:c r="DX134" s="109"/>
     </x:row>
     <x:row r="135" ht="25" customHeight="1">
       <x:c r="A135" s="10"/>
@@ -19723,6 +20040,7 @@
       <x:c r="DU135" s="106"/>
       <x:c r="DV135" s="106"/>
       <x:c r="DW135" s="106"/>
+      <x:c r="DX135" s="109"/>
     </x:row>
     <x:row r="136" ht="25" customHeight="1">
       <x:c r="A136" s="10"/>
@@ -19812,6 +20130,7 @@
       <x:c r="DU136" s="106"/>
       <x:c r="DV136" s="106"/>
       <x:c r="DW136" s="106"/>
+      <x:c r="DX136" s="109"/>
     </x:row>
     <x:row r="137" ht="25" customHeight="1">
       <x:c r="A137" s="10"/>
@@ -19901,6 +20220,7 @@
       <x:c r="DU137" s="106"/>
       <x:c r="DV137" s="106"/>
       <x:c r="DW137" s="106"/>
+      <x:c r="DX137" s="109"/>
     </x:row>
     <x:row r="138" ht="25" customHeight="1">
       <x:c r="A138" s="10"/>
@@ -19990,6 +20310,7 @@
       <x:c r="DU138" s="106"/>
       <x:c r="DV138" s="106"/>
       <x:c r="DW138" s="106"/>
+      <x:c r="DX138" s="109"/>
     </x:row>
     <x:row r="139" ht="25" customHeight="1">
       <x:c r="A139" s="10"/>
@@ -20079,6 +20400,7 @@
       <x:c r="DU139" s="106"/>
       <x:c r="DV139" s="106"/>
       <x:c r="DW139" s="106"/>
+      <x:c r="DX139" s="109"/>
     </x:row>
     <x:row r="140" ht="25" customHeight="1">
       <x:c r="A140" s="10"/>
@@ -20168,6 +20490,7 @@
       <x:c r="DU140" s="106"/>
       <x:c r="DV140" s="106"/>
       <x:c r="DW140" s="106"/>
+      <x:c r="DX140" s="109"/>
     </x:row>
     <x:row r="141" ht="25" customHeight="1">
       <x:c r="A141" s="10"/>
@@ -20257,6 +20580,7 @@
       <x:c r="DU141" s="106"/>
       <x:c r="DV141" s="106"/>
       <x:c r="DW141" s="106"/>
+      <x:c r="DX141" s="109"/>
     </x:row>
     <x:row r="142" ht="25" customHeight="1">
       <x:c r="A142" s="10"/>
@@ -20346,6 +20670,7 @@
       <x:c r="DU142" s="106"/>
       <x:c r="DV142" s="106"/>
       <x:c r="DW142" s="106"/>
+      <x:c r="DX142" s="109"/>
     </x:row>
     <x:row r="143" ht="25" customHeight="1">
       <x:c r="A143" s="10"/>
@@ -20435,6 +20760,7 @@
       <x:c r="DU143" s="106"/>
       <x:c r="DV143" s="106"/>
       <x:c r="DW143" s="106"/>
+      <x:c r="DX143" s="109"/>
     </x:row>
     <x:row r="144" ht="25" customHeight="1">
       <x:c r="A144" s="10"/>
@@ -20524,6 +20850,7 @@
       <x:c r="DU144" s="106"/>
       <x:c r="DV144" s="106"/>
       <x:c r="DW144" s="106"/>
+      <x:c r="DX144" s="109"/>
     </x:row>
     <x:row r="145" ht="25" customHeight="1">
       <x:c r="A145" s="10"/>
@@ -20613,6 +20940,7 @@
       <x:c r="DU145" s="106"/>
       <x:c r="DV145" s="106"/>
       <x:c r="DW145" s="106"/>
+      <x:c r="DX145" s="109"/>
     </x:row>
     <x:row r="146" ht="25" customHeight="1">
       <x:c r="A146" s="10"/>
@@ -20702,6 +21030,7 @@
       <x:c r="DU146" s="106"/>
       <x:c r="DV146" s="106"/>
       <x:c r="DW146" s="106"/>
+      <x:c r="DX146" s="109"/>
     </x:row>
     <x:row r="147" ht="25" customHeight="1">
       <x:c r="A147" s="10"/>
@@ -20791,6 +21120,7 @@
       <x:c r="DU147" s="106"/>
       <x:c r="DV147" s="106"/>
       <x:c r="DW147" s="106"/>
+      <x:c r="DX147" s="109"/>
     </x:row>
     <x:row r="148" ht="25" customHeight="1">
       <x:c r="A148" s="10"/>
@@ -20880,6 +21210,7 @@
       <x:c r="DU148" s="106"/>
       <x:c r="DV148" s="106"/>
       <x:c r="DW148" s="106"/>
+      <x:c r="DX148" s="109"/>
     </x:row>
     <x:row r="149" ht="25" customHeight="1">
       <x:c r="A149" s="10"/>
@@ -20969,6 +21300,7 @@
       <x:c r="DU149" s="106"/>
       <x:c r="DV149" s="106"/>
       <x:c r="DW149" s="106"/>
+      <x:c r="DX149" s="109"/>
     </x:row>
     <x:row r="150" ht="25" customHeight="1">
       <x:c r="A150" s="10"/>
@@ -21058,6 +21390,7 @@
       <x:c r="DU150" s="106"/>
       <x:c r="DV150" s="106"/>
       <x:c r="DW150" s="106"/>
+      <x:c r="DX150" s="109"/>
     </x:row>
     <x:row r="151" ht="25" customHeight="1">
       <x:c r="A151" s="10"/>
@@ -21147,6 +21480,7 @@
       <x:c r="DU151" s="106"/>
       <x:c r="DV151" s="106"/>
       <x:c r="DW151" s="106"/>
+      <x:c r="DX151" s="109"/>
     </x:row>
     <x:row r="152" ht="25" customHeight="1">
       <x:c r="A152" s="10"/>
@@ -21236,6 +21570,7 @@
       <x:c r="DU152" s="106"/>
       <x:c r="DV152" s="106"/>
       <x:c r="DW152" s="106"/>
+      <x:c r="DX152" s="109"/>
     </x:row>
     <x:row r="153" ht="25" customHeight="1">
       <x:c r="A153" s="10"/>
@@ -21325,6 +21660,7 @@
       <x:c r="DU153" s="106"/>
       <x:c r="DV153" s="106"/>
       <x:c r="DW153" s="106"/>
+      <x:c r="DX153" s="109"/>
     </x:row>
     <x:row r="154" ht="25" customHeight="1">
       <x:c r="A154" s="10"/>
@@ -21414,6 +21750,7 @@
       <x:c r="DU154" s="106"/>
       <x:c r="DV154" s="106"/>
       <x:c r="DW154" s="106"/>
+      <x:c r="DX154" s="109"/>
     </x:row>
     <x:row r="155" ht="25" customHeight="1">
       <x:c r="A155" s="10"/>
@@ -21503,6 +21840,7 @@
       <x:c r="DU155" s="106"/>
       <x:c r="DV155" s="106"/>
       <x:c r="DW155" s="106"/>
+      <x:c r="DX155" s="109"/>
     </x:row>
     <x:row r="156" ht="25" customHeight="1">
       <x:c r="A156" s="10"/>
@@ -21592,6 +21930,7 @@
       <x:c r="DU156" s="106"/>
       <x:c r="DV156" s="106"/>
       <x:c r="DW156" s="106"/>
+      <x:c r="DX156" s="109"/>
     </x:row>
     <x:row r="157" ht="25" customHeight="1">
       <x:c r="A157" s="10"/>
@@ -21681,6 +22020,7 @@
       <x:c r="DU157" s="106"/>
       <x:c r="DV157" s="106"/>
       <x:c r="DW157" s="106"/>
+      <x:c r="DX157" s="109"/>
     </x:row>
     <x:row r="158" ht="25" customHeight="1">
       <x:c r="A158" s="10"/>
@@ -21770,6 +22110,7 @@
       <x:c r="DU158" s="106"/>
       <x:c r="DV158" s="106"/>
       <x:c r="DW158" s="106"/>
+      <x:c r="DX158" s="109"/>
     </x:row>
     <x:row r="159" ht="25" customHeight="1">
       <x:c r="A159" s="10"/>
@@ -21859,6 +22200,7 @@
       <x:c r="DU159" s="106"/>
       <x:c r="DV159" s="106"/>
       <x:c r="DW159" s="106"/>
+      <x:c r="DX159" s="109"/>
     </x:row>
     <x:row r="160" ht="25" customHeight="1">
       <x:c r="A160" s="10"/>
@@ -21948,6 +22290,7 @@
       <x:c r="DU160" s="106"/>
       <x:c r="DV160" s="106"/>
       <x:c r="DW160" s="106"/>
+      <x:c r="DX160" s="109"/>
     </x:row>
     <x:row r="161" ht="25" customHeight="1">
       <x:c r="A161" s="10"/>
@@ -22037,6 +22380,7 @@
       <x:c r="DU161" s="106"/>
       <x:c r="DV161" s="106"/>
       <x:c r="DW161" s="106"/>
+      <x:c r="DX161" s="109"/>
     </x:row>
     <x:row r="162" ht="25" customHeight="1">
       <x:c r="A162" s="10"/>
@@ -22126,6 +22470,7 @@
       <x:c r="DU162" s="106"/>
       <x:c r="DV162" s="106"/>
       <x:c r="DW162" s="106"/>
+      <x:c r="DX162" s="109"/>
     </x:row>
     <x:row r="163" ht="25" customHeight="1">
       <x:c r="A163" s="10"/>
@@ -22215,6 +22560,7 @@
       <x:c r="DU163" s="106"/>
       <x:c r="DV163" s="106"/>
       <x:c r="DW163" s="106"/>
+      <x:c r="DX163" s="109"/>
     </x:row>
     <x:row r="164" ht="25" customHeight="1">
       <x:c r="A164" s="10"/>
@@ -22304,6 +22650,7 @@
       <x:c r="DU164" s="106"/>
       <x:c r="DV164" s="106"/>
       <x:c r="DW164" s="106"/>
+      <x:c r="DX164" s="109"/>
     </x:row>
     <x:row r="165" ht="25" customHeight="1">
       <x:c r="A165" s="10"/>
@@ -22393,6 +22740,7 @@
       <x:c r="DU165" s="106"/>
       <x:c r="DV165" s="106"/>
       <x:c r="DW165" s="106"/>
+      <x:c r="DX165" s="109"/>
     </x:row>
     <x:row r="166" ht="25" customHeight="1">
       <x:c r="A166" s="10"/>
@@ -22482,6 +22830,7 @@
       <x:c r="DU166" s="106"/>
       <x:c r="DV166" s="106"/>
       <x:c r="DW166" s="106"/>
+      <x:c r="DX166" s="109"/>
     </x:row>
     <x:row r="167" ht="25" customHeight="1">
       <x:c r="A167" s="10"/>
@@ -22571,6 +22920,7 @@
       <x:c r="DU167" s="106"/>
       <x:c r="DV167" s="106"/>
       <x:c r="DW167" s="106"/>
+      <x:c r="DX167" s="109"/>
     </x:row>
     <x:row r="168" ht="25" customHeight="1">
       <x:c r="A168" s="10"/>
@@ -22660,6 +23010,7 @@
       <x:c r="DU168" s="106"/>
       <x:c r="DV168" s="106"/>
       <x:c r="DW168" s="106"/>
+      <x:c r="DX168" s="109"/>
     </x:row>
     <x:row r="169" ht="25" customHeight="1">
       <x:c r="A169" s="10"/>
@@ -22749,6 +23100,7 @@
       <x:c r="DU169" s="106"/>
       <x:c r="DV169" s="106"/>
       <x:c r="DW169" s="106"/>
+      <x:c r="DX169" s="109"/>
     </x:row>
     <x:row r="170" ht="25" customHeight="1">
       <x:c r="A170" s="10"/>
@@ -22838,6 +23190,7 @@
       <x:c r="DU170" s="106"/>
       <x:c r="DV170" s="106"/>
       <x:c r="DW170" s="106"/>
+      <x:c r="DX170" s="109"/>
     </x:row>
     <x:row r="171" ht="25" customHeight="1">
       <x:c r="A171" s="10"/>
@@ -22927,6 +23280,7 @@
       <x:c r="DU171" s="106"/>
       <x:c r="DV171" s="106"/>
       <x:c r="DW171" s="106"/>
+      <x:c r="DX171" s="109"/>
     </x:row>
     <x:row r="172" ht="25" customHeight="1">
       <x:c r="A172" s="10"/>
@@ -23016,6 +23370,7 @@
       <x:c r="DU172" s="106"/>
       <x:c r="DV172" s="106"/>
       <x:c r="DW172" s="106"/>
+      <x:c r="DX172" s="109"/>
     </x:row>
     <x:row r="173" ht="25" customHeight="1">
       <x:c r="A173" s="10"/>
@@ -23105,6 +23460,7 @@
       <x:c r="DU173" s="106"/>
       <x:c r="DV173" s="106"/>
       <x:c r="DW173" s="106"/>
+      <x:c r="DX173" s="109"/>
     </x:row>
     <x:row r="174" ht="25" customHeight="1">
       <x:c r="A174" s="10"/>
@@ -23194,6 +23550,7 @@
       <x:c r="DU174" s="106"/>
       <x:c r="DV174" s="106"/>
       <x:c r="DW174" s="106"/>
+      <x:c r="DX174" s="109"/>
     </x:row>
     <x:row r="175" ht="25" customHeight="1">
       <x:c r="A175" s="10"/>
@@ -23283,6 +23640,7 @@
       <x:c r="DU175" s="106"/>
       <x:c r="DV175" s="106"/>
       <x:c r="DW175" s="106"/>
+      <x:c r="DX175" s="109"/>
     </x:row>
     <x:row r="176" ht="25" customHeight="1">
       <x:c r="A176" s="10"/>
@@ -23372,6 +23730,7 @@
       <x:c r="DU176" s="106"/>
       <x:c r="DV176" s="106"/>
       <x:c r="DW176" s="106"/>
+      <x:c r="DX176" s="109"/>
     </x:row>
     <x:row r="177" ht="25" customHeight="1">
       <x:c r="A177" s="10"/>
@@ -23461,6 +23820,7 @@
       <x:c r="DU177" s="106"/>
       <x:c r="DV177" s="106"/>
       <x:c r="DW177" s="106"/>
+      <x:c r="DX177" s="109"/>
     </x:row>
     <x:row r="178" ht="25" customHeight="1">
       <x:c r="A178" s="10"/>
@@ -23550,6 +23910,7 @@
       <x:c r="DU178" s="106"/>
       <x:c r="DV178" s="106"/>
       <x:c r="DW178" s="106"/>
+      <x:c r="DX178" s="109"/>
     </x:row>
     <x:row r="179" ht="25" customHeight="1">
       <x:c r="A179" s="10"/>
@@ -23639,6 +24000,7 @@
       <x:c r="DU179" s="106"/>
       <x:c r="DV179" s="106"/>
       <x:c r="DW179" s="106"/>
+      <x:c r="DX179" s="109"/>
     </x:row>
     <x:row r="180" ht="25" customHeight="1">
       <x:c r="A180" s="10"/>
@@ -23728,6 +24090,7 @@
       <x:c r="DU180" s="106"/>
       <x:c r="DV180" s="106"/>
       <x:c r="DW180" s="106"/>
+      <x:c r="DX180" s="109"/>
     </x:row>
     <x:row r="181" ht="25" customHeight="1">
       <x:c r="A181" s="10"/>
@@ -23817,6 +24180,7 @@
       <x:c r="DU181" s="106"/>
       <x:c r="DV181" s="106"/>
       <x:c r="DW181" s="106"/>
+      <x:c r="DX181" s="109"/>
     </x:row>
     <x:row r="182" ht="25" customHeight="1">
       <x:c r="A182" s="10"/>
@@ -23906,6 +24270,7 @@
       <x:c r="DU182" s="106"/>
       <x:c r="DV182" s="106"/>
       <x:c r="DW182" s="106"/>
+      <x:c r="DX182" s="109"/>
     </x:row>
     <x:row r="183" ht="25" customHeight="1">
       <x:c r="A183" s="10"/>
@@ -23995,6 +24360,7 @@
       <x:c r="DU183" s="106"/>
       <x:c r="DV183" s="106"/>
       <x:c r="DW183" s="106"/>
+      <x:c r="DX183" s="109"/>
     </x:row>
     <x:row r="184" ht="25" customHeight="1">
       <x:c r="A184" s="10"/>
@@ -24084,6 +24450,7 @@
       <x:c r="DU184" s="106"/>
       <x:c r="DV184" s="106"/>
       <x:c r="DW184" s="106"/>
+      <x:c r="DX184" s="109"/>
     </x:row>
     <x:row r="185" ht="25" customHeight="1">
       <x:c r="A185" s="10"/>
@@ -24173,6 +24540,7 @@
       <x:c r="DU185" s="106"/>
       <x:c r="DV185" s="106"/>
       <x:c r="DW185" s="106"/>
+      <x:c r="DX185" s="109"/>
     </x:row>
     <x:row r="186" ht="25" customHeight="1">
       <x:c r="A186" s="10"/>
@@ -24262,6 +24630,7 @@
       <x:c r="DU186" s="106"/>
       <x:c r="DV186" s="106"/>
       <x:c r="DW186" s="106"/>
+      <x:c r="DX186" s="109"/>
     </x:row>
     <x:row r="187" ht="25" customHeight="1">
       <x:c r="A187" s="10"/>
@@ -24351,6 +24720,7 @@
       <x:c r="DU187" s="106"/>
       <x:c r="DV187" s="106"/>
       <x:c r="DW187" s="106"/>
+      <x:c r="DX187" s="109"/>
     </x:row>
     <x:row r="188" ht="25" customHeight="1">
       <x:c r="A188" s="10"/>
@@ -24440,6 +24810,7 @@
       <x:c r="DU188" s="106"/>
       <x:c r="DV188" s="106"/>
       <x:c r="DW188" s="106"/>
+      <x:c r="DX188" s="109"/>
     </x:row>
     <x:row r="189" ht="25" customHeight="1">
       <x:c r="A189" s="10"/>
@@ -24529,6 +24900,7 @@
       <x:c r="DU189" s="106"/>
       <x:c r="DV189" s="106"/>
       <x:c r="DW189" s="106"/>
+      <x:c r="DX189" s="109"/>
     </x:row>
     <x:row r="190" ht="25" customHeight="1">
       <x:c r="A190" s="10"/>
@@ -24618,6 +24990,7 @@
       <x:c r="DU190" s="106"/>
       <x:c r="DV190" s="106"/>
       <x:c r="DW190" s="106"/>
+      <x:c r="DX190" s="109"/>
     </x:row>
     <x:row r="191" ht="25" customHeight="1">
       <x:c r="A191" s="10"/>
@@ -24707,6 +25080,7 @@
       <x:c r="DU191" s="106"/>
       <x:c r="DV191" s="106"/>
       <x:c r="DW191" s="106"/>
+      <x:c r="DX191" s="109"/>
     </x:row>
     <x:row r="192" ht="25" customHeight="1">
       <x:c r="A192" s="10"/>
@@ -24796,6 +25170,7 @@
       <x:c r="DU192" s="106"/>
       <x:c r="DV192" s="106"/>
       <x:c r="DW192" s="106"/>
+      <x:c r="DX192" s="109"/>
     </x:row>
     <x:row r="193" ht="25" customHeight="1">
       <x:c r="A193" s="10"/>
@@ -24885,6 +25260,7 @@
       <x:c r="DU193" s="106"/>
       <x:c r="DV193" s="106"/>
       <x:c r="DW193" s="106"/>
+      <x:c r="DX193" s="109"/>
     </x:row>
     <x:row r="194" ht="25" customHeight="1">
       <x:c r="A194" s="10"/>
@@ -24974,6 +25350,7 @@
       <x:c r="DU194" s="106"/>
       <x:c r="DV194" s="106"/>
       <x:c r="DW194" s="106"/>
+      <x:c r="DX194" s="109"/>
     </x:row>
     <x:row r="195" ht="25" customHeight="1">
       <x:c r="A195" s="10"/>
@@ -25063,6 +25440,7 @@
       <x:c r="DU195" s="106"/>
       <x:c r="DV195" s="106"/>
       <x:c r="DW195" s="106"/>
+      <x:c r="DX195" s="109"/>
     </x:row>
     <x:row r="196" ht="25" customHeight="1">
       <x:c r="A196" s="10"/>
@@ -25152,6 +25530,7 @@
       <x:c r="DU196" s="106"/>
       <x:c r="DV196" s="106"/>
       <x:c r="DW196" s="106"/>
+      <x:c r="DX196" s="109"/>
     </x:row>
     <x:row r="197" ht="25" customHeight="1">
       <x:c r="A197" s="10"/>
@@ -25241,6 +25620,7 @@
       <x:c r="DU197" s="106"/>
       <x:c r="DV197" s="106"/>
       <x:c r="DW197" s="106"/>
+      <x:c r="DX197" s="109"/>
     </x:row>
     <x:row r="198" ht="25" customHeight="1">
       <x:c r="A198" s="10"/>
@@ -25330,6 +25710,7 @@
       <x:c r="DU198" s="106"/>
       <x:c r="DV198" s="106"/>
       <x:c r="DW198" s="106"/>
+      <x:c r="DX198" s="109"/>
     </x:row>
     <x:row r="199" ht="25" customHeight="1">
       <x:c r="A199" s="10"/>
@@ -25419,6 +25800,7 @@
       <x:c r="DU199" s="106"/>
       <x:c r="DV199" s="106"/>
       <x:c r="DW199" s="106"/>
+      <x:c r="DX199" s="109"/>
     </x:row>
     <x:row r="200" ht="25" customHeight="1">
       <x:c r="A200" s="10"/>
@@ -25508,9 +25890,10 @@
       <x:c r="DU200" s="106"/>
       <x:c r="DV200" s="106"/>
       <x:c r="DW200" s="106"/>
+      <x:c r="DX200" s="109"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="48">
+  <x:dataValidations count="49">
     <x:dataValidation type="list" sqref="K2:K200">
       <x:formula1>"自身,敵一体,味方一体,自身中心,敵中心"</x:formula1>
     </x:dataValidation>
@@ -25657,10 +26040,13 @@
       <x:formula1>0.01</x:formula1>
       <x:formula2>1</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="DT2:DT200">
+      <x:formula1>"光の弾,衝撃波,魔方陣,斬撃,光の柱,煙と粒子,固有スプライト"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6846b5e35f994260"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R857149f39ec44096"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25776,7 +26162,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7276936c4c154f83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc36efa74d9a4e41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29149,7 +29535,7 @@
         <x:v>画像設定</x:v>
       </x:c>
       <x:c r="B276" s="89" t="str">
-        <x:v>発射物_画像番号（右端DT列）</x:v>
+        <x:v>発射物_素材（DT）／固有スプライト（DX）（右端DT列）</x:v>
       </x:c>
       <x:c r="C276" s="89" t="str">
         <x:v>空欄ならスキルIDと同じ番号。別の正の整数も可</x:v>
@@ -29408,6 +29794,174 @@
       </x:c>
       <x:c r="D295" s="89" t="str">
         <x:v>既存範囲スキルの自動調整はコード反映後から有効</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" ht="48" customHeight="1">
+      <x:c r="A298" s="142" t="str">
+        <x:v>共通素材と固有スプライト</x:v>
+      </x:c>
+      <x:c r="B298" s="142" t="str">
+        <x:v>列</x:v>
+      </x:c>
+      <x:c r="C298" s="142" t="str">
+        <x:v>設定方法</x:v>
+      </x:c>
+      <x:c r="D298" s="142" t="str">
+        <x:v>例</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" ht="48" customHeight="1">
+      <x:c r="A299" s="89" t="str">
+        <x:v>共通素材</x:v>
+      </x:c>
+      <x:c r="B299" s="89" t="str">
+        <x:v>DT：発射物_素材</x:v>
+      </x:c>
+      <x:c r="C299" s="89" t="str">
+        <x:v>6種類または固有スプライトを選択</x:v>
+      </x:c>
+      <x:c r="D299" s="89" t="str">
+        <x:v>光の弾／衝撃波／魔方陣／斬撃／光の柱／煙と粒子</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" ht="48" customHeight="1">
+      <x:c r="A300" s="89" t="str">
+        <x:v>画像の配置</x:v>
+      </x:c>
+      <x:c r="B300" s="89" t="str">
+        <x:v>Assets/素材/Projectile</x:v>
+      </x:c>
+      <x:c r="C300" s="89" t="str">
+        <x:v>光の弾.png または 1.光の弾.png のように配置</x:v>
+      </x:c>
+      <x:c r="D300" s="89" t="str">
+        <x:v>番号だけの1.png～6.pngも対応。名前付き画像を優先</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" ht="48" customHeight="1">
+      <x:c r="A301" s="89" t="str">
+        <x:v>固有画像</x:v>
+      </x:c>
+      <x:c r="B301" s="89" t="str">
+        <x:v>DX：発射物_固有スプライト</x:v>
+      </x:c>
+      <x:c r="C301" s="89" t="str">
+        <x:v>DTで固有スプライトを選び、DXに画像名またはパス</x:v>
+      </x:c>
+      <x:c r="D301" s="89" t="str">
+        <x:v>Assets/素材/Projectile/固有/竜の炎.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" ht="48" customHeight="1">
+      <x:c r="A302" s="89" t="str">
+        <x:v>複数Sprite画像</x:v>
+      </x:c>
+      <x:c r="B302" s="89" t="str">
+        <x:v>DX：発射物_固有スプライト</x:v>
+      </x:c>
+      <x:c r="C302" s="89" t="str">
+        <x:v>アセットパスの後に #Sprite名 を付ける</x:v>
+      </x:c>
+      <x:c r="D302" s="89" t="str">
+        <x:v>Assets/素材/Projectile/固有/炎.png#炎_0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" ht="48" customHeight="1">
+      <x:c r="A303" s="89" t="str">
+        <x:v>名前の重複</x:v>
+      </x:c>
+      <x:c r="B303" s="89" t="str">
+        <x:v>DX：発射物_固有スプライト</x:v>
+      </x:c>
+      <x:c r="C303" s="89" t="str">
+        <x:v>同じ画像名がある場合はアセットパスで指定</x:v>
+      </x:c>
+      <x:c r="D303" s="89" t="str">
+        <x:v>指定が曖昧な場合は取り込み前にエラー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" ht="48" customHeight="1">
+      <x:c r="A304" s="89" t="str">
+        <x:v>表示色</x:v>
+      </x:c>
+      <x:c r="B304" s="89" t="str">
+        <x:v>DF：発射物_色</x:v>
+      </x:c>
+      <x:c r="C304" s="89" t="str">
+        <x:v>#RRGGBB または #RRGGBBAA。白素材に乗算</x:v>
+      </x:c>
+      <x:c r="D304" s="89" t="str">
+        <x:v>火：#FF703FFF／水：#72DBFFFF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" ht="48" customHeight="1">
+      <x:c r="A305" s="89" t="str">
+        <x:v>透明度</x:v>
+      </x:c>
+      <x:c r="B305" s="89" t="str">
+        <x:v>DF：発射物_色</x:v>
+      </x:c>
+      <x:c r="C305" s="89" t="str">
+        <x:v>末尾AA。FF＝不透明、B3＝約70％、00＝透明</x:v>
+      </x:c>
+      <x:c r="D305" s="89" t="str">
+        <x:v>陣はB3～CC、弾はFFに再設定</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" ht="48" customHeight="1">
+      <x:c r="A306" s="89" t="str">
+        <x:v>元の色を保持</x:v>
+      </x:c>
+      <x:c r="B306" s="89" t="str">
+        <x:v>DF：発射物_色</x:v>
+      </x:c>
+      <x:c r="C306" s="89" t="str">
+        <x:v>色付き固有画像は白を指定</x:v>
+      </x:c>
+      <x:c r="D306" s="89" t="str">
+        <x:v>固有スプライト ＋ #FFFFFFFF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" ht="48" customHeight="1">
+      <x:c r="A307" s="89" t="str">
+        <x:v>表示サイズ</x:v>
+      </x:c>
+      <x:c r="B307" s="89" t="str">
+        <x:v>DE・DU列</x:v>
+      </x:c>
+      <x:c r="C307" s="89" t="str">
+        <x:v>弾は表示倍率、範囲技は範囲への自動調整を使用</x:v>
+      </x:c>
+      <x:c r="D307" s="89" t="str">
+        <x:v>素材を変えてもダメージ範囲は変わらない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" ht="48" customHeight="1">
+      <x:c r="A308" s="89" t="str">
+        <x:v>旧Excel互換</x:v>
+      </x:c>
+      <x:c r="B308" s="89" t="str">
+        <x:v>旧：発射物_画像番号</x:v>
+      </x:c>
+      <x:c r="C308" s="89" t="str">
+        <x:v>新しい素材列が空なら旧画像番号、未指定ならスキルID</x:v>
+      </x:c>
+      <x:c r="D308" s="89" t="str">
+        <x:v>旧列は新テンプレートでは素材選択列へ変更</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" ht="48" customHeight="1">
+      <x:c r="A309" s="89" t="str">
+        <x:v>反映方法</x:v>
+      </x:c>
+      <x:c r="B309" s="89" t="str">
+        <x:v>スキル取り込み</x:v>
+      </x:c>
+      <x:c r="C309" s="89" t="str">
+        <x:v>更新Excelを取り込むと既存Prefabの画像・色を更新</x:v>
+      </x:c>
+      <x:c r="D309" s="89" t="str">
+        <x:v>PrefabのID・参照は維持</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
